--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -601,7 +601,7 @@
         <v>45791</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -727,7 +727,7 @@
         <v>45835</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45275</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>45940</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>45961</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>44631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45981</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>46163</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2354,7 +2354,7 @@
         <v>46058</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>45786</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>45849</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45597</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>45945</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45509</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3055,7 +3055,7 @@
         <v>45786</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>45981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44844</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>46279</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>46170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45785</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
         <v>45957</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>45971</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>46167</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4234,7 +4234,7 @@
         <v>45993</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4352,7 +4352,7 @@
         <v>46163</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>45940</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4585,7 +4585,7 @@
         <v>45842</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44694</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45541</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>45930</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5054,7 +5054,7 @@
         <v>46163</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5172,7 +5172,7 @@
         <v>46010</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5290,7 +5290,7 @@
         <v>46253</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
         <v>46216</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5525,7 +5525,7 @@
         <v>46163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5638,7 +5638,7 @@
         <v>46163</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>45607</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>45929</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5981,7 +5981,7 @@
         <v>45926</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6098,7 +6098,7 @@
         <v>45246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>45985</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>45596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>46163</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>46265</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6673,7 +6673,7 @@
         <v>46198</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6790,7 +6790,7 @@
         <v>45373</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6902,7 +6902,7 @@
         <v>46283</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>46155</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44624</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44560</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45105</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>46128</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>46168</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>45910</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>45791</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>46170</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45594</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8269,7 +8269,7 @@
         <v>45518</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8379,7 +8379,7 @@
         <v>45063</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8490,7 +8490,7 @@
         <v>45575</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
         <v>45916</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8702,7 +8702,7 @@
         <v>44994</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>45940</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8932,7 +8932,7 @@
         <v>46150</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9047,7 +9047,7 @@
         <v>45321</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9153,7 +9153,7 @@
         <v>45943</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>45974</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44693</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>46125</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9605,7 +9605,7 @@
         <v>46167</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9716,7 +9716,7 @@
         <v>45978</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45978</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         <v>46198</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10057,7 +10057,7 @@
         <v>45971</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10172,7 +10172,7 @@
         <v>46168</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>45708</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10397,7 +10397,7 @@
         <v>46198</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10508,7 +10508,7 @@
         <v>45940</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10619,7 +10619,7 @@
         <v>44831</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45687</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>46010</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>44571</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44643</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>44872</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45761</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11496,7 +11496,7 @@
         <v>44477</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11601,7 +11601,7 @@
         <v>45189</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11711,7 +11711,7 @@
         <v>44960</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11816,7 +11816,7 @@
         <v>44888</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11926,7 +11926,7 @@
         <v>44929</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>45321</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12141,7 +12141,7 @@
         <v>45131</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12246,7 +12246,7 @@
         <v>45093</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44923</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12465,7 +12465,7 @@
         <v>45089</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12570,7 +12570,7 @@
         <v>45923</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12680,7 +12680,7 @@
         <v>45923</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>46150</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12904,7 +12904,7 @@
         <v>45866</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         <v>45761</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>44706</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13227,7 +13227,7 @@
         <v>46163</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13336,7 +13336,7 @@
         <v>45992</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13441,7 +13441,7 @@
         <v>46164</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46008</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13665,7 +13665,7 @@
         <v>44929</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13770,7 +13770,7 @@
         <v>45114</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45463</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>46009</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>46175</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14199,7 +14199,7 @@
         <v>45993</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45975</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14427,7 +14427,7 @@
         <v>44998</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45596</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45644</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>46247</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>46219</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14975,7 +14975,7 @@
         <v>46265</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>46269</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15195,7 +15195,7 @@
         <v>46276</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>45486</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>45791</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15524,7 +15524,7 @@
         <v>45825</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>44560</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>44771</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44869</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>44502</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>44503</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44550</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44730</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44482</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>44771</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44730</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44851</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>44872</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44720</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44560</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>44658</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>44827</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44590</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44706</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44785</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>44482</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44508</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44470</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>44715</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44482</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17551,7 +17551,7 @@
         <v>44893</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17624,7 +17624,7 @@
         <v>45569</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45594</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45611</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>44711</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>45317</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>45572</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>45622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18165,7 +18165,7 @@
         <v>45219</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>45687</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>44841</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45212</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18462,7 +18462,7 @@
         <v>45761</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44844</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18618,7 +18618,7 @@
         <v>45512</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18696,7 +18696,7 @@
         <v>44960</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45645</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>44852</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45519</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>44730</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>45450</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45105</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>44859</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19300,7 +19300,7 @@
         <v>44895</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19378,7 +19378,7 @@
         <v>45371</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19451,7 +19451,7 @@
         <v>45106</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45754</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>45161</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19680,7 +19680,7 @@
         <v>45646</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>45622</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45208</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19909,7 +19909,7 @@
         <v>45625</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19982,7 +19982,7 @@
         <v>44859</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20060,7 +20060,7 @@
         <v>45208</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20138,7 +20138,7 @@
         <v>45579</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20211,7 +20211,7 @@
         <v>45603</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20289,7 +20289,7 @@
         <v>44890</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20367,7 +20367,7 @@
         <v>45191</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20445,7 +20445,7 @@
         <v>45744</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20523,7 +20523,7 @@
         <v>45623</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20601,7 +20601,7 @@
         <v>44515</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>44893</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45502</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20825,7 +20825,7 @@
         <v>44994</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20898,7 +20898,7 @@
         <v>45512</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>45208</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21049,7 +21049,7 @@
         <v>45246</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45562</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21200,7 +21200,7 @@
         <v>45594</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>44916</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21356,7 +21356,7 @@
         <v>45210</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21434,7 +21434,7 @@
         <v>45210</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45202</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21590,7 +21590,7 @@
         <v>45253</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>45968</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21746,7 +21746,7 @@
         <v>45531</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21824,7 +21824,7 @@
         <v>45849</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21902,7 +21902,7 @@
         <v>45644</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>45607</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22053,7 +22053,7 @@
         <v>45954</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22126,7 +22126,7 @@
         <v>45825</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22199,7 +22199,7 @@
         <v>45637</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22272,7 +22272,7 @@
         <v>44859</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22350,7 +22350,7 @@
         <v>44687</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22423,7 +22423,7 @@
         <v>46136</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22501,7 +22501,7 @@
         <v>45827</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22579,7 +22579,7 @@
         <v>45537</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45902</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22730,7 +22730,7 @@
         <v>45813</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22808,7 +22808,7 @@
         <v>45562</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45860</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22959,7 +22959,7 @@
         <v>44789</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23032,7 +23032,7 @@
         <v>44893</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45891</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23183,7 +23183,7 @@
         <v>45895</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>44552</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23329,7 +23329,7 @@
         <v>45474</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23402,7 +23402,7 @@
         <v>45189</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23475,7 +23475,7 @@
         <v>45629</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23553,7 +23553,7 @@
         <v>45849</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23631,7 +23631,7 @@
         <v>45971</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>44978</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45898</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23860,7 +23860,7 @@
         <v>45562</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23938,7 +23938,7 @@
         <v>45541</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>45898</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45903</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24172,7 +24172,7 @@
         <v>44825</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>45799</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>45902</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>45903</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24484,7 +24484,7 @@
         <v>45903</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24562,7 +24562,7 @@
         <v>45588</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24635,7 +24635,7 @@
         <v>45845</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>46037</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45868</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>45225</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24937,7 +24937,7 @@
         <v>44459</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25010,7 +25010,7 @@
         <v>45574</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25088,7 +25088,7 @@
         <v>46062</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25166,7 +25166,7 @@
         <v>45301</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25239,7 +25239,7 @@
         <v>45301</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25312,7 +25312,7 @@
         <v>45297</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>45909</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25458,7 +25458,7 @@
         <v>46141</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25536,7 +25536,7 @@
         <v>45911</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25614,7 +25614,7 @@
         <v>45911</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25692,7 +25692,7 @@
         <v>45910</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>45910</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25843,7 +25843,7 @@
         <v>45910</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25916,7 +25916,7 @@
         <v>46141</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25994,7 +25994,7 @@
         <v>45911</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26072,7 +26072,7 @@
         <v>45581</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26150,7 +26150,7 @@
         <v>46141</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26228,7 +26228,7 @@
         <v>45335</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26301,7 +26301,7 @@
         <v>45917</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26374,7 +26374,7 @@
         <v>45639</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26452,7 +26452,7 @@
         <v>45915</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45512</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26603,7 +26603,7 @@
         <v>45196</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26681,7 +26681,7 @@
         <v>45902</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>45912</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45924</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45924</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26993,7 +26993,7 @@
         <v>45925</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45219</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27144,7 +27144,7 @@
         <v>45924</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27222,7 +27222,7 @@
         <v>45924</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>45924</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27378,7 +27378,7 @@
         <v>45924</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27456,7 +27456,7 @@
         <v>46066</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>45926</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27612,7 +27612,7 @@
         <v>45926</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27690,7 +27690,7 @@
         <v>45379</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27768,7 +27768,7 @@
         <v>45926</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>46142</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27924,7 +27924,7 @@
         <v>46142</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28002,7 +28002,7 @@
         <v>45099</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28080,7 +28080,7 @@
         <v>45113</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>46147</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45488</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>44970</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>44970</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28465,7 +28465,7 @@
         <v>45940</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28543,7 +28543,7 @@
         <v>45940</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45940</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28699,7 +28699,7 @@
         <v>45551</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28772,7 +28772,7 @@
         <v>45944</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28845,7 +28845,7 @@
         <v>44853</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28923,7 +28923,7 @@
         <v>45279</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>46148</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>45099</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29152,7 +29152,7 @@
         <v>45883</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29225,7 +29225,7 @@
         <v>46148</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29303,7 +29303,7 @@
         <v>46150</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45568</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29454,7 +29454,7 @@
         <v>45952</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29527,7 +29527,7 @@
         <v>45954</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29605,7 +29605,7 @@
         <v>45954</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29683,7 +29683,7 @@
         <v>45957</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29761,7 +29761,7 @@
         <v>45954</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29834,7 +29834,7 @@
         <v>44825</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29907,7 +29907,7 @@
         <v>45954</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29985,7 +29985,7 @@
         <v>45957</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45954</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45954</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>45954</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>45954</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>45957</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>45954</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>46150</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>45043</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30672,7 +30672,7 @@
         <v>45399</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30750,7 +30750,7 @@
         <v>45644</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30828,7 +30828,7 @@
         <v>45924</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30906,7 +30906,7 @@
         <v>45965</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30979,7 +30979,7 @@
         <v>45965</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31057,7 +31057,7 @@
         <v>45891</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45963</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>45891</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>45288</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45966</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31442,7 +31442,7 @@
         <v>45904</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31515,7 +31515,7 @@
         <v>45743</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31588,7 +31588,7 @@
         <v>46155</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31666,7 +31666,7 @@
         <v>45971</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31744,7 +31744,7 @@
         <v>45971</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31822,7 +31822,7 @@
         <v>45968</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31900,7 +31900,7 @@
         <v>45971</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31978,7 +31978,7 @@
         <v>44903</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>45579</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32124,7 +32124,7 @@
         <v>45579</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>46155</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32275,7 +32275,7 @@
         <v>45971</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32353,7 +32353,7 @@
         <v>45973</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32431,7 +32431,7 @@
         <v>45973</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32509,7 +32509,7 @@
         <v>45973</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32587,7 +32587,7 @@
         <v>45973</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32665,7 +32665,7 @@
         <v>46155</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32738,7 +32738,7 @@
         <v>45973</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32816,7 +32816,7 @@
         <v>45972</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32894,7 +32894,7 @@
         <v>45974</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45975</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33050,7 +33050,7 @@
         <v>45974</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33128,7 +33128,7 @@
         <v>45974</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45974</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33284,7 +33284,7 @@
         <v>45974</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33362,7 +33362,7 @@
         <v>46155</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33440,7 +33440,7 @@
         <v>46142</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45679</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>46113</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33664,7 +33664,7 @@
         <v>46155</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33742,7 +33742,7 @@
         <v>45981</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33820,7 +33820,7 @@
         <v>45705</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33893,7 +33893,7 @@
         <v>45112</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33971,7 +33971,7 @@
         <v>45198</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34049,7 +34049,7 @@
         <v>45265</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34122,7 +34122,7 @@
         <v>44865</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34200,7 +34200,7 @@
         <v>46160</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>45909</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34351,7 +34351,7 @@
         <v>45989</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34424,7 +34424,7 @@
         <v>46161</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45988</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>45929</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45929</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45887</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34814,7 +34814,7 @@
         <v>45891</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34892,7 +34892,7 @@
         <v>45988</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34970,7 +34970,7 @@
         <v>45989</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35043,7 +35043,7 @@
         <v>45989</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35116,7 +35116,7 @@
         <v>45989</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35194,7 +35194,7 @@
         <v>46160</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35272,7 +35272,7 @@
         <v>45481</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35345,7 +35345,7 @@
         <v>45411</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35423,7 +35423,7 @@
         <v>44771</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45624</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>45103</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>45775</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>45166</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35798,7 +35798,7 @@
         <v>45995</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35871,7 +35871,7 @@
         <v>45995</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35949,7 +35949,7 @@
         <v>45995</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36027,7 +36027,7 @@
         <v>46001</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36105,7 +36105,7 @@
         <v>45520</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36178,7 +36178,7 @@
         <v>46001</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36256,7 +36256,7 @@
         <v>44883</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36334,7 +36334,7 @@
         <v>46167</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36412,7 +36412,7 @@
         <v>46007</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>46007</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36568,7 +36568,7 @@
         <v>45791</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36646,7 +36646,7 @@
         <v>46008</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36724,7 +36724,7 @@
         <v>45062</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36802,7 +36802,7 @@
         <v>46008</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36880,7 +36880,7 @@
         <v>45168</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>46009</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37036,7 +37036,7 @@
         <v>46009</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37109,7 +37109,7 @@
         <v>46008</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37187,7 +37187,7 @@
         <v>46008</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37265,7 +37265,7 @@
         <v>46008</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37343,7 +37343,7 @@
         <v>46008</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>46008</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>46008</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45616</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>45765</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45594</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37806,7 +37806,7 @@
         <v>45740</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37879,7 +37879,7 @@
         <v>46010</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46010</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38035,7 +38035,7 @@
         <v>44476</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38113,7 +38113,7 @@
         <v>44533</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45569</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45761</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38347,7 +38347,7 @@
         <v>45589</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38420,7 +38420,7 @@
         <v>46029</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38498,7 +38498,7 @@
         <v>45110</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38571,7 +38571,7 @@
         <v>46038</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38644,7 +38644,7 @@
         <v>45833</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38717,7 +38717,7 @@
         <v>45166</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38795,7 +38795,7 @@
         <v>45834</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38868,7 +38868,7 @@
         <v>46171</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38941,7 +38941,7 @@
         <v>45119</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39019,7 +39019,7 @@
         <v>45526</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39092,7 +39092,7 @@
         <v>44730</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39170,7 +39170,7 @@
         <v>46002</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39248,7 +39248,7 @@
         <v>45373</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39321,7 +39321,7 @@
         <v>46171</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39399,7 +39399,7 @@
         <v>45243</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39472,7 +39472,7 @@
         <v>45512</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>46171</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45961</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39706,7 +39706,7 @@
         <v>46171</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39784,7 +39784,7 @@
         <v>46163</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39862,7 +39862,7 @@
         <v>46171</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39940,7 +39940,7 @@
         <v>45961</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40018,7 +40018,7 @@
         <v>46176</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>44915</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>46171</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40252,7 +40252,7 @@
         <v>46175</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40325,7 +40325,7 @@
         <v>46171</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40403,7 +40403,7 @@
         <v>46171</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40481,7 +40481,7 @@
         <v>45485</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>46167</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40637,7 +40637,7 @@
         <v>45644</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40710,7 +40710,7 @@
         <v>46136</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40788,7 +40788,7 @@
         <v>45603</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40866,7 +40866,7 @@
         <v>45621</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>44942</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41017,7 +41017,7 @@
         <v>46142</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41095,7 +41095,7 @@
         <v>45975</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41173,7 +41173,7 @@
         <v>45938</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>46163</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41324,7 +41324,7 @@
         <v>45224</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41397,7 +41397,7 @@
         <v>45831</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41470,7 +41470,7 @@
         <v>46007</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>46183</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45754</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41704,7 +41704,7 @@
         <v>44599</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41777,7 +41777,7 @@
         <v>46185</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41855,7 +41855,7 @@
         <v>46185</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41933,7 +41933,7 @@
         <v>45244</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42006,7 +42006,7 @@
         <v>44970</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42084,7 +42084,7 @@
         <v>45198</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>46190</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42240,7 +42240,7 @@
         <v>45596</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42318,7 +42318,7 @@
         <v>46183</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42396,7 +42396,7 @@
         <v>46191</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42469,7 +42469,7 @@
         <v>46184</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>46190</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42625,7 +42625,7 @@
         <v>46190</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42703,7 +42703,7 @@
         <v>46190</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>44879</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>46030</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42927,7 +42927,7 @@
         <v>46160</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43005,7 +43005,7 @@
         <v>46160</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>46198</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>45631</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>46160</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>46160</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43395,7 +43395,7 @@
         <v>44819</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43473,7 +43473,7 @@
         <v>46146</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>46146</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>46114</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43707,7 +43707,7 @@
         <v>45062</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43785,7 +43785,7 @@
         <v>45404</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>44826</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43936,7 +43936,7 @@
         <v>46119</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>46122</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44092,7 +44092,7 @@
         <v>46122</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44170,7 +44170,7 @@
         <v>46122</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>46122</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44326,7 +44326,7 @@
         <v>46122</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>46126</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44482,7 +44482,7 @@
         <v>46126</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44560,7 +44560,7 @@
         <v>46126</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45593</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>45156</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44789,7 +44789,7 @@
         <v>46128</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44862,7 +44862,7 @@
         <v>46155</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44940,7 +44940,7 @@
         <v>46171</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>46204</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45096,7 +45096,7 @@
         <v>45372</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>46134</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45247,7 +45247,7 @@
         <v>46135</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45325,7 +45325,7 @@
         <v>44459</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45403,7 +45403,7 @@
         <v>44820</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45481,7 +45481,7 @@
         <v>44820</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45559,7 +45559,7 @@
         <v>45960</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45637,7 +45637,7 @@
         <v>44708</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45715,7 +45715,7 @@
         <v>46247</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45793,7 +45793,7 @@
         <v>45988</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45871,7 +45871,7 @@
         <v>46062</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45949,7 +45949,7 @@
         <v>45835</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46027,7 +46027,7 @@
         <v>46247</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46105,7 +46105,7 @@
         <v>45218</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46178,7 +46178,7 @@
         <v>46136</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46256,7 +46256,7 @@
         <v>46247</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46329,7 +46329,7 @@
         <v>45243</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46402,7 +46402,7 @@
         <v>46248</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46475,7 +46475,7 @@
         <v>45560</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46553,7 +46553,7 @@
         <v>45519</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>46205</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46704,7 +46704,7 @@
         <v>46206</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46782,7 +46782,7 @@
         <v>45071</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46860,7 +46860,7 @@
         <v>46206</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -46938,7 +46938,7 @@
         <v>46190</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>45317</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>45680</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47162,7 +47162,7 @@
         <v>45205</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44581</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>45603</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47396,7 +47396,7 @@
         <v>45554</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45253</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47547,7 +47547,7 @@
         <v>45187</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47625,7 +47625,7 @@
         <v>45110</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47698,7 +47698,7 @@
         <v>44729</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47776,7 +47776,7 @@
         <v>46167</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47854,7 +47854,7 @@
         <v>46195</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47932,7 +47932,7 @@
         <v>46142</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>46253</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48088,7 +48088,7 @@
         <v>44960</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48166,7 +48166,7 @@
         <v>46255</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48244,7 +48244,7 @@
         <v>46255</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>44967</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48395,7 +48395,7 @@
         <v>46255</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48473,7 +48473,7 @@
         <v>46142</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48551,7 +48551,7 @@
         <v>46255</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>46255</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48707,7 +48707,7 @@
         <v>46255</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48785,7 +48785,7 @@
         <v>45258</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>46255</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48936,7 +48936,7 @@
         <v>46154</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49014,7 +49014,7 @@
         <v>45685</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49087,7 +49087,7 @@
         <v>46258</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>46258</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49243,7 +49243,7 @@
         <v>45541</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49321,7 +49321,7 @@
         <v>46260</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>46260</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49467,7 +49467,7 @@
         <v>45622</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49545,7 +49545,7 @@
         <v>46260</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49618,7 +49618,7 @@
         <v>46260</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49691,7 +49691,7 @@
         <v>46195</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49769,7 +49769,7 @@
         <v>46195</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49847,7 +49847,7 @@
         <v>46195</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
         <v>46195</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50003,7 +50003,7 @@
         <v>46195</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50081,7 +50081,7 @@
         <v>46198</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50159,7 +50159,7 @@
         <v>46195</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50237,7 +50237,7 @@
         <v>46195</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>46195</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>46195</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>46198</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50549,7 +50549,7 @@
         <v>46195</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50627,7 +50627,7 @@
         <v>45497</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50700,7 +50700,7 @@
         <v>46218</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50778,7 +50778,7 @@
         <v>46217</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50856,7 +50856,7 @@
         <v>45056</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45638</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51007,7 +51007,7 @@
         <v>46198</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51085,7 +51085,7 @@
         <v>46260</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51158,7 +51158,7 @@
         <v>46260</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51231,7 +51231,7 @@
         <v>46260</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>46219</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51382,7 +51382,7 @@
         <v>46265</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51460,7 +51460,7 @@
         <v>46262</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51538,7 +51538,7 @@
         <v>45602</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51611,7 +51611,7 @@
         <v>46265</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51689,7 +51689,7 @@
         <v>45176</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51762,7 +51762,7 @@
         <v>46220</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51840,7 +51840,7 @@
         <v>45622</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51918,7 +51918,7 @@
         <v>45622</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -51996,7 +51996,7 @@
         <v>45622</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52074,7 +52074,7 @@
         <v>45687</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52147,7 +52147,7 @@
         <v>45762</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52220,7 +52220,7 @@
         <v>45602</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52293,7 +52293,7 @@
         <v>46267</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52366,7 +52366,7 @@
         <v>46225</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52444,7 +52444,7 @@
         <v>45545</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52517,7 +52517,7 @@
         <v>46273</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52595,7 +52595,7 @@
         <v>46272</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52668,7 +52668,7 @@
         <v>46273</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52746,7 +52746,7 @@
         <v>46273</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52819,7 +52819,7 @@
         <v>46273</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52897,7 +52897,7 @@
         <v>46230</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -52975,7 +52975,7 @@
         <v>46230</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53053,7 +53053,7 @@
         <v>45784</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53126,7 +53126,7 @@
         <v>46206</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53204,7 +53204,7 @@
         <v>46275</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53277,7 +53277,7 @@
         <v>45565</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53350,7 +53350,7 @@
         <v>45230</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53428,7 +53428,7 @@
         <v>46275</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53501,7 +53501,7 @@
         <v>46279</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53579,7 +53579,7 @@
         <v>45609</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53657,7 +53657,7 @@
         <v>45784</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53730,7 +53730,7 @@
         <v>45134</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53808,7 +53808,7 @@
         <v>46233</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53886,7 +53886,7 @@
         <v>46279</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -53964,7 +53964,7 @@
         <v>46276</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54037,7 +54037,7 @@
         <v>46279</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54115,7 +54115,7 @@
         <v>45581</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54193,7 +54193,7 @@
         <v>45560</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54271,7 +54271,7 @@
         <v>46267</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54349,7 +54349,7 @@
         <v>45789</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54427,7 +54427,7 @@
         <v>45789</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54505,7 +54505,7 @@
         <v>45789</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54583,7 +54583,7 @@
         <v>46267</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54661,7 +54661,7 @@
         <v>45581</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54739,7 +54739,7 @@
         <v>45581</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54817,7 +54817,7 @@
         <v>45600</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54890,7 +54890,7 @@
         <v>45569</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -54968,7 +54968,7 @@
         <v>45460</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55041,7 +55041,7 @@
         <v>45789</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55119,7 +55119,7 @@
         <v>46280</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>46281</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55275,7 +55275,7 @@
         <v>45791</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55353,7 +55353,7 @@
         <v>45791</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55431,7 +55431,7 @@
         <v>45524</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55509,7 +55509,7 @@
         <v>45533</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55587,7 +55587,7 @@
         <v>46280</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55665,7 +55665,7 @@
         <v>45586</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55738,7 +55738,7 @@
         <v>45786</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55811,7 +55811,7 @@
         <v>44915</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55889,7 +55889,7 @@
         <v>45770</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -55962,7 +55962,7 @@
         <v>45791</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56040,7 +56040,7 @@
         <v>46241</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56118,7 +56118,7 @@
         <v>46241</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56196,7 +56196,7 @@
         <v>45453</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>45541</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56352,7 +56352,7 @@
         <v>45776</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56425,7 +56425,7 @@
         <v>45796</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56503,7 +56503,7 @@
         <v>46283</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56581,7 +56581,7 @@
         <v>45791</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56659,7 +56659,7 @@
         <v>45791</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56737,7 +56737,7 @@
         <v>46283</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56815,7 +56815,7 @@
         <v>46241</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56888,7 +56888,7 @@
         <v>46241</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -56966,7 +56966,7 @@
         <v>45499</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57039,7 +57039,7 @@
         <v>46241</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57117,7 +57117,7 @@
         <v>45799</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57195,7 +57195,7 @@
         <v>46283</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57273,7 +57273,7 @@
         <v>46283</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57351,7 +57351,7 @@
         <v>45800</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57429,7 +57429,7 @@
         <v>46282</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57507,7 +57507,7 @@
         <v>45800</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57585,7 +57585,7 @@
         <v>45805</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57663,7 +57663,7 @@
         <v>45810</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57741,7 +57741,7 @@
         <v>45810</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57819,7 +57819,7 @@
         <v>45810</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57897,7 +57897,7 @@
         <v>45569</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -57975,7 +57975,7 @@
         <v>45813</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58053,7 +58053,7 @@
         <v>45813</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58131,7 +58131,7 @@
         <v>45813</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58209,7 +58209,7 @@
         <v>45813</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58287,7 +58287,7 @@
         <v>45824</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58360,7 +58360,7 @@
         <v>45827</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58438,7 +58438,7 @@
         <v>45826</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58516,7 +58516,7 @@
         <v>45826</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>45831</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45831</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58750,7 +58750,7 @@
         <v>45832</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58828,7 +58828,7 @@
         <v>45835</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58906,7 +58906,7 @@
         <v>45840</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -58979,7 +58979,7 @@
         <v>45840</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59057,7 +59057,7 @@
         <v>45845</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59135,7 +59135,7 @@
         <v>45502</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59213,7 +59213,7 @@
         <v>45849</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>45525</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>45825</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59442,7 +59442,7 @@
         <v>45512</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59520,7 +59520,7 @@
         <v>45832</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59598,7 +59598,7 @@
         <v>45832</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59676,7 +59676,7 @@
         <v>45832</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59754,7 +59754,7 @@
         <v>45840</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59832,7 +59832,7 @@
         <v>44680</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59910,7 +59910,7 @@
         <v>45869</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59988,7 +59988,7 @@
         <v>45567</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>45337</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60139,7 +60139,7 @@
         <v>45761</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60212,7 +60212,7 @@
         <v>45875</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60285,7 +60285,7 @@
         <v>45167</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60363,7 +60363,7 @@
         <v>45015</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60441,7 +60441,7 @@
         <v>45216</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60519,7 +60519,7 @@
         <v>45400</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60597,7 +60597,7 @@
         <v>45391</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60675,7 +60675,7 @@
         <v>44805</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60753,7 +60753,7 @@
         <v>45015</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60831,7 +60831,7 @@
         <v>46190</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -601,7 +601,7 @@
         <v>45835</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45275</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>45940</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>45961</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>44631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45981</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>45849</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>46163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>46058</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45945</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45597</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>45509</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44844</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>46279</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>46170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45957</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45971</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45785</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45842</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45993</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>46163</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44694</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45930</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46010</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>46163</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>46253</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>46216</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>46163</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>46163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45541</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>45926</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>45929</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45985</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>45596</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>46265</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>46198</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45246</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>46283</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>46155</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>46163</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45373</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44624</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44560</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45105</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>46168</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>45910</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>45791</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>46170</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45063</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44831</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44994</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45575</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45916</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>45940</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45978</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>45943</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>45974</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>46150</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44693</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>46125</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>46167</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>45518</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45971</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>46198</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45594</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>46168</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45708</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>46198</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45321</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45940</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45978</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45687</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>46010</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>44571</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44643</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45463</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45993</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45923</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45923</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>44888</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45093</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>44929</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>45114</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45866</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>44960</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45992</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45189</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44923</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>46150</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>45761</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45089</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>44998</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45131</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45321</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>46163</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46164</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45825</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44477</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>46175</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>45975</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44560</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>45596</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>45644</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44706</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>46219</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>46265</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>46269</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45761</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>46276</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>46247</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44872</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44929</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45486</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45791</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>44771</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44869</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>44502</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>44503</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44550</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44730</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44482</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>44771</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44730</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44851</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>44872</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44720</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44560</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>44658</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>44827</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44590</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44706</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>44616</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44785</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>44482</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44508</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44470</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>44715</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44819</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45335</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45202</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44825</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45071</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44826</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45526</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44825</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>44859</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45219</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45372</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45208</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45450</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45105</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45119</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>44853</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45512</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45453</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45541</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>44883</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44852</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45796</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>44915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45499</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45621</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45502</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45791</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45776</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45791</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45791</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>46029</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45770</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45474</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44844</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45541</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45813</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45799</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45537</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>45800</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45607</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>44895</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45512</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45512</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>44994</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45891</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44515</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>46002</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45895</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45562</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45898</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45898</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45961</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45961</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>44978</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45519</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45902</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45903</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45903</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45903</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45799</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45868</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45909</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45800</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44893</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44893</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45910</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45910</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45911</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45911</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45911</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45910</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45915</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45603</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45917</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>45975</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45924</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>45831</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45224</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45912</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45924</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45924</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>46007</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45902</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45924</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45925</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45926</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45805</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44893</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45926</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45560</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45926</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45062</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45810</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45810</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>45810</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>45622</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45622</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45761</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45940</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45940</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45940</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45579</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>45944</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45740</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45187</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45952</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45954</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45954</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45954</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45623</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45954</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45954</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45954</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45954</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45954</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45957</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45954</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44970</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45957</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45957</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>46114</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44711</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>46119</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44960</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45569</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45891</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45891</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45624</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45963</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45924</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45603</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45629</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>46122</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>46122</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>46122</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45904</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>46122</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45966</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>46122</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45965</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45965</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45625</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>46126</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>46126</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45968</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45301</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45813</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45813</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45519</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45972</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45593</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45813</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45971</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45971</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45971</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45971</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45813</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45974</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45974</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>45973</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>45974</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45973</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>46126</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45973</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45973</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45974</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45974</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45062</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45975</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>46128</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>46134</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45210</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>45981</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45638</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45644</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31137,7 +31137,7 @@
         <v>45887</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45891</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45929</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>45929</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45568</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>45988</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45988</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>46135</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>45849</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>45909</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45989</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>45960</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45989</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45989</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45989</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>46136</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>46062</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>46136</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>44729</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45995</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45995</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45995</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45825</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>45849</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>45845</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>46066</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>46001</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46001</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>45827</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>45968</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>44581</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45225</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44820</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>44820</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45954</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>46007</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>46008</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>46007</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>46008</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45971</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>46008</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>46008</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>46008</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45835</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>46008</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>46008</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>46008</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>45687</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>46010</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>46010</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>46009</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45762</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>46009</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45531</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45562</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45860</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45902</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45765</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45574</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45824</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45826</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>46037</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45588</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44916</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>46141</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>46141</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45826</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>45581</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45827</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>46141</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>46142</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>45497</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>46142</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45106</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>46062</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>46148</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>46147</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45411</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>46150</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45832</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>46150</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45831</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45831</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>46148</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44942</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>45603</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>44730</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45973</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45883</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45637</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>46142</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45835</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>46155</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>45679</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>46155</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>46155</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>46155</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>46155</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>46113</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45099</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>46160</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45265</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46160</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>46161</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45761</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45840</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45840</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45845</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45502</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45288</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45849</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45525</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45791</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45825</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>46167</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>44865</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>45833</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45834</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45399</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>46038</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>46171</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45512</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>46171</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>45832</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45832</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45840</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>46171</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45832</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45569</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>46175</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45567</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>46171</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>44476</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>44680</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>46171</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>46171</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>46171</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>46163</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>46171</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>46176</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41970,7 +41970,7 @@
         <v>46167</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45869</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45258</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45404</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45938</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>46136</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45110</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>46142</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>44533</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>46183</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45337</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46163</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>46185</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>46185</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45572</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45488</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>45596</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43266,7 +43266,7 @@
         <v>45761</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>46184</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>46190</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>46190</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>46190</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>45113</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>46183</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>45602</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43880,7 +43880,7 @@
         <v>46190</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>45112</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>46191</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45875</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45644</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45639</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>46030</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>46160</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45569</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46146</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>46146</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>46160</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>46160</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>46160</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>46198</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45541</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45622</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45189</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>46171</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>45191</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>45622</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45594</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45198</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>46155</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>46190</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45805,7 +45805,7 @@
         <v>46205</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>46204</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>46248</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>46142</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45512</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45622</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45622</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>46167</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45099</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>46206</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>46206</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45687</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45168</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>45208</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>46195</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>46253</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47043,7 +47043,7 @@
         <v>44789</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>45166</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>44708</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>44687</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>46255</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45210</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>44841</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47574,7 +47574,7 @@
         <v>46255</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>46255</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45754</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>46255</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>46255</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45645</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>46255</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>46255</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45244</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>46198</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>46198</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>46195</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>46154</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>46198</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>46260</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>46260</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>46258</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>46195</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>46195</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>46195</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>45156</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>46260</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>46260</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>46260</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>46260</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>46260</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>46195</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>46142</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>46258</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>46195</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>46195</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>46195</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45685</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>45219</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50176,7 +50176,7 @@
         <v>46195</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50254,7 +50254,7 @@
         <v>45253</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>46195</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>45253</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>46217</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50566,7 +50566,7 @@
         <v>46218</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46219</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>46262</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45198</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>45208</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>45246</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>45754</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>46265</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>45744</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>46265</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>46220</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>46225</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>46267</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>44771</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>44915</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>44859</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>46230</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>46272</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>46206</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>46273</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>46230</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>46273</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52252,7 +52252,7 @@
         <v>46273</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>46273</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>46267</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52486,7 +52486,7 @@
         <v>46267</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>46275</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52637,7 +52637,7 @@
         <v>46275</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52710,7 +52710,7 @@
         <v>46276</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>45243</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52856,7 +52856,7 @@
         <v>46280</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>46279</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53012,7 +53012,7 @@
         <v>46279</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45616</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>46233</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53246,7 +53246,7 @@
         <v>46280</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53324,7 +53324,7 @@
         <v>45279</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53397,7 +53397,7 @@
         <v>45301</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53470,7 +53470,7 @@
         <v>46279</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45775</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>46281</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53704,7 +53704,7 @@
         <v>46282</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53782,7 +53782,7 @@
         <v>44879</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53855,7 +53855,7 @@
         <v>46241</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>46241</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>44970</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>46241</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>44552</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54235,7 +54235,7 @@
         <v>46283</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54313,7 +54313,7 @@
         <v>46283</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>46241</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>46241</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>46283</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>46283</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>46287</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54781,7 +54781,7 @@
         <v>46287</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54859,7 +54859,7 @@
         <v>44730</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>44599</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>44859</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>44960</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>46288</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>46247</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55317,7 +55317,7 @@
         <v>46290</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>46247</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>46247</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>46286</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45196</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>45205</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>46290</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55858,7 +55858,7 @@
         <v>46290</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>46290</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56014,7 +56014,7 @@
         <v>46286</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56092,7 +56092,7 @@
         <v>46290</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56170,7 +56170,7 @@
         <v>45594</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56248,7 +56248,7 @@
         <v>45594</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>46290</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45043</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56482,7 +56482,7 @@
         <v>44903</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>44970</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45161</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>45562</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>44890</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56862,7 +56862,7 @@
         <v>45371</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45243</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45373</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>45631</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57159,7 +57159,7 @@
         <v>45176</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57232,7 +57232,7 @@
         <v>45056</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>45166</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45110</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>45551</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57534,7 +57534,7 @@
         <v>44967</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>45554</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45520</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>45481</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57826,7 +57826,7 @@
         <v>45297</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57899,7 +57899,7 @@
         <v>45218</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57972,7 +57972,7 @@
         <v>45644</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45611</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58123,7 +58123,7 @@
         <v>45602</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>45103</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58269,7 +58269,7 @@
         <v>45680</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45579</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45579</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>44482</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>45317</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>45379</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45212</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58785,7 +58785,7 @@
         <v>45646</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45317</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58931,7 +58931,7 @@
         <v>45485</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         <v>45743</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59082,7 +59082,7 @@
         <v>45784</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59155,7 +59155,7 @@
         <v>45784</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59228,7 +59228,7 @@
         <v>45545</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59301,7 +59301,7 @@
         <v>45565</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45460</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>45230</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45581</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>45609</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45581</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>45134</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>45789</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>45789</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>45600</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>45533</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60144,7 +60144,7 @@
         <v>45569</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60222,7 +60222,7 @@
         <v>45789</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>45789</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60378,7 +60378,7 @@
         <v>45586</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60451,7 +60451,7 @@
         <v>45581</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45560</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>45791</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60685,7 +60685,7 @@
         <v>45786</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>45524</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60836,7 +60836,7 @@
         <v>45791</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60914,7 +60914,7 @@
         <v>45167</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60992,7 +60992,7 @@
         <v>45015</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61070,7 +61070,7 @@
         <v>45216</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61148,7 +61148,7 @@
         <v>45400</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61226,7 +61226,7 @@
         <v>45391</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61304,7 +61304,7 @@
         <v>44805</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61382,7 +61382,7 @@
         <v>45015</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61460,7 +61460,7 @@
         <v>46190</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -601,7 +601,7 @@
         <v>45835</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -735,7 +735,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -861,7 +861,7 @@
         <v>45275</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
         <v>45940</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1120,7 +1120,7 @@
         <v>45961</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1372,7 +1372,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>44631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1740,7 +1740,7 @@
         <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1861,7 +1861,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1985,7 +1985,7 @@
         <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>45981</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
         <v>45849</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>46163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2467,7 +2467,7 @@
         <v>46058</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>45786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45945</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2822,7 +2822,7 @@
         <v>45597</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2943,7 +2943,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3059,7 +3059,7 @@
         <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>45509</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>44844</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>46279</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>46170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45957</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3767,7 +3767,7 @@
         <v>45971</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45785</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4000,7 +4000,7 @@
         <v>46010</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4119,7 +4119,7 @@
         <v>45842</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4242,7 +4242,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4357,7 +4357,7 @@
         <v>45993</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4475,7 +4475,7 @@
         <v>46163</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4589,7 +4589,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>44694</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4822,7 +4822,7 @@
         <v>45930</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4940,7 +4940,7 @@
         <v>46010</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5058,7 +5058,7 @@
         <v>46163</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
         <v>46253</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>46216</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>46163</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5524,7 +5524,7 @@
         <v>46163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>45541</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5751,7 +5751,7 @@
         <v>45926</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5868,7 +5868,7 @@
         <v>45929</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5985,7 +5985,7 @@
         <v>45985</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6102,7 +6102,7 @@
         <v>45607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6215,7 +6215,7 @@
         <v>45596</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6332,7 +6332,7 @@
         <v>46265</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6449,7 +6449,7 @@
         <v>46198</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45246</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6678,7 +6678,7 @@
         <v>46283</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6791,7 +6791,7 @@
         <v>46155</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>46163</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7020,7 +7020,7 @@
         <v>45373</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44624</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7249,7 +7249,7 @@
         <v>44560</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7365,7 +7365,7 @@
         <v>45901</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45105</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>46168</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>46128</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>45910</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>45791</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>46170</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>45063</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8274,7 +8274,7 @@
         <v>44831</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8385,7 +8385,7 @@
         <v>44994</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8500,7 +8500,7 @@
         <v>45575</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8606,7 +8606,7 @@
         <v>45916</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8712,7 +8712,7 @@
         <v>45940</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>45978</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8942,7 +8942,7 @@
         <v>45943</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9053,7 +9053,7 @@
         <v>45974</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9168,7 +9168,7 @@
         <v>46150</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>44693</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9398,7 +9398,7 @@
         <v>46125</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9509,7 +9509,7 @@
         <v>46167</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>45518</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9730,7 +9730,7 @@
         <v>45971</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9845,7 +9845,7 @@
         <v>46198</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45594</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10062,7 +10062,7 @@
         <v>46168</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>45708</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10287,7 +10287,7 @@
         <v>46198</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>45321</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10504,7 +10504,7 @@
         <v>45940</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>45978</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10730,7 +10730,7 @@
         <v>45687</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>46010</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10956,7 +10956,7 @@
         <v>44571</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11066,7 +11066,7 @@
         <v>44643</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44872</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>45463</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45993</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>45923</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>45923</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>44888</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11835,7 +11835,7 @@
         <v>45093</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>44929</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12050,7 +12050,7 @@
         <v>45114</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45866</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>44960</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12369,7 +12369,7 @@
         <v>45992</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12474,7 +12474,7 @@
         <v>45189</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12584,7 +12584,7 @@
         <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>44923</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12803,7 +12803,7 @@
         <v>46150</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>45761</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13026,7 +13026,7 @@
         <v>45089</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13131,7 +13131,7 @@
         <v>44998</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13236,7 +13236,7 @@
         <v>45131</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13341,7 +13341,7 @@
         <v>45321</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13446,7 +13446,7 @@
         <v>46163</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>46164</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>45825</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13888,7 +13888,7 @@
         <v>44477</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13993,7 +13993,7 @@
         <v>46175</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>45975</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>44560</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14322,7 +14322,7 @@
         <v>45596</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14432,7 +14432,7 @@
         <v>45644</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14541,7 +14541,7 @@
         <v>44706</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14646,7 +14646,7 @@
         <v>46219</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14756,7 +14756,7 @@
         <v>46265</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>46269</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45761</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15081,7 +15081,7 @@
         <v>46276</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15191,7 +15191,7 @@
         <v>46247</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15305,7 +15305,7 @@
         <v>44872</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>44929</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15525,7 +15525,7 @@
         <v>45486</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45791</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>44771</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15817,7 +15817,7 @@
         <v>44869</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15890,7 +15890,7 @@
         <v>44502</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15963,7 +15963,7 @@
         <v>44503</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16041,7 +16041,7 @@
         <v>44550</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16119,7 +16119,7 @@
         <v>44730</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>44482</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16270,7 +16270,7 @@
         <v>44771</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16343,7 +16343,7 @@
         <v>44730</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16421,7 +16421,7 @@
         <v>44851</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16494,7 +16494,7 @@
         <v>44872</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16572,7 +16572,7 @@
         <v>44720</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16645,7 +16645,7 @@
         <v>44560</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16723,7 +16723,7 @@
         <v>44658</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16796,7 +16796,7 @@
         <v>44827</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44590</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44706</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>44616</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44785</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17176,7 +17176,7 @@
         <v>44482</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17249,7 +17249,7 @@
         <v>44508</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44470</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>44715</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17478,7 +17478,7 @@
         <v>44819</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17556,7 +17556,7 @@
         <v>45335</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17629,7 +17629,7 @@
         <v>45202</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>45705</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44825</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17858,7 +17858,7 @@
         <v>45071</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17936,7 +17936,7 @@
         <v>44826</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18014,7 +18014,7 @@
         <v>45526</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18087,7 +18087,7 @@
         <v>44825</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18160,7 +18160,7 @@
         <v>44859</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45219</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45372</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18389,7 +18389,7 @@
         <v>45208</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18467,7 +18467,7 @@
         <v>45450</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>45105</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45119</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>44853</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18769,7 +18769,7 @@
         <v>45512</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18847,7 +18847,7 @@
         <v>45453</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18925,7 +18925,7 @@
         <v>45541</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>44883</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19081,7 +19081,7 @@
         <v>44852</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19154,7 +19154,7 @@
         <v>45796</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>44915</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45499</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45621</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>45502</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45791</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19612,7 +19612,7 @@
         <v>45776</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19685,7 +19685,7 @@
         <v>45791</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19763,7 +19763,7 @@
         <v>45791</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>46029</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19919,7 +19919,7 @@
         <v>45770</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19992,7 +19992,7 @@
         <v>45474</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
         <v>44844</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45541</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20221,7 +20221,7 @@
         <v>45813</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20299,7 +20299,7 @@
         <v>45799</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20377,7 +20377,7 @@
         <v>45537</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20455,7 +20455,7 @@
         <v>45800</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>45607</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20611,7 +20611,7 @@
         <v>44895</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45512</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45512</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>44994</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20918,7 +20918,7 @@
         <v>45891</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20996,7 +20996,7 @@
         <v>44515</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21074,7 +21074,7 @@
         <v>46002</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21152,7 +21152,7 @@
         <v>45895</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21225,7 +21225,7 @@
         <v>45562</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21303,7 +21303,7 @@
         <v>45898</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45898</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21459,7 +21459,7 @@
         <v>45961</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21537,7 +21537,7 @@
         <v>45961</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21615,7 +21615,7 @@
         <v>44978</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>45519</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21761,7 +21761,7 @@
         <v>45902</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45903</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>45903</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45903</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45799</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22151,7 +22151,7 @@
         <v>45868</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45909</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45800</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>44893</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>44893</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45910</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22599,7 +22599,7 @@
         <v>45910</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22672,7 +22672,7 @@
         <v>45911</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>45911</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45911</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>45910</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45915</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45603</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23130,7 +23130,7 @@
         <v>45917</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23203,7 +23203,7 @@
         <v>45975</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23281,7 +23281,7 @@
         <v>45924</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23359,7 +23359,7 @@
         <v>45831</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45224</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23505,7 +23505,7 @@
         <v>45912</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45924</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45924</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>45924</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23817,7 +23817,7 @@
         <v>45924</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23895,7 +23895,7 @@
         <v>46007</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23973,7 +23973,7 @@
         <v>45902</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24051,7 +24051,7 @@
         <v>45924</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45925</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24202,7 +24202,7 @@
         <v>45926</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24280,7 +24280,7 @@
         <v>45805</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24358,7 +24358,7 @@
         <v>44893</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24431,7 +24431,7 @@
         <v>45926</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24509,7 +24509,7 @@
         <v>45560</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24587,7 +24587,7 @@
         <v>45926</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24665,7 +24665,7 @@
         <v>45062</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45810</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24821,7 +24821,7 @@
         <v>45810</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>45810</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24977,7 +24977,7 @@
         <v>45622</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25055,7 +25055,7 @@
         <v>45622</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45761</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>45940</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45940</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25367,7 +25367,7 @@
         <v>45940</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45579</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>45944</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45740</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25664,7 +25664,7 @@
         <v>45187</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45952</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45954</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45954</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25966,7 +25966,7 @@
         <v>45954</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>45623</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45954</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45954</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26278,7 +26278,7 @@
         <v>45954</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26351,7 +26351,7 @@
         <v>45954</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26429,7 +26429,7 @@
         <v>45954</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26502,7 +26502,7 @@
         <v>45957</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26580,7 +26580,7 @@
         <v>45954</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26653,7 +26653,7 @@
         <v>44970</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26731,7 +26731,7 @@
         <v>45957</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26809,7 +26809,7 @@
         <v>45957</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>46114</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26965,7 +26965,7 @@
         <v>44711</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>46119</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>44960</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45569</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27277,7 +27277,7 @@
         <v>45891</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45891</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27433,7 +27433,7 @@
         <v>45624</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27506,7 +27506,7 @@
         <v>45963</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27584,7 +27584,7 @@
         <v>45924</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45603</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45629</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27818,7 +27818,7 @@
         <v>46122</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>46122</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27974,7 +27974,7 @@
         <v>46122</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45904</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28125,7 +28125,7 @@
         <v>46122</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28203,7 +28203,7 @@
         <v>45966</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28281,7 +28281,7 @@
         <v>46122</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45965</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45965</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28510,7 +28510,7 @@
         <v>45625</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28583,7 +28583,7 @@
         <v>46126</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28661,7 +28661,7 @@
         <v>46126</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28739,7 +28739,7 @@
         <v>45968</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>45301</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28890,7 +28890,7 @@
         <v>45813</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45813</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29046,7 +29046,7 @@
         <v>45519</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29119,7 +29119,7 @@
         <v>45972</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29197,7 +29197,7 @@
         <v>45593</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29275,7 +29275,7 @@
         <v>45813</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>45971</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45971</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29509,7 +29509,7 @@
         <v>45971</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29587,7 +29587,7 @@
         <v>45971</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29665,7 +29665,7 @@
         <v>45813</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29743,7 +29743,7 @@
         <v>45974</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29821,7 +29821,7 @@
         <v>45974</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29899,7 +29899,7 @@
         <v>45973</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29977,7 +29977,7 @@
         <v>45974</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45973</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30133,7 +30133,7 @@
         <v>46126</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30211,7 +30211,7 @@
         <v>45973</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30289,7 +30289,7 @@
         <v>45973</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30367,7 +30367,7 @@
         <v>45974</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30445,7 +30445,7 @@
         <v>45974</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30523,7 +30523,7 @@
         <v>45062</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45975</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30679,7 +30679,7 @@
         <v>46128</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>46134</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45210</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30908,7 +30908,7 @@
         <v>45981</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30986,7 +30986,7 @@
         <v>45638</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31059,7 +31059,7 @@
         <v>45644</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31137,7 +31137,7 @@
         <v>45887</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>45891</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>45929</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>45929</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31449,7 +31449,7 @@
         <v>45568</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>45988</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31600,7 +31600,7 @@
         <v>45988</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31678,7 +31678,7 @@
         <v>46135</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>45849</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31834,7 +31834,7 @@
         <v>45909</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45989</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31980,7 +31980,7 @@
         <v>45960</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32058,7 +32058,7 @@
         <v>45989</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32131,7 +32131,7 @@
         <v>45989</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32209,7 +32209,7 @@
         <v>45989</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32282,7 +32282,7 @@
         <v>46136</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32360,7 +32360,7 @@
         <v>46062</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32438,7 +32438,7 @@
         <v>46136</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>44729</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32594,7 +32594,7 @@
         <v>45995</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32667,7 +32667,7 @@
         <v>45995</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32745,7 +32745,7 @@
         <v>45995</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>45825</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32896,7 +32896,7 @@
         <v>45849</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32974,7 +32974,7 @@
         <v>45845</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>46066</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33130,7 +33130,7 @@
         <v>46001</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33208,7 +33208,7 @@
         <v>46001</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33286,7 +33286,7 @@
         <v>45827</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33364,7 +33364,7 @@
         <v>45968</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33442,7 +33442,7 @@
         <v>44581</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33520,7 +33520,7 @@
         <v>45225</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33598,7 +33598,7 @@
         <v>44820</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>44820</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33754,7 +33754,7 @@
         <v>45954</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33827,7 +33827,7 @@
         <v>46007</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>46008</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33983,7 +33983,7 @@
         <v>46007</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34061,7 +34061,7 @@
         <v>46008</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34139,7 +34139,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45971</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>46008</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34373,7 +34373,7 @@
         <v>46008</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34451,7 +34451,7 @@
         <v>46008</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45835</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34607,7 +34607,7 @@
         <v>46008</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34685,7 +34685,7 @@
         <v>46008</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34763,7 +34763,7 @@
         <v>46008</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>45687</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>46010</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34992,7 +34992,7 @@
         <v>46010</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>46009</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35148,7 +35148,7 @@
         <v>45762</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35221,7 +35221,7 @@
         <v>46009</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35294,7 +35294,7 @@
         <v>45531</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35372,7 +35372,7 @@
         <v>45562</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45860</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45902</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
         <v>45765</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45574</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35752,7 +35752,7 @@
         <v>45824</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35825,7 +35825,7 @@
         <v>45826</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35903,7 +35903,7 @@
         <v>46037</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35976,7 +35976,7 @@
         <v>45588</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36049,7 +36049,7 @@
         <v>44916</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>46141</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36205,7 +36205,7 @@
         <v>46141</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45826</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36361,7 +36361,7 @@
         <v>45581</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>45827</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36517,7 +36517,7 @@
         <v>46141</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36595,7 +36595,7 @@
         <v>46142</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36673,7 +36673,7 @@
         <v>45497</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36746,7 +36746,7 @@
         <v>46142</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36824,7 +36824,7 @@
         <v>45106</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36897,7 +36897,7 @@
         <v>46062</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36975,7 +36975,7 @@
         <v>46148</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>46147</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>45411</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37209,7 +37209,7 @@
         <v>46150</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37287,7 +37287,7 @@
         <v>45832</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>46150</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45831</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37521,7 +37521,7 @@
         <v>45831</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>46148</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37677,7 +37677,7 @@
         <v>44942</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37750,7 +37750,7 @@
         <v>45603</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>44730</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37906,7 +37906,7 @@
         <v>45973</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45883</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38057,7 +38057,7 @@
         <v>45637</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38130,7 +38130,7 @@
         <v>46142</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38208,7 +38208,7 @@
         <v>45835</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38286,7 +38286,7 @@
         <v>46155</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>45679</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38432,7 +38432,7 @@
         <v>46155</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38510,7 +38510,7 @@
         <v>46155</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>46155</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>46155</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>46113</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45099</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>46160</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45265</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39046,7 +39046,7 @@
         <v>46160</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39124,7 +39124,7 @@
         <v>46161</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
         <v>45761</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45840</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39358,7 +39358,7 @@
         <v>45840</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39431,7 +39431,7 @@
         <v>45845</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>45502</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39587,7 +39587,7 @@
         <v>45288</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39660,7 +39660,7 @@
         <v>45849</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45525</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39811,7 +39811,7 @@
         <v>45791</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39889,7 +39889,7 @@
         <v>45825</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>46167</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40045,7 +40045,7 @@
         <v>44865</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>45833</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40196,7 +40196,7 @@
         <v>45834</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45399</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40347,7 +40347,7 @@
         <v>46038</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40420,7 +40420,7 @@
         <v>46171</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40498,7 +40498,7 @@
         <v>45512</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40576,7 +40576,7 @@
         <v>46171</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>45832</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40732,7 +40732,7 @@
         <v>45832</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40810,7 +40810,7 @@
         <v>45840</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>46171</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>45832</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41039,7 +41039,7 @@
         <v>45569</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41117,7 +41117,7 @@
         <v>46175</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41190,7 +41190,7 @@
         <v>45567</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>46171</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>44476</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41424,7 +41424,7 @@
         <v>44680</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41502,7 +41502,7 @@
         <v>46171</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41580,7 +41580,7 @@
         <v>46171</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41658,7 +41658,7 @@
         <v>46171</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41736,7 +41736,7 @@
         <v>46163</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41814,7 +41814,7 @@
         <v>46171</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41892,7 +41892,7 @@
         <v>46176</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41970,7 +41970,7 @@
         <v>46167</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45869</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45258</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45404</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45938</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42350,7 +42350,7 @@
         <v>46136</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>45110</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42501,7 +42501,7 @@
         <v>46142</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>44533</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>46183</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45337</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46163</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42881,7 +42881,7 @@
         <v>46185</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>46185</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43037,7 +43037,7 @@
         <v>45572</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43115,7 +43115,7 @@
         <v>45488</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43188,7 +43188,7 @@
         <v>45596</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43266,7 +43266,7 @@
         <v>45761</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43339,7 +43339,7 @@
         <v>46184</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>46190</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43495,7 +43495,7 @@
         <v>46190</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43573,7 +43573,7 @@
         <v>46190</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43651,7 +43651,7 @@
         <v>45113</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>46183</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43807,7 +43807,7 @@
         <v>45602</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43880,7 +43880,7 @@
         <v>46190</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43958,7 +43958,7 @@
         <v>45112</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44036,7 +44036,7 @@
         <v>46191</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44109,7 +44109,7 @@
         <v>45875</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>45644</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45639</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44333,7 +44333,7 @@
         <v>46030</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44406,7 +44406,7 @@
         <v>46160</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44484,7 +44484,7 @@
         <v>45569</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>46146</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44640,7 +44640,7 @@
         <v>46146</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44718,7 +44718,7 @@
         <v>46160</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>46160</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44874,7 +44874,7 @@
         <v>46160</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44952,7 +44952,7 @@
         <v>46198</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45030,7 +45030,7 @@
         <v>45541</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45108,7 +45108,7 @@
         <v>45622</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45186,7 +45186,7 @@
         <v>45189</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>46171</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>45191</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45415,7 +45415,7 @@
         <v>45622</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45493,7 +45493,7 @@
         <v>45594</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>45198</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45649,7 +45649,7 @@
         <v>46155</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45727,7 +45727,7 @@
         <v>46190</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45805,7 +45805,7 @@
         <v>46205</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>46204</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>46248</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46034,7 +46034,7 @@
         <v>46142</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46112,7 +46112,7 @@
         <v>45512</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46190,7 +46190,7 @@
         <v>45622</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46268,7 +46268,7 @@
         <v>45622</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46346,7 +46346,7 @@
         <v>46167</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45099</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46502,7 +46502,7 @@
         <v>46206</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>46206</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46658,7 +46658,7 @@
         <v>45687</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45168</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46809,7 +46809,7 @@
         <v>45208</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46887,7 +46887,7 @@
         <v>46195</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46965,7 +46965,7 @@
         <v>46253</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47043,7 +47043,7 @@
         <v>44789</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47116,7 +47116,7 @@
         <v>45166</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>44708</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>44687</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47345,7 +47345,7 @@
         <v>46255</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47423,7 +47423,7 @@
         <v>45210</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>44841</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47574,7 +47574,7 @@
         <v>46255</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47652,7 +47652,7 @@
         <v>46255</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45754</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47808,7 +47808,7 @@
         <v>46255</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47886,7 +47886,7 @@
         <v>46255</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45645</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48042,7 +48042,7 @@
         <v>46255</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48120,7 +48120,7 @@
         <v>46255</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48198,7 +48198,7 @@
         <v>45244</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48271,7 +48271,7 @@
         <v>46198</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>46198</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48427,7 +48427,7 @@
         <v>46195</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48505,7 +48505,7 @@
         <v>46154</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48583,7 +48583,7 @@
         <v>46198</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48661,7 +48661,7 @@
         <v>46260</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48734,7 +48734,7 @@
         <v>46260</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>46258</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>46195</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48963,7 +48963,7 @@
         <v>46195</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49041,7 +49041,7 @@
         <v>46195</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>45156</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>46260</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49265,7 +49265,7 @@
         <v>46260</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>46260</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49411,7 +49411,7 @@
         <v>46260</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49484,7 +49484,7 @@
         <v>46260</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49557,7 +49557,7 @@
         <v>46195</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49635,7 +49635,7 @@
         <v>46142</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49713,7 +49713,7 @@
         <v>46258</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49791,7 +49791,7 @@
         <v>46195</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49869,7 +49869,7 @@
         <v>46195</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49947,7 +49947,7 @@
         <v>46195</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50025,7 +50025,7 @@
         <v>45685</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50098,7 +50098,7 @@
         <v>45219</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50176,7 +50176,7 @@
         <v>46195</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50254,7 +50254,7 @@
         <v>45253</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50332,7 +50332,7 @@
         <v>46195</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50410,7 +50410,7 @@
         <v>45253</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50488,7 +50488,7 @@
         <v>46217</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50566,7 +50566,7 @@
         <v>46218</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46219</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50722,7 +50722,7 @@
         <v>46262</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50800,7 +50800,7 @@
         <v>45198</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50878,7 +50878,7 @@
         <v>45208</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50951,7 +50951,7 @@
         <v>45246</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51024,7 +51024,7 @@
         <v>45754</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51102,7 +51102,7 @@
         <v>46265</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51180,7 +51180,7 @@
         <v>45744</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51258,7 +51258,7 @@
         <v>46265</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51336,7 +51336,7 @@
         <v>46220</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51414,7 +51414,7 @@
         <v>46225</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51492,7 +51492,7 @@
         <v>46267</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51565,7 +51565,7 @@
         <v>44771</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51638,7 +51638,7 @@
         <v>44915</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51716,7 +51716,7 @@
         <v>44859</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>46230</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51872,7 +51872,7 @@
         <v>46272</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51945,7 +51945,7 @@
         <v>46206</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>46273</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52096,7 +52096,7 @@
         <v>46230</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52174,7 +52174,7 @@
         <v>46273</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52252,7 +52252,7 @@
         <v>46273</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52330,7 +52330,7 @@
         <v>46273</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52408,7 +52408,7 @@
         <v>46267</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52486,7 +52486,7 @@
         <v>46267</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52564,7 +52564,7 @@
         <v>46275</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52637,7 +52637,7 @@
         <v>46275</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52710,7 +52710,7 @@
         <v>46276</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52783,7 +52783,7 @@
         <v>45243</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52856,7 +52856,7 @@
         <v>46280</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>46279</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53012,7 +53012,7 @@
         <v>46279</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53090,7 +53090,7 @@
         <v>45616</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53168,7 +53168,7 @@
         <v>46233</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53246,7 +53246,7 @@
         <v>46280</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53324,7 +53324,7 @@
         <v>45279</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53397,7 +53397,7 @@
         <v>45301</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53470,7 +53470,7 @@
         <v>46279</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>45775</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53626,7 +53626,7 @@
         <v>46281</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53704,7 +53704,7 @@
         <v>46282</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53782,7 +53782,7 @@
         <v>44879</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53855,7 +53855,7 @@
         <v>46241</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>46241</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54011,7 +54011,7 @@
         <v>44970</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54089,7 +54089,7 @@
         <v>46241</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>44552</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54235,7 +54235,7 @@
         <v>46283</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54313,7 +54313,7 @@
         <v>46283</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>46241</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>46241</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>46283</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>46283</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54703,7 +54703,7 @@
         <v>46287</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54781,7 +54781,7 @@
         <v>46287</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54859,7 +54859,7 @@
         <v>44730</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54937,7 +54937,7 @@
         <v>44599</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>44859</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>44960</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>46288</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55239,7 +55239,7 @@
         <v>46247</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55317,7 +55317,7 @@
         <v>46290</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55395,7 +55395,7 @@
         <v>46247</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>46247</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>46286</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45196</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>45205</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>46290</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55858,7 +55858,7 @@
         <v>46290</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>46290</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56014,7 +56014,7 @@
         <v>46286</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56092,7 +56092,7 @@
         <v>46290</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56170,7 +56170,7 @@
         <v>45594</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56248,7 +56248,7 @@
         <v>45594</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56326,7 +56326,7 @@
         <v>46290</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45043</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56482,7 +56482,7 @@
         <v>44903</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>44970</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>45161</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56711,7 +56711,7 @@
         <v>45562</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56784,7 +56784,7 @@
         <v>44890</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56862,7 +56862,7 @@
         <v>45371</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56935,7 +56935,7 @@
         <v>45243</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>45373</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57081,7 +57081,7 @@
         <v>45631</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57159,7 +57159,7 @@
         <v>45176</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57232,7 +57232,7 @@
         <v>45056</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57310,7 +57310,7 @@
         <v>45166</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57388,7 +57388,7 @@
         <v>45110</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57461,7 +57461,7 @@
         <v>45551</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57534,7 +57534,7 @@
         <v>44967</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57607,7 +57607,7 @@
         <v>45554</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45520</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57753,7 +57753,7 @@
         <v>45481</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57826,7 +57826,7 @@
         <v>45297</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57899,7 +57899,7 @@
         <v>45218</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57972,7 +57972,7 @@
         <v>45644</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58045,7 +58045,7 @@
         <v>45611</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58123,7 +58123,7 @@
         <v>45602</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58196,7 +58196,7 @@
         <v>45103</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58269,7 +58269,7 @@
         <v>45680</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58342,7 +58342,7 @@
         <v>45579</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58415,7 +58415,7 @@
         <v>45579</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58488,7 +58488,7 @@
         <v>44482</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58561,7 +58561,7 @@
         <v>45317</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58634,7 +58634,7 @@
         <v>45379</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58712,7 +58712,7 @@
         <v>45212</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58785,7 +58785,7 @@
         <v>45646</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45317</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58931,7 +58931,7 @@
         <v>45485</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59009,7 +59009,7 @@
         <v>45743</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59082,7 +59082,7 @@
         <v>45784</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59155,7 +59155,7 @@
         <v>45784</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59228,7 +59228,7 @@
         <v>45545</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59301,7 +59301,7 @@
         <v>45565</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59374,7 +59374,7 @@
         <v>45460</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59447,7 +59447,7 @@
         <v>45230</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59525,7 +59525,7 @@
         <v>45581</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59603,7 +59603,7 @@
         <v>45609</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59681,7 +59681,7 @@
         <v>45581</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59759,7 +59759,7 @@
         <v>45134</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59837,7 +59837,7 @@
         <v>45789</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59915,7 +59915,7 @@
         <v>45789</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -59993,7 +59993,7 @@
         <v>45600</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60066,7 +60066,7 @@
         <v>45533</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60144,7 +60144,7 @@
         <v>45569</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60222,7 +60222,7 @@
         <v>45789</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>45789</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60378,7 +60378,7 @@
         <v>45586</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60451,7 +60451,7 @@
         <v>45581</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60529,7 +60529,7 @@
         <v>45560</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60607,7 +60607,7 @@
         <v>45791</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60685,7 +60685,7 @@
         <v>45786</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60758,7 +60758,7 @@
         <v>45524</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60836,7 +60836,7 @@
         <v>45791</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -60914,7 +60914,7 @@
         <v>45167</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -60992,7 +60992,7 @@
         <v>45015</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61070,7 +61070,7 @@
         <v>45216</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61148,7 +61148,7 @@
         <v>45400</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61226,7 +61226,7 @@
         <v>45391</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61304,7 +61304,7 @@
         <v>44805</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -61382,7 +61382,7 @@
         <v>45015</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -61460,7 +61460,7 @@
         <v>46190</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45940</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>45961</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>45981</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2233,7 +2233,7 @@
         <v>45849</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2346,7 +2346,7 @@
         <v>46163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2468,7 +2468,7 @@
         <v>46058</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>45786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45945</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2823,7 +2823,7 @@
         <v>45597</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2944,7 +2944,7 @@
         <v>45786</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3060,7 +3060,7 @@
         <v>45981</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45509</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
         <v>44844</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3417,7 +3417,7 @@
         <v>46279</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>46170</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>46010</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45957</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45971</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
         <v>45842</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4129,7 +4129,7 @@
         <v>45785</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4358,7 +4358,7 @@
         <v>45993</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>46163</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         <v>46275</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4636,10 +4636,10 @@
         <v>6</v>
       </c>
       <c r="T35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U35" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>45940</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4823,7 +4823,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4937,7 +4937,7 @@
         <v>46010</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5055,7 +5055,7 @@
         <v>45541</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5169,7 +5169,7 @@
         <v>45930</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5287,7 +5287,7 @@
         <v>46163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>46163</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>46163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>46216</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5748,7 +5748,7 @@
         <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>45926</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>45985</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6100,7 +6100,7 @@
         <v>45607</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45246</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6325,7 +6325,7 @@
         <v>45596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>46260</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>46260</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>46265</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6787,7 +6787,7 @@
         <v>46198</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         <v>46283</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>46155</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7134,7 +7134,7 @@
         <v>45373</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7246,7 +7246,7 @@
         <v>46163</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7358,7 +7358,7 @@
         <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7592,7 +7592,7 @@
         <v>45791</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7704,7 +7704,7 @@
         <v>45901</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7815,7 +7815,7 @@
         <v>44560</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>45105</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8047,7 +8047,7 @@
         <v>46128</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>46168</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>45910</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8390,7 +8390,7 @@
         <v>46170</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
         <v>44872</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>45594</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8723,7 +8723,7 @@
         <v>44831</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8834,7 +8834,7 @@
         <v>45518</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8944,7 +8944,7 @@
         <v>45916</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9050,7 +9050,7 @@
         <v>45923</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9161,7 +9161,7 @@
         <v>45940</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>45943</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>45063</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45978</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9613,7 +9613,7 @@
         <v>45974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>45575</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9834,7 +9834,7 @@
         <v>44923</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9944,7 +9944,7 @@
         <v>44994</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10059,7 +10059,7 @@
         <v>46150</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10174,7 +10174,7 @@
         <v>45321</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10280,7 +10280,7 @@
         <v>46125</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10391,7 +10391,7 @@
         <v>46167</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>46198</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10613,7 +10613,7 @@
         <v>45971</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10728,7 +10728,7 @@
         <v>46168</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10843,7 +10843,7 @@
         <v>46260</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>46260</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11063,7 +11063,7 @@
         <v>46198</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45940</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>45978</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11400,7 +11400,7 @@
         <v>44693</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11515,7 +11515,7 @@
         <v>45708</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11625,7 +11625,7 @@
         <v>45687</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11736,7 +11736,7 @@
         <v>46010</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>44571</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11961,7 +11961,7 @@
         <v>44643</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44872</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12176,7 +12176,7 @@
         <v>44477</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12281,7 +12281,7 @@
         <v>45761</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12386,7 +12386,7 @@
         <v>45189</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12496,7 +12496,7 @@
         <v>45486</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12605,7 +12605,7 @@
         <v>46008</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>45791</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>44960</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12930,7 +12930,7 @@
         <v>44888</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45993</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>45923</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13264,7 +13264,7 @@
         <v>44929</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>45866</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13483,7 +13483,7 @@
         <v>45321</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>45131</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13693,7 +13693,7 @@
         <v>45093</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13803,7 +13803,7 @@
         <v>45992</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13908,7 +13908,7 @@
         <v>45089</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14013,7 +14013,7 @@
         <v>45825</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14123,7 +14123,7 @@
         <v>46150</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14237,7 +14237,7 @@
         <v>44560</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14347,7 +14347,7 @@
         <v>45761</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14456,7 +14456,7 @@
         <v>46163</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14565,7 +14565,7 @@
         <v>44706</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14670,7 +14670,7 @@
         <v>46164</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14784,7 +14784,7 @@
         <v>46009</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14893,7 +14893,7 @@
         <v>46175</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45975</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45596</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15222,7 +15222,7 @@
         <v>45644</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44929</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>45114</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>45463</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15651,7 +15651,7 @@
         <v>46219</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15761,7 +15761,7 @@
         <v>46265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15871,7 +15871,7 @@
         <v>44998</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>46269</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16086,7 +16086,7 @@
         <v>46276</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16196,7 +16196,7 @@
         <v>46247</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>44771</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>44869</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>44502</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>44503</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16607,7 +16607,7 @@
         <v>44550</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16685,7 +16685,7 @@
         <v>44730</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>44482</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
         <v>44771</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16909,7 +16909,7 @@
         <v>44730</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16987,7 +16987,7 @@
         <v>44851</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -17060,7 +17060,7 @@
         <v>44872</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>44720</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17211,7 +17211,7 @@
         <v>44560</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17289,7 +17289,7 @@
         <v>44658</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17362,7 +17362,7 @@
         <v>44827</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>44590</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>44616</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>44706</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17664,7 +17664,7 @@
         <v>44785</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>44482</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44508</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>44715</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17971,7 +17971,7 @@
         <v>44482</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -18044,7 +18044,7 @@
         <v>44893</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>44841</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45569</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18268,7 +18268,7 @@
         <v>45594</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18346,7 +18346,7 @@
         <v>45212</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45611</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>44711</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18575,7 +18575,7 @@
         <v>45317</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18648,7 +18648,7 @@
         <v>45219</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45572</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18804,7 +18804,7 @@
         <v>45622</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18882,7 +18882,7 @@
         <v>45581</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18960,7 +18960,7 @@
         <v>45560</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -19038,7 +19038,7 @@
         <v>45789</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19116,7 +19116,7 @@
         <v>45789</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>45789</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19272,7 +19272,7 @@
         <v>45581</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19350,7 +19350,7 @@
         <v>45581</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19428,7 +19428,7 @@
         <v>45600</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45569</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19579,7 +19579,7 @@
         <v>46001</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19657,7 +19657,7 @@
         <v>45687</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19730,7 +19730,7 @@
         <v>45460</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19803,7 +19803,7 @@
         <v>45789</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45541</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45799</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44844</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20115,7 +20115,7 @@
         <v>46007</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20193,7 +20193,7 @@
         <v>45791</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20271,7 +20271,7 @@
         <v>45791</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20349,7 +20349,7 @@
         <v>45512</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20427,7 +20427,7 @@
         <v>45645</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>44852</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>46007</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20656,7 +20656,7 @@
         <v>46008</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>46008</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20812,7 +20812,7 @@
         <v>46009</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20890,7 +20890,7 @@
         <v>46009</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20963,7 +20963,7 @@
         <v>45607</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -21041,7 +21041,7 @@
         <v>46008</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>46008</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>44960</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21275,7 +21275,7 @@
         <v>46008</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21353,7 +21353,7 @@
         <v>46008</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>46008</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>46008</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>46010</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>45524</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45533</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>46010</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45519</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45813</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -22050,7 +22050,7 @@
         <v>45891</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45895</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22201,7 +22201,7 @@
         <v>46029</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>44730</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22357,7 +22357,7 @@
         <v>45450</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>45105</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22503,7 +22503,7 @@
         <v>45586</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22576,7 +22576,7 @@
         <v>44895</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22654,7 +22654,7 @@
         <v>44978</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22727,7 +22727,7 @@
         <v>45898</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>44859</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22883,7 +22883,7 @@
         <v>45898</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>45371</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -23034,7 +23034,7 @@
         <v>45903</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -23112,7 +23112,7 @@
         <v>45902</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45903</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23268,7 +23268,7 @@
         <v>45903</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45868</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23419,7 +23419,7 @@
         <v>45106</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23492,7 +23492,7 @@
         <v>45786</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23565,7 +23565,7 @@
         <v>46002</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23643,7 +23643,7 @@
         <v>45754</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>45161</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45909</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45911</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23950,7 +23950,7 @@
         <v>45911</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>45910</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>44915</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45910</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24257,7 +24257,7 @@
         <v>45770</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45791</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24408,7 +24408,7 @@
         <v>45910</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24481,7 +24481,7 @@
         <v>45453</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45541</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24637,7 +24637,7 @@
         <v>45911</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24715,7 +24715,7 @@
         <v>45776</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>45796</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24866,7 +24866,7 @@
         <v>45622</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24944,7 +24944,7 @@
         <v>45646</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -25017,7 +25017,7 @@
         <v>45961</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45791</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25173,7 +25173,7 @@
         <v>45791</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25251,7 +25251,7 @@
         <v>45917</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25324,7 +25324,7 @@
         <v>45499</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>45799</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45915</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25548,7 +25548,7 @@
         <v>45961</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>45800</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25704,7 +25704,7 @@
         <v>45800</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25782,7 +25782,7 @@
         <v>45902</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>45805</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45625</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -26011,7 +26011,7 @@
         <v>45208</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -26089,7 +26089,7 @@
         <v>45912</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45924</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26245,7 +26245,7 @@
         <v>45924</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>45925</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45208</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>45924</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26552,7 +26552,7 @@
         <v>45924</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45924</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44859</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26786,7 +26786,7 @@
         <v>45579</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>45926</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26937,7 +26937,7 @@
         <v>45926</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -27093,7 +27093,7 @@
         <v>45810</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27171,7 +27171,7 @@
         <v>45975</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>45224</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27322,7 +27322,7 @@
         <v>45831</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>46007</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45603</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45940</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45940</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>45940</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>44890</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27863,7 +27863,7 @@
         <v>45810</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27941,7 +27941,7 @@
         <v>45944</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -28014,7 +28014,7 @@
         <v>45810</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -28092,7 +28092,7 @@
         <v>45191</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28170,7 +28170,7 @@
         <v>45569</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>45623</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45952</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45744</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28477,7 +28477,7 @@
         <v>45954</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28555,7 +28555,7 @@
         <v>45813</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>45954</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45957</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28789,7 +28789,7 @@
         <v>45954</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28862,7 +28862,7 @@
         <v>45954</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>45954</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -29013,7 +29013,7 @@
         <v>45954</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -29091,7 +29091,7 @@
         <v>45954</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29169,7 +29169,7 @@
         <v>45954</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29242,7 +29242,7 @@
         <v>45813</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29320,7 +29320,7 @@
         <v>45957</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29398,7 +29398,7 @@
         <v>45813</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29476,7 +29476,7 @@
         <v>45954</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29549,7 +29549,7 @@
         <v>44515</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29627,7 +29627,7 @@
         <v>45813</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29705,7 +29705,7 @@
         <v>44893</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29778,7 +29778,7 @@
         <v>44994</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29851,7 +29851,7 @@
         <v>45502</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29924,7 +29924,7 @@
         <v>45924</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -30002,7 +30002,7 @@
         <v>45965</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -30075,7 +30075,7 @@
         <v>45965</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30153,7 +30153,7 @@
         <v>45891</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30231,7 +30231,7 @@
         <v>45963</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30309,7 +30309,7 @@
         <v>45891</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30387,7 +30387,7 @@
         <v>45966</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>45904</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>45971</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30616,7 +30616,7 @@
         <v>45971</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30694,7 +30694,7 @@
         <v>45968</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>45971</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>45971</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>45973</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -31006,7 +31006,7 @@
         <v>45973</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -31084,7 +31084,7 @@
         <v>45973</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31162,7 +31162,7 @@
         <v>45973</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31240,7 +31240,7 @@
         <v>45972</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31318,7 +31318,7 @@
         <v>45253</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31396,7 +31396,7 @@
         <v>45974</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45208</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31547,7 +31547,7 @@
         <v>45975</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31625,7 +31625,7 @@
         <v>45974</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31703,7 +31703,7 @@
         <v>45974</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31781,7 +31781,7 @@
         <v>45512</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31859,7 +31859,7 @@
         <v>45974</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>45974</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>45246</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -32088,7 +32088,7 @@
         <v>45981</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32166,7 +32166,7 @@
         <v>45562</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32244,7 +32244,7 @@
         <v>45594</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32322,7 +32322,7 @@
         <v>44916</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32400,7 +32400,7 @@
         <v>46114</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32478,7 +32478,7 @@
         <v>45210</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32556,7 +32556,7 @@
         <v>45824</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32629,7 +32629,7 @@
         <v>45210</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32707,7 +32707,7 @@
         <v>45909</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32780,7 +32780,7 @@
         <v>45989</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32853,7 +32853,7 @@
         <v>45988</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32931,7 +32931,7 @@
         <v>45929</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -33009,7 +33009,7 @@
         <v>45929</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45202</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33165,7 +33165,7 @@
         <v>45887</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33243,7 +33243,7 @@
         <v>45891</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33321,7 +33321,7 @@
         <v>45988</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33399,7 +33399,7 @@
         <v>45989</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>46119</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33550,7 +33550,7 @@
         <v>45989</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45989</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>46122</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>46122</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33857,7 +33857,7 @@
         <v>46122</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33935,7 +33935,7 @@
         <v>46122</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -34013,7 +34013,7 @@
         <v>45827</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -34091,7 +34091,7 @@
         <v>45644</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45826</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34242,7 +34242,7 @@
         <v>46126</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34320,7 +34320,7 @@
         <v>46126</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>45995</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>45995</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45995</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>46126</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34705,7 +34705,7 @@
         <v>45637</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34778,7 +34778,7 @@
         <v>45826</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34856,7 +34856,7 @@
         <v>44859</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>46001</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -35012,7 +35012,7 @@
         <v>45831</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -35090,7 +35090,7 @@
         <v>45831</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>46128</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35241,7 +35241,7 @@
         <v>44687</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35314,7 +35314,7 @@
         <v>45832</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35392,7 +35392,7 @@
         <v>46134</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35470,7 +35470,7 @@
         <v>45562</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35543,7 +35543,7 @@
         <v>46135</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35621,7 +35621,7 @@
         <v>44789</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35694,7 +35694,7 @@
         <v>44893</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35767,7 +35767,7 @@
         <v>45960</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45835</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35923,7 +35923,7 @@
         <v>44552</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35996,7 +35996,7 @@
         <v>45988</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>46062</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>45474</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36225,7 +36225,7 @@
         <v>45835</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36303,7 +36303,7 @@
         <v>45189</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36376,7 +36376,7 @@
         <v>45629</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36454,7 +36454,7 @@
         <v>45840</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45840</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36605,7 +36605,7 @@
         <v>45968</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>44825</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>45845</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45531</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36917,7 +36917,7 @@
         <v>45849</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36995,7 +36995,7 @@
         <v>45502</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -37073,7 +37073,7 @@
         <v>45954</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37146,7 +37146,7 @@
         <v>45825</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37219,7 +37219,7 @@
         <v>45301</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37292,7 +37292,7 @@
         <v>45301</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37365,7 +37365,7 @@
         <v>45297</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37438,7 +37438,7 @@
         <v>45849</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37516,7 +37516,7 @@
         <v>45525</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37589,7 +37589,7 @@
         <v>45827</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45335</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>45639</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>45902</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>45512</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37969,7 +37969,7 @@
         <v>45196</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -38047,7 +38047,7 @@
         <v>45860</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45825</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38203,7 +38203,7 @@
         <v>45849</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>45971</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38359,7 +38359,7 @@
         <v>45219</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45562</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38515,7 +38515,7 @@
         <v>45588</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38588,7 +38588,7 @@
         <v>45379</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38666,7 +38666,7 @@
         <v>45845</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>46037</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45225</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38895,7 +38895,7 @@
         <v>45512</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45574</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -39051,7 +39051,7 @@
         <v>45099</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39129,7 +39129,7 @@
         <v>46062</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>46141</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39285,7 +39285,7 @@
         <v>45113</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39363,7 +39363,7 @@
         <v>45832</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>45832</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39519,7 +39519,7 @@
         <v>45832</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39597,7 +39597,7 @@
         <v>45840</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39675,7 +39675,7 @@
         <v>46141</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45488</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39826,7 +39826,7 @@
         <v>44970</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39904,7 +39904,7 @@
         <v>44970</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>44680</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45581</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>45551</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40211,7 +40211,7 @@
         <v>46141</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>45869</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40367,7 +40367,7 @@
         <v>45567</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44853</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40523,7 +40523,7 @@
         <v>46066</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40601,7 +40601,7 @@
         <v>45279</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40674,7 +40674,7 @@
         <v>45099</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>46142</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>46142</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>45337</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45568</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>46147</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>44825</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41205,7 +41205,7 @@
         <v>46148</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41283,7 +41283,7 @@
         <v>45883</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41356,7 +41356,7 @@
         <v>46148</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41434,7 +41434,7 @@
         <v>46150</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41512,7 +41512,7 @@
         <v>45761</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41585,7 +41585,7 @@
         <v>45043</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41663,7 +41663,7 @@
         <v>46150</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41741,7 +41741,7 @@
         <v>45399</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41819,7 +41819,7 @@
         <v>45644</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41897,7 +41897,7 @@
         <v>46155</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>46155</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -42053,7 +42053,7 @@
         <v>45973</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>46155</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42204,7 +42204,7 @@
         <v>45288</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42277,7 +42277,7 @@
         <v>46155</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42355,7 +42355,7 @@
         <v>46142</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45679</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42506,7 +42506,7 @@
         <v>46113</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42579,7 +42579,7 @@
         <v>46155</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42657,7 +42657,7 @@
         <v>45743</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42730,7 +42730,7 @@
         <v>46160</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42808,7 +42808,7 @@
         <v>46161</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42886,7 +42886,7 @@
         <v>44903</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42959,7 +42959,7 @@
         <v>45579</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -43032,7 +43032,7 @@
         <v>45579</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43105,7 +43105,7 @@
         <v>46160</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43183,7 +43183,7 @@
         <v>45875</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43256,7 +43256,7 @@
         <v>46167</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43334,7 +43334,7 @@
         <v>45791</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43412,7 +43412,7 @@
         <v>45705</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43485,7 +43485,7 @@
         <v>45112</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43563,7 +43563,7 @@
         <v>45198</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43641,7 +43641,7 @@
         <v>45265</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43714,7 +43714,7 @@
         <v>44865</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43792,7 +43792,7 @@
         <v>46038</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43865,7 +43865,7 @@
         <v>45833</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>45834</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -44011,7 +44011,7 @@
         <v>46171</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44084,7 +44084,7 @@
         <v>46171</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44162,7 +44162,7 @@
         <v>46171</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44240,7 +44240,7 @@
         <v>46171</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44318,7 +44318,7 @@
         <v>46163</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44396,7 +44396,7 @@
         <v>46171</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44474,7 +44474,7 @@
         <v>46176</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>46171</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44630,7 +44630,7 @@
         <v>46175</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>46171</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44781,7 +44781,7 @@
         <v>46171</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>46167</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44937,7 +44937,7 @@
         <v>45537</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -45015,7 +45015,7 @@
         <v>45481</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45088,7 +45088,7 @@
         <v>45411</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45166,7 +45166,7 @@
         <v>46142</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45244,7 +45244,7 @@
         <v>45938</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45322,7 +45322,7 @@
         <v>44771</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>46163</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45468,7 +45468,7 @@
         <v>45624</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>45103</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45775</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45692,7 +45692,7 @@
         <v>45166</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45770,7 +45770,7 @@
         <v>46183</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45848,7 +45848,7 @@
         <v>46185</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>46185</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -46004,7 +46004,7 @@
         <v>45520</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46077,7 +46077,7 @@
         <v>46190</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46155,7 +46155,7 @@
         <v>45596</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>44883</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46311,7 +46311,7 @@
         <v>46183</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>46191</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46462,7 +46462,7 @@
         <v>45062</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46540,7 +46540,7 @@
         <v>45168</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>46184</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>46190</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46774,7 +46774,7 @@
         <v>46190</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>46190</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46930,7 +46930,7 @@
         <v>45616</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>45765</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45594</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47159,7 +47159,7 @@
         <v>45740</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47232,7 +47232,7 @@
         <v>46030</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>46160</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47383,7 +47383,7 @@
         <v>46160</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47461,7 +47461,7 @@
         <v>46198</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47539,7 +47539,7 @@
         <v>46160</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47617,7 +47617,7 @@
         <v>46160</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>46146</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>46146</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47851,7 +47851,7 @@
         <v>44476</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47929,7 +47929,7 @@
         <v>44533</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -48007,7 +48007,7 @@
         <v>45569</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48085,7 +48085,7 @@
         <v>45761</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>45110</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>46155</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48314,7 +48314,7 @@
         <v>46171</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48392,7 +48392,7 @@
         <v>46204</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48470,7 +48470,7 @@
         <v>45166</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48548,7 +48548,7 @@
         <v>46205</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48626,7 +48626,7 @@
         <v>46206</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>46206</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48782,7 +48782,7 @@
         <v>46190</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48860,7 +48860,7 @@
         <v>45119</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48938,7 +48938,7 @@
         <v>45526</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>44730</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49089,7 +49089,7 @@
         <v>46167</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49167,7 +49167,7 @@
         <v>46195</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49245,7 +49245,7 @@
         <v>46142</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49323,7 +49323,7 @@
         <v>45373</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49396,7 +49396,7 @@
         <v>45243</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>46142</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45512</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49625,7 +49625,7 @@
         <v>46154</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49703,7 +49703,7 @@
         <v>45685</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>46258</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49854,7 +49854,7 @@
         <v>46258</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>46260</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>46195</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50083,7 +50083,7 @@
         <v>46195</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>46195</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50239,7 +50239,7 @@
         <v>46195</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50317,7 +50317,7 @@
         <v>46195</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50395,7 +50395,7 @@
         <v>46198</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50473,7 +50473,7 @@
         <v>44915</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50551,7 +50551,7 @@
         <v>46195</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50629,7 +50629,7 @@
         <v>45485</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50707,7 +50707,7 @@
         <v>46195</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50785,7 +50785,7 @@
         <v>46195</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50863,7 +50863,7 @@
         <v>46195</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>46198</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45644</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>46195</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51170,7 +51170,7 @@
         <v>46218</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51248,7 +51248,7 @@
         <v>46217</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51326,7 +51326,7 @@
         <v>46198</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51404,7 +51404,7 @@
         <v>46260</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51477,7 +51477,7 @@
         <v>46260</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51550,7 +51550,7 @@
         <v>45603</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51628,7 +51628,7 @@
         <v>46219</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51706,7 +51706,7 @@
         <v>46265</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51784,7 +51784,7 @@
         <v>45621</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51862,7 +51862,7 @@
         <v>44942</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51935,7 +51935,7 @@
         <v>46262</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -52013,7 +52013,7 @@
         <v>46265</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>46220</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52169,7 +52169,7 @@
         <v>46267</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52242,7 +52242,7 @@
         <v>46225</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52320,7 +52320,7 @@
         <v>46273</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52398,7 +52398,7 @@
         <v>46272</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52471,7 +52471,7 @@
         <v>46273</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52549,7 +52549,7 @@
         <v>46273</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52622,7 +52622,7 @@
         <v>46273</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52700,7 +52700,7 @@
         <v>46230</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52778,7 +52778,7 @@
         <v>46230</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52856,7 +52856,7 @@
         <v>46206</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52934,7 +52934,7 @@
         <v>45754</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -53012,7 +53012,7 @@
         <v>46275</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53085,7 +53085,7 @@
         <v>46279</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53163,7 +53163,7 @@
         <v>46233</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53241,7 +53241,7 @@
         <v>46279</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53319,7 +53319,7 @@
         <v>46276</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53392,7 +53392,7 @@
         <v>46279</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53470,7 +53470,7 @@
         <v>46267</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53548,7 +53548,7 @@
         <v>44599</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53621,7 +53621,7 @@
         <v>46267</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53699,7 +53699,7 @@
         <v>46280</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53777,7 +53777,7 @@
         <v>46281</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53855,7 +53855,7 @@
         <v>46280</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53933,7 +53933,7 @@
         <v>45244</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -54006,7 +54006,7 @@
         <v>44970</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54084,7 +54084,7 @@
         <v>45198</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54162,7 +54162,7 @@
         <v>46283</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54240,7 +54240,7 @@
         <v>46283</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54318,7 +54318,7 @@
         <v>44879</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54391,7 +54391,7 @@
         <v>46283</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54469,7 +54469,7 @@
         <v>46283</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54547,7 +54547,7 @@
         <v>46282</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54625,7 +54625,7 @@
         <v>46241</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54698,7 +54698,7 @@
         <v>45631</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54776,7 +54776,7 @@
         <v>46287</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54854,7 +54854,7 @@
         <v>44819</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54932,7 +54932,7 @@
         <v>46287</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -55010,7 +55010,7 @@
         <v>46241</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55088,7 +55088,7 @@
         <v>46241</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55166,7 +55166,7 @@
         <v>46241</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55244,7 +55244,7 @@
         <v>46241</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55322,7 +55322,7 @@
         <v>45062</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55400,7 +55400,7 @@
         <v>45404</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55473,7 +55473,7 @@
         <v>46288</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55546,7 +55546,7 @@
         <v>44826</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>46286</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55702,7 +55702,7 @@
         <v>46290</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55780,7 +55780,7 @@
         <v>45593</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55858,7 +55858,7 @@
         <v>46290</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55936,7 +55936,7 @@
         <v>45156</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -56009,7 +56009,7 @@
         <v>46290</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -56087,7 +56087,7 @@
         <v>46247</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56165,7 +56165,7 @@
         <v>46286</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56243,7 +56243,7 @@
         <v>46248</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56316,7 +56316,7 @@
         <v>46247</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56389,7 +56389,7 @@
         <v>46290</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56467,7 +56467,7 @@
         <v>46290</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56545,7 +56545,7 @@
         <v>45372</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56618,7 +56618,7 @@
         <v>46290</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56696,7 +56696,7 @@
         <v>46247</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56774,7 +56774,7 @@
         <v>46294</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>44820</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56930,7 +56930,7 @@
         <v>44820</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -57008,7 +57008,7 @@
         <v>44708</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -57086,7 +57086,7 @@
         <v>46294</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57164,7 +57164,7 @@
         <v>46294</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57242,7 +57242,7 @@
         <v>45218</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57315,7 +57315,7 @@
         <v>46294</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57393,7 +57393,7 @@
         <v>46294</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57471,7 +57471,7 @@
         <v>46255</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57549,7 +57549,7 @@
         <v>46255</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57627,7 +57627,7 @@
         <v>46255</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57705,7 +57705,7 @@
         <v>45243</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57778,7 +57778,7 @@
         <v>45560</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57856,7 +57856,7 @@
         <v>45519</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57929,7 +57929,7 @@
         <v>46253</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -58007,7 +58007,7 @@
         <v>45071</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -58085,7 +58085,7 @@
         <v>46122</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58163,7 +58163,7 @@
         <v>46255</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58241,7 +58241,7 @@
         <v>45317</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58314,7 +58314,7 @@
         <v>45680</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58387,7 +58387,7 @@
         <v>46255</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>45205</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58543,7 +58543,7 @@
         <v>46255</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58621,7 +58621,7 @@
         <v>46255</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58699,7 +58699,7 @@
         <v>44581</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58777,7 +58777,7 @@
         <v>45603</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58855,7 +58855,7 @@
         <v>45554</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58928,7 +58928,7 @@
         <v>45253</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -59006,7 +59006,7 @@
         <v>45187</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -59084,7 +59084,7 @@
         <v>45110</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59157,7 +59157,7 @@
         <v>44729</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59235,7 +59235,7 @@
         <v>44960</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59313,7 +59313,7 @@
         <v>44967</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59386,7 +59386,7 @@
         <v>45258</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59459,7 +59459,7 @@
         <v>45541</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59537,7 +59537,7 @@
         <v>45622</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59615,7 +59615,7 @@
         <v>45497</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59688,7 +59688,7 @@
         <v>45056</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59766,7 +59766,7 @@
         <v>45638</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59839,7 +59839,7 @@
         <v>45602</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59912,7 +59912,7 @@
         <v>45176</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59985,7 +59985,7 @@
         <v>45622</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -60063,7 +60063,7 @@
         <v>45622</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60141,7 +60141,7 @@
         <v>45622</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60219,7 +60219,7 @@
         <v>45687</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60292,7 +60292,7 @@
         <v>45762</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60365,7 +60365,7 @@
         <v>45602</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60438,7 +60438,7 @@
         <v>45545</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60511,7 +60511,7 @@
         <v>45784</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60584,7 +60584,7 @@
         <v>45565</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60657,7 +60657,7 @@
         <v>45230</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60735,7 +60735,7 @@
         <v>45609</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60813,7 +60813,7 @@
         <v>45784</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60886,7 +60886,7 @@
         <v>45134</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60964,7 +60964,7 @@
         <v>45167</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -61042,7 +61042,7 @@
         <v>45015</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61120,7 +61120,7 @@
         <v>45216</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61198,7 +61198,7 @@
         <v>45400</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61276,7 +61276,7 @@
         <v>45391</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61354,7 +61354,7 @@
         <v>44805</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61432,7 +61432,7 @@
         <v>45015</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -61510,7 +61510,7 @@
         <v>46190</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -601,7 +601,7 @@
         <v>45275</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45791</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -858,7 +858,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45940</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>45961</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1373,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         <v>44631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1620,7 +1620,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1862,7 +1862,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>46275</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2224,7 +2224,7 @@
         <v>45981</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2351,7 @@
         <v>45849</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2464,7 @@
         <v>46163</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2586,7 +2586,7 @@
         <v>46058</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2707,7 +2707,7 @@
         <v>45786</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2936,7 +2936,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>45597</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3174,7 +3174,7 @@
         <v>45786</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3290,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3415,7 +3415,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3535,7 +3535,7 @@
         <v>46279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3651,7 +3651,7 @@
         <v>46170</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45957</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45842</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         <v>45971</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4128,7 +4128,7 @@
         <v>46010</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>45785</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4361,7 +4361,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>45993</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>46163</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4708,7 +4708,7 @@
         <v>45940</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4827,7 +4827,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4941,7 +4941,7 @@
         <v>45930</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5059,7 +5059,7 @@
         <v>46010</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5177,7 +5177,7 @@
         <v>45541</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5291,7 +5291,7 @@
         <v>46163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>46163</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>46163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>46216</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>45926</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5987,7 +5987,7 @@
         <v>45985</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6104,7 +6104,7 @@
         <v>45246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>45607</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>45596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>46198</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6563,7 +6563,7 @@
         <v>46283</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6676,7 +6676,7 @@
         <v>46163</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6788,7 +6788,7 @@
         <v>46155</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>45373</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7017,7 +7017,7 @@
         <v>46260</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7129,7 +7129,7 @@
         <v>46260</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7245,7 +7245,7 @@
         <v>46265</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>45901</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7707,7 +7707,7 @@
         <v>44560</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7823,7 +7823,7 @@
         <v>45791</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7935,7 +7935,7 @@
         <v>45105</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8051,7 +8051,7 @@
         <v>46168</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8167,7 +8167,7 @@
         <v>46128</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8283,7 +8283,7 @@
         <v>45910</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>46170</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>44872</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8621,7 +8621,7 @@
         <v>45063</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8732,7 +8732,7 @@
         <v>44994</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45916</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>45518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>45923</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9174,7 +9174,7 @@
         <v>44831</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>45594</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>45940</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>45943</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45321</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>45978</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>44923</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>46150</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>46125</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
         <v>46167</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>45971</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>46198</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10626,7 +10626,7 @@
         <v>46168</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>46198</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10852,7 +10852,7 @@
         <v>45940</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>45978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11078,7 +11078,7 @@
         <v>45708</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11188,7 +11188,7 @@
         <v>46260</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11298,7 +11298,7 @@
         <v>46260</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11408,7 +11408,7 @@
         <v>44693</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>45687</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>46010</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11749,7 +11749,7 @@
         <v>44571</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11859,7 +11859,7 @@
         <v>44643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11964,7 +11964,7 @@
         <v>44872</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12074,7 +12074,7 @@
         <v>45761</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12183,7 +12183,7 @@
         <v>45089</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12288,7 +12288,7 @@
         <v>44998</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>45463</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45131</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>45321</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>44929</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>45486</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12932,7 +12932,7 @@
         <v>45923</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13042,7 +13042,7 @@
         <v>45791</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13152,7 +13152,7 @@
         <v>44888</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13262,7 +13262,7 @@
         <v>45093</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13372,7 +13372,7 @@
         <v>44929</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>45114</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13582,7 +13582,7 @@
         <v>44706</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44960</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13792,7 +13792,7 @@
         <v>45866</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45825</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14011,7 +14011,7 @@
         <v>45189</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14121,7 +14121,7 @@
         <v>44560</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>45761</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14336,7 +14336,7 @@
         <v>45992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>46008</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14551,7 +14551,7 @@
         <v>45993</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14665,7 +14665,7 @@
         <v>46163</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46164</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>46009</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>46175</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15102,7 +15102,7 @@
         <v>45975</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>45596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15326,7 +15326,7 @@
         <v>45644</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15435,7 +15435,7 @@
         <v>46219</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15545,7 +15545,7 @@
         <v>46276</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15655,7 +15655,7 @@
         <v>46247</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15769,7 +15769,7 @@
         <v>46265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15879,7 +15879,7 @@
         <v>46269</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>44771</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16062,7 +16062,7 @@
         <v>44869</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16135,7 +16135,7 @@
         <v>44502</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>44503</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>44550</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44560</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16442,7 +16442,7 @@
         <v>44658</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16515,7 +16515,7 @@
         <v>44827</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16593,7 +16593,7 @@
         <v>44730</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>44590</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16744,7 +16744,7 @@
         <v>44851</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16817,7 +16817,7 @@
         <v>44482</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>44616</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16963,7 +16963,7 @@
         <v>44706</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>44771</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>44482</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>44508</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>44785</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17343,7 +17343,7 @@
         <v>44872</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44730</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>44715</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17577,7 +17577,7 @@
         <v>44720</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17650,7 +17650,7 @@
         <v>45056</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         <v>45372</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         <v>45166</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17879,7 +17879,7 @@
         <v>45411</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17957,7 +17957,7 @@
         <v>44819</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44942</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45110</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45603</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>44730</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>45551</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45705</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45637</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>44967</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45219</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18707,7 +18707,7 @@
         <v>45554</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18780,7 +18780,7 @@
         <v>45335</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
         <v>45099</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45520</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>45265</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>44825</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45202</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>45481</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>45208</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19384,7 +19384,7 @@
         <v>45297</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>45218</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45450</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45071</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19681,7 +19681,7 @@
         <v>45644</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19754,7 +19754,7 @@
         <v>44826</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19832,7 +19832,7 @@
         <v>44853</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>45105</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45119</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20061,7 +20061,7 @@
         <v>45611</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20139,7 +20139,7 @@
         <v>45526</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20212,7 +20212,7 @@
         <v>45512</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44825</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44859</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>45602</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>45288</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45103</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>44865</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45680</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>44883</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>44852</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45399</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45541</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>45813</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45799</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45579</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45579</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>45537</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>44482</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45607</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21649,7 +21649,7 @@
         <v>45569</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45621</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45502</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45891</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>45317</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45895</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45898</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45898</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45474</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>44844</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45379</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44895</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45512</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45512</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>44978</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45212</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45902</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>44994</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45646</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>45317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44515</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45903</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45903</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23398,7 +23398,7 @@
         <v>45903</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23476,7 +23476,7 @@
         <v>45562</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45258</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23627,7 +23627,7 @@
         <v>45868</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23700,7 +23700,7 @@
         <v>45404</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23773,7 +23773,7 @@
         <v>45485</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45909</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23924,7 +23924,7 @@
         <v>45743</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23997,7 +23997,7 @@
         <v>45110</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24070,7 +24070,7 @@
         <v>45910</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24148,7 +24148,7 @@
         <v>45910</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24221,7 +24221,7 @@
         <v>45911</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45519</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24372,7 +24372,7 @@
         <v>45911</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24450,7 +24450,7 @@
         <v>45911</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>44533</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24606,7 +24606,7 @@
         <v>45910</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24679,7 +24679,7 @@
         <v>45915</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24752,7 +24752,7 @@
         <v>45784</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24825,7 +24825,7 @@
         <v>45784</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24898,7 +24898,7 @@
         <v>45545</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>44893</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>44893</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45565</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>45460</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25263,7 +25263,7 @@
         <v>45230</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>45917</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25414,7 +25414,7 @@
         <v>45572</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25492,7 +25492,7 @@
         <v>45581</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25570,7 +25570,7 @@
         <v>45488</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25643,7 +25643,7 @@
         <v>45609</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25721,7 +25721,7 @@
         <v>45581</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25799,7 +25799,7 @@
         <v>45603</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25877,7 +25877,7 @@
         <v>45134</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25955,7 +25955,7 @@
         <v>45789</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45789</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>45600</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26184,7 +26184,7 @@
         <v>45533</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26262,7 +26262,7 @@
         <v>45569</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26340,7 +26340,7 @@
         <v>45912</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26418,7 +26418,7 @@
         <v>45924</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26496,7 +26496,7 @@
         <v>45789</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26574,7 +26574,7 @@
         <v>45113</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26652,7 +26652,7 @@
         <v>45924</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26730,7 +26730,7 @@
         <v>45924</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45924</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26886,7 +26886,7 @@
         <v>45602</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45789</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27037,7 +27037,7 @@
         <v>45902</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45586</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45581</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27266,7 +27266,7 @@
         <v>45924</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27344,7 +27344,7 @@
         <v>45925</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27417,7 +27417,7 @@
         <v>45112</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27495,7 +27495,7 @@
         <v>45926</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27573,7 +27573,7 @@
         <v>45560</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27651,7 +27651,7 @@
         <v>45926</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45791</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45786</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27880,7 +27880,7 @@
         <v>45644</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27953,7 +27953,7 @@
         <v>44893</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28026,7 +28026,7 @@
         <v>45926</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45524</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28182,7 +28182,7 @@
         <v>45560</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28260,7 +28260,7 @@
         <v>45639</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45453</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28416,7 +28416,7 @@
         <v>45541</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45569</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28572,7 +28572,7 @@
         <v>45062</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45796</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28728,7 +28728,7 @@
         <v>45541</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28806,7 +28806,7 @@
         <v>45622</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28884,7 +28884,7 @@
         <v>44915</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>45499</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45189</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45791</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29186,7 +29186,7 @@
         <v>45191</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29264,7 +29264,7 @@
         <v>45776</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45622</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45791</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29493,7 +29493,7 @@
         <v>45791</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29571,7 +29571,7 @@
         <v>45594</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29649,7 +29649,7 @@
         <v>45622</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29727,7 +29727,7 @@
         <v>45622</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29805,7 +29805,7 @@
         <v>45770</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29878,7 +29878,7 @@
         <v>45198</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29956,7 +29956,7 @@
         <v>45800</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30034,7 +30034,7 @@
         <v>45799</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>45800</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30190,7 +30190,7 @@
         <v>45579</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30263,7 +30263,7 @@
         <v>45512</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30341,7 +30341,7 @@
         <v>45805</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30419,7 +30419,7 @@
         <v>45622</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30497,7 +30497,7 @@
         <v>45622</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30575,7 +30575,7 @@
         <v>45099</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30653,7 +30653,7 @@
         <v>45810</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>45810</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45810</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30887,7 +30887,7 @@
         <v>45740</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30960,7 +30960,7 @@
         <v>45187</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31038,7 +31038,7 @@
         <v>45687</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31111,7 +31111,7 @@
         <v>45168</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31189,7 +31189,7 @@
         <v>45940</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31267,7 +31267,7 @@
         <v>45940</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31345,7 +31345,7 @@
         <v>45940</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31423,7 +31423,7 @@
         <v>45208</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31501,7 +31501,7 @@
         <v>45569</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31579,7 +31579,7 @@
         <v>44789</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31652,7 +31652,7 @@
         <v>45944</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31725,7 +31725,7 @@
         <v>45623</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31803,7 +31803,7 @@
         <v>45813</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31881,7 +31881,7 @@
         <v>45813</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31959,7 +31959,7 @@
         <v>45813</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32037,7 +32037,7 @@
         <v>45166</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45813</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32193,7 +32193,7 @@
         <v>44970</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32271,7 +32271,7 @@
         <v>44708</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32349,7 +32349,7 @@
         <v>44687</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32422,7 +32422,7 @@
         <v>45210</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>44711</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32578,7 +32578,7 @@
         <v>44841</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44960</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32729,7 +32729,7 @@
         <v>45754</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45624</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45603</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32958,7 +32958,7 @@
         <v>45645</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33036,7 +33036,7 @@
         <v>45824</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45629</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33187,7 +33187,7 @@
         <v>45826</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33265,7 +33265,7 @@
         <v>45244</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33338,7 +33338,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33411,7 +33411,7 @@
         <v>45826</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33489,7 +33489,7 @@
         <v>45625</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45827</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33640,7 +33640,7 @@
         <v>45301</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33713,7 +33713,7 @@
         <v>45156</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33786,7 +33786,7 @@
         <v>45519</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>45593</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33937,7 +33937,7 @@
         <v>45832</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34015,7 +34015,7 @@
         <v>45831</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34093,7 +34093,7 @@
         <v>45831</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34171,7 +34171,7 @@
         <v>45954</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34244,7 +34244,7 @@
         <v>45954</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45954</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>45954</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45954</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45954</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45954</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34707,7 +34707,7 @@
         <v>45954</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34780,7 +34780,7 @@
         <v>45957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34858,7 +34858,7 @@
         <v>45954</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34931,7 +34931,7 @@
         <v>45957</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35009,7 +35009,7 @@
         <v>45891</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35087,7 +35087,7 @@
         <v>45219</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35165,7 +35165,7 @@
         <v>45253</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>45253</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45891</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35399,7 +35399,7 @@
         <v>45062</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35477,7 +35477,7 @@
         <v>45835</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>45963</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>45924</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>45840</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>45904</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35862,7 +35862,7 @@
         <v>45966</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35940,7 +35940,7 @@
         <v>45840</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>45198</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36091,7 +36091,7 @@
         <v>45965</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45965</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>45210</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36320,7 +36320,7 @@
         <v>45208</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45968</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>45638</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45644</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>45972</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>45568</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36773,7 +36773,7 @@
         <v>45845</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36851,7 +36851,7 @@
         <v>45971</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>45971</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37007,7 +37007,7 @@
         <v>45971</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37085,7 +37085,7 @@
         <v>45971</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>45502</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37241,7 +37241,7 @@
         <v>45974</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37397,7 +37397,7 @@
         <v>45973</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>45974</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45973</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>45246</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37704,7 +37704,7 @@
         <v>45754</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37782,7 +37782,7 @@
         <v>45973</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37860,7 +37860,7 @@
         <v>45744</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45973</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>45974</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45849</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>45974</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>45525</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45975</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>44729</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>45825</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45512</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45832</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38713,7 +38713,7 @@
         <v>45832</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38791,7 +38791,7 @@
         <v>45840</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38869,7 +38869,7 @@
         <v>45832</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45567</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>44680</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>44581</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39181,7 +39181,7 @@
         <v>44771</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45869</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>44820</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39410,7 +39410,7 @@
         <v>44820</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39488,7 +39488,7 @@
         <v>45337</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39561,7 +39561,7 @@
         <v>44915</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>44859</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39717,7 +39717,7 @@
         <v>45687</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39790,7 +39790,7 @@
         <v>45761</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>45762</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39936,7 +39936,7 @@
         <v>45875</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45981</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40087,7 +40087,7 @@
         <v>45765</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40160,7 +40160,7 @@
         <v>45243</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>45616</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45279</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40384,7 +40384,7 @@
         <v>45301</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>44916</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40535,7 +40535,7 @@
         <v>45775</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40613,7 +40613,7 @@
         <v>44879</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40686,7 +40686,7 @@
         <v>45887</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40764,7 +40764,7 @@
         <v>45891</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40842,7 +40842,7 @@
         <v>45929</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>45929</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>45497</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41071,7 +41071,7 @@
         <v>45988</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41149,7 +41149,7 @@
         <v>45106</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41222,7 +41222,7 @@
         <v>45988</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41300,7 +41300,7 @@
         <v>45909</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41373,7 +41373,7 @@
         <v>45989</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41446,7 +41446,7 @@
         <v>45989</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41519,7 +41519,7 @@
         <v>45989</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41597,7 +41597,7 @@
         <v>45989</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41670,7 +41670,7 @@
         <v>46114</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41748,7 +41748,7 @@
         <v>44970</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41826,7 +41826,7 @@
         <v>46119</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41904,7 +41904,7 @@
         <v>44552</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41977,7 +41977,7 @@
         <v>46122</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42055,7 +42055,7 @@
         <v>46122</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>46122</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45995</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45995</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42362,7 +42362,7 @@
         <v>45995</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42440,7 +42440,7 @@
         <v>46122</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42518,7 +42518,7 @@
         <v>46126</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42596,7 +42596,7 @@
         <v>46126</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42674,7 +42674,7 @@
         <v>46126</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42752,7 +42752,7 @@
         <v>44730</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42830,7 +42830,7 @@
         <v>46001</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>46001</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42986,7 +42986,7 @@
         <v>44599</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43059,7 +43059,7 @@
         <v>46128</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43132,7 +43132,7 @@
         <v>46134</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43210,7 +43210,7 @@
         <v>44859</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43288,7 +43288,7 @@
         <v>44960</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43366,7 +43366,7 @@
         <v>46007</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>46008</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43522,7 +43522,7 @@
         <v>46007</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>46008</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43678,7 +43678,7 @@
         <v>46008</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43756,7 +43756,7 @@
         <v>46008</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>46008</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43912,7 +43912,7 @@
         <v>45196</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>46135</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>45849</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44146,7 +44146,7 @@
         <v>46008</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44224,7 +44224,7 @@
         <v>46008</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44302,7 +44302,7 @@
         <v>45205</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44380,7 +44380,7 @@
         <v>46008</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>45960</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44536,7 +44536,7 @@
         <v>46010</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>46010</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>46009</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44770,7 +44770,7 @@
         <v>46062</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44848,7 +44848,7 @@
         <v>46009</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44921,7 +44921,7 @@
         <v>45825</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44994,7 +44994,7 @@
         <v>45849</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45072,7 +45072,7 @@
         <v>45594</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45594</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45228,7 +45228,7 @@
         <v>45043</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45306,7 +45306,7 @@
         <v>45845</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45384,7 +45384,7 @@
         <v>46066</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45462,7 +45462,7 @@
         <v>44903</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45535,7 +45535,7 @@
         <v>45827</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45613,7 +45613,7 @@
         <v>45968</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45691,7 +45691,7 @@
         <v>46029</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45769,7 +45769,7 @@
         <v>44970</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45225</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45954</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45998,7 +45998,7 @@
         <v>45988</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46076,7 +46076,7 @@
         <v>45971</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46154,7 +46154,7 @@
         <v>45835</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46232,7 +46232,7 @@
         <v>46002</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46310,7 +46310,7 @@
         <v>45531</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46388,7 +46388,7 @@
         <v>45161</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46466,7 +46466,7 @@
         <v>45562</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46539,7 +46539,7 @@
         <v>44890</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>45562</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46695,7 +46695,7 @@
         <v>45860</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46773,7 +46773,7 @@
         <v>45902</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46846,7 +46846,7 @@
         <v>45961</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46924,7 +46924,7 @@
         <v>45574</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>45961</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>45371</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45243</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47226,7 +47226,7 @@
         <v>46037</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47299,7 +47299,7 @@
         <v>45373</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47372,7 +47372,7 @@
         <v>45588</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47445,7 +47445,7 @@
         <v>46141</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47523,7 +47523,7 @@
         <v>45631</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47601,7 +47601,7 @@
         <v>45176</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47674,7 +47674,7 @@
         <v>46141</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>45581</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>46141</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>46142</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47986,7 +47986,7 @@
         <v>46142</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48064,7 +48064,7 @@
         <v>46062</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48142,7 +48142,7 @@
         <v>46148</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48220,7 +48220,7 @@
         <v>45975</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48298,7 +48298,7 @@
         <v>45831</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48371,7 +48371,7 @@
         <v>46150</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48449,7 +48449,7 @@
         <v>45224</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48522,7 +48522,7 @@
         <v>46150</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>46007</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>46148</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45973</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48834,7 +48834,7 @@
         <v>45883</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
         <v>46142</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48985,7 +48985,7 @@
         <v>46155</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49058,7 +49058,7 @@
         <v>45679</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49131,7 +49131,7 @@
         <v>46155</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49209,7 +49209,7 @@
         <v>46155</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49287,7 +49287,7 @@
         <v>46155</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49365,7 +49365,7 @@
         <v>46155</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49443,7 +49443,7 @@
         <v>46113</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49516,7 +49516,7 @@
         <v>46160</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49594,7 +49594,7 @@
         <v>46160</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49672,7 +49672,7 @@
         <v>46161</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>45791</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49828,7 +49828,7 @@
         <v>46167</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49906,7 +49906,7 @@
         <v>45833</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45834</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50052,7 +50052,7 @@
         <v>46038</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50125,7 +50125,7 @@
         <v>46171</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>46171</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50281,7 +50281,7 @@
         <v>46171</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50354,7 +50354,7 @@
         <v>46175</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50427,7 +50427,7 @@
         <v>46171</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50505,7 +50505,7 @@
         <v>46171</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50583,7 +50583,7 @@
         <v>46171</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>46171</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50739,7 +50739,7 @@
         <v>46163</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50817,7 +50817,7 @@
         <v>46171</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50895,7 +50895,7 @@
         <v>46176</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50973,7 +50973,7 @@
         <v>46167</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51051,7 +51051,7 @@
         <v>45938</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51129,7 +51129,7 @@
         <v>46142</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51207,7 +51207,7 @@
         <v>46183</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51285,7 +51285,7 @@
         <v>46163</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51358,7 +51358,7 @@
         <v>46185</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51436,7 +51436,7 @@
         <v>46185</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51514,7 +51514,7 @@
         <v>45596</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51592,7 +51592,7 @@
         <v>46184</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51670,7 +51670,7 @@
         <v>46190</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51748,7 +51748,7 @@
         <v>46190</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51826,7 +51826,7 @@
         <v>46190</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>46183</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51982,7 +51982,7 @@
         <v>46190</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52060,7 +52060,7 @@
         <v>46191</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52133,7 +52133,7 @@
         <v>46030</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52206,7 +52206,7 @@
         <v>46160</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52284,7 +52284,7 @@
         <v>46146</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52362,7 +52362,7 @@
         <v>46146</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52440,7 +52440,7 @@
         <v>46160</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52518,7 +52518,7 @@
         <v>46160</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52596,7 +52596,7 @@
         <v>46160</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52674,7 +52674,7 @@
         <v>46198</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>46171</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>46155</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52908,7 +52908,7 @@
         <v>46190</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52986,7 +52986,7 @@
         <v>46205</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>46142</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53142,7 +53142,7 @@
         <v>46167</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53220,7 +53220,7 @@
         <v>46206</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53298,7 +53298,7 @@
         <v>46206</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53376,7 +53376,7 @@
         <v>46195</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53454,7 +53454,7 @@
         <v>46198</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53532,7 +53532,7 @@
         <v>46198</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53610,7 +53610,7 @@
         <v>46195</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53688,7 +53688,7 @@
         <v>46154</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53766,7 +53766,7 @@
         <v>46198</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53844,7 +53844,7 @@
         <v>46195</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53922,7 +53922,7 @@
         <v>46195</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54000,7 +54000,7 @@
         <v>46195</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54078,7 +54078,7 @@
         <v>46195</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54156,7 +54156,7 @@
         <v>46142</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54234,7 +54234,7 @@
         <v>46195</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54312,7 +54312,7 @@
         <v>46195</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54390,7 +54390,7 @@
         <v>46195</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54468,7 +54468,7 @@
         <v>45685</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54541,7 +54541,7 @@
         <v>46195</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54619,7 +54619,7 @@
         <v>46195</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54697,7 +54697,7 @@
         <v>46217</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54775,7 +54775,7 @@
         <v>46218</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54853,7 +54853,7 @@
         <v>46219</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54931,7 +54931,7 @@
         <v>46265</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55009,7 +55009,7 @@
         <v>46225</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55087,7 +55087,7 @@
         <v>46267</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55160,7 +55160,7 @@
         <v>46230</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55238,7 +55238,7 @@
         <v>46272</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55311,7 +55311,7 @@
         <v>46206</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55389,7 +55389,7 @@
         <v>46273</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55462,7 +55462,7 @@
         <v>46230</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>46273</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55618,7 +55618,7 @@
         <v>46273</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55696,7 +55696,7 @@
         <v>46273</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55774,7 +55774,7 @@
         <v>46267</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55852,7 +55852,7 @@
         <v>46267</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55930,7 +55930,7 @@
         <v>46275</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56003,7 +56003,7 @@
         <v>46276</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56076,7 +56076,7 @@
         <v>46280</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56154,7 +56154,7 @@
         <v>46279</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56232,7 +56232,7 @@
         <v>46279</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56310,7 +56310,7 @@
         <v>46233</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56388,7 +56388,7 @@
         <v>46280</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56466,7 +56466,7 @@
         <v>46279</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56544,7 +56544,7 @@
         <v>46281</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56622,7 +56622,7 @@
         <v>46282</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56700,7 +56700,7 @@
         <v>46241</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56778,7 +56778,7 @@
         <v>46241</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56856,7 +56856,7 @@
         <v>46241</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56929,7 +56929,7 @@
         <v>46283</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57007,7 +57007,7 @@
         <v>46283</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57085,7 +57085,7 @@
         <v>46241</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57163,7 +57163,7 @@
         <v>46241</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57241,7 +57241,7 @@
         <v>46283</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57319,7 +57319,7 @@
         <v>46283</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57397,7 +57397,7 @@
         <v>46287</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57475,7 +57475,7 @@
         <v>46287</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57553,7 +57553,7 @@
         <v>46288</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57626,7 +57626,7 @@
         <v>46247</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57704,7 +57704,7 @@
         <v>46290</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57782,7 +57782,7 @@
         <v>46247</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57855,7 +57855,7 @@
         <v>46286</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57933,7 +57933,7 @@
         <v>46290</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58011,7 +58011,7 @@
         <v>46290</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58089,7 +58089,7 @@
         <v>46290</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58167,7 +58167,7 @@
         <v>46286</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58245,7 +58245,7 @@
         <v>46290</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58323,7 +58323,7 @@
         <v>46290</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58401,7 +58401,7 @@
         <v>46294</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58479,7 +58479,7 @@
         <v>46248</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>46294</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58630,7 +58630,7 @@
         <v>46294</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58708,7 +58708,7 @@
         <v>46294</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58786,7 +58786,7 @@
         <v>46294</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58864,7 +58864,7 @@
         <v>46255</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58942,7 +58942,7 @@
         <v>46255</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59020,7 +59020,7 @@
         <v>46255</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59098,7 +59098,7 @@
         <v>46255</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59176,7 +59176,7 @@
         <v>46122</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59254,7 +59254,7 @@
         <v>46255</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59332,7 +59332,7 @@
         <v>46255</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59410,7 +59410,7 @@
         <v>46255</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59488,7 +59488,7 @@
         <v>46301</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59561,7 +59561,7 @@
         <v>46258</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59639,7 +59639,7 @@
         <v>46253</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59717,7 +59717,7 @@
         <v>46258</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59795,7 +59795,7 @@
         <v>46262</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59873,7 +59873,7 @@
         <v>46247</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>46147</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60029,7 +60029,7 @@
         <v>46204</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60107,7 +60107,7 @@
         <v>46260</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60180,7 +60180,7 @@
         <v>46260</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60253,7 +60253,7 @@
         <v>46265</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60331,7 +60331,7 @@
         <v>46260</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60404,7 +60404,7 @@
         <v>46220</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60482,7 +60482,7 @@
         <v>45167</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60560,7 +60560,7 @@
         <v>45015</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60638,7 +60638,7 @@
         <v>45216</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60716,7 +60716,7 @@
         <v>45400</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60794,7 +60794,7 @@
         <v>45391</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60872,7 +60872,7 @@
         <v>44805</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60950,7 +60950,7 @@
         <v>45015</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61028,7 +61028,7 @@
         <v>46190</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -584,24 +584,24 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S 4522-2023</t>
+          <t>A 23094-2025</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>samrådsanmälan</t>
+          <t>avverkningsanmälan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D2" s="1" t="n">
-        <v>45275</v>
+        <v>45791</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -619,45 +619,172 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>597.4</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="K2" t="n">
-        <v>6</v>
-      </c>
       <c r="L2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="R2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S2" t="n">
         <v>18</v>
       </c>
       <c r="T2" t="n">
+        <v>31</v>
+      </c>
+      <c r="U2" t="n">
+        <v>22</v>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Hårklockmossa
+Dropptaggsvamp
+Fjällig taggsvamp s.str.
+Motaggsvamp
+Orange taggsvamp
+Skarp dropptaggsvamp
+Trubbklockmossa
+Ullticka
+Fällmossa
+Platt fjädermossa
+Svart trolldruva
+Svavelriska
+Trädporella
+Blåsippa
+Hårklomossa
+Kattfot
+Svart taggsvamp agg.
+Vanlig padda</t>
+        </is>
+      </c>
+      <c r="W2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/artfynd/A 23094-2025 artfynd.xlsx", "A 23094-2025")</f>
+        <v/>
+      </c>
+      <c r="X2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/kartor/A 23094-2025 karta.png", "A 23094-2025")</f>
+        <v/>
+      </c>
+      <c r="Y2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/kartor_geotiff/A 23094-2025 georefererad karta.tif", "A 23094-2025")</f>
+        <v/>
+      </c>
+      <c r="AA2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomål/A 23094-2025 FSC-klagomål.docx", "A 23094-2025")</f>
+        <v/>
+      </c>
+      <c r="AB2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomålsmail/A 23094-2025 FSC-klagomål mail.docx", "A 23094-2025")</f>
+        <v/>
+      </c>
+      <c r="AC2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsyn/A 23094-2025 tillsynsbegäran.docx", "A 23094-2025")</f>
+        <v/>
+      </c>
+      <c r="AD2">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsynsmail/A 23094-2025 tillsynsbegäran mail.docx", "A 23094-2025")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>S 4522-2023</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>45275</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>LUDVIKA</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>597.4</v>
+      </c>
+      <c r="J3" t="n">
+        <v>5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>2</v>
+      </c>
+      <c r="N3" t="n">
+        <v>2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>9</v>
+      </c>
+      <c r="R3" t="n">
+        <v>4</v>
+      </c>
+      <c r="S3" t="n">
+        <v>18</v>
+      </c>
+      <c r="T3" t="n">
         <v>23</v>
       </c>
-      <c r="U2" t="n">
+      <c r="U3" t="n">
         <v>9</v>
       </c>
-      <c r="V2" s="2" t="inlineStr">
+      <c r="V3" s="2" t="inlineStr">
         <is>
           <t>Bitter taggsvamp
 Mosippa
@@ -679,162 +806,36 @@
 Lopplummer (aggregat)</t>
         </is>
       </c>
-      <c r="W2">
+      <c r="W3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/artfynd/S 4522-2023 artfynd.xlsx", "S 4522-2023")</f>
         <v/>
       </c>
-      <c r="X2">
+      <c r="X3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/kartor/S 4522-2023 karta.png", "S 4522-2023")</f>
         <v/>
       </c>
-      <c r="Y2">
+      <c r="Y3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/kartor_geotiff/S 4522-2023 georefererad karta.tif", "S 4522-2023")</f>
         <v/>
       </c>
-      <c r="Z2">
+      <c r="Z3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/knärot/S 4522-2023 karta knärot.png", "S 4522-2023")</f>
         <v/>
       </c>
-      <c r="AA2">
+      <c r="AA3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomål/S 4522-2023 FSC-klagomål.docx", "S 4522-2023")</f>
         <v/>
       </c>
-      <c r="AB2">
+      <c r="AB3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomålsmail/S 4522-2023 FSC-klagomål mail.docx", "S 4522-2023")</f>
         <v/>
       </c>
-      <c r="AC2">
+      <c r="AC3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsyn/S 4522-2023 tillsynsbegäran.docx", "S 4522-2023")</f>
         <v/>
       </c>
-      <c r="AD2">
+      <c r="AD3">
         <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsynsmail/S 4522-2023 tillsynsbegäran mail.docx", "S 4522-2023")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>A 23094-2025</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>45791</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46306</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>LUDVIKA</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5</v>
-      </c>
-      <c r="L3" t="n">
-        <v>7</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>1</v>
-      </c>
-      <c r="P3" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>8</v>
-      </c>
-      <c r="R3" t="n">
-        <v>1</v>
-      </c>
-      <c r="S3" t="n">
-        <v>17</v>
-      </c>
-      <c r="T3" t="n">
-        <v>30</v>
-      </c>
-      <c r="U3" t="n">
-        <v>21</v>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>Hårklockmossa
-Dropptaggsvamp
-Fjällig taggsvamp s.str.
-Motaggsvamp
-Orange taggsvamp
-Skarp dropptaggsvamp
-Trubbklockmossa
-Ullticka
-Fällmossa
-Platt fjädermossa
-Svart trolldruva
-Svavelriska
-Trädporella
-Blåsippa
-Kattfot
-Svart taggsvamp agg.
-Vanlig padda</t>
-        </is>
-      </c>
-      <c r="W3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/artfynd/A 23094-2025 artfynd.xlsx", "A 23094-2025")</f>
-        <v/>
-      </c>
-      <c r="X3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/kartor/A 23094-2025 karta.png", "A 23094-2025")</f>
-        <v/>
-      </c>
-      <c r="Y3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/kartor_geotiff/A 23094-2025 georefererad karta.tif", "A 23094-2025")</f>
-        <v/>
-      </c>
-      <c r="AA3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomål/A 23094-2025 FSC-klagomål.docx", "A 23094-2025")</f>
-        <v/>
-      </c>
-      <c r="AB3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/klagomålsmail/A 23094-2025 FSC-klagomål mail.docx", "A 23094-2025")</f>
-        <v/>
-      </c>
-      <c r="AC3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsyn/A 23094-2025 tillsynsbegäran.docx", "A 23094-2025")</f>
-        <v/>
-      </c>
-      <c r="AD3">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2085/tillsynsmail/A 23094-2025 tillsynsbegäran mail.docx", "A 23094-2025")</f>
         <v/>
       </c>
     </row>
@@ -858,7 +859,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +993,7 @@
         <v>45940</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1121,7 +1122,7 @@
         <v>45961</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1248,7 +1249,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1373,7 +1374,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1498,7 +1499,7 @@
         <v>44631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1620,7 +1621,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1741,7 +1742,7 @@
         <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1862,7 +1863,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1986,7 +1987,7 @@
         <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2106,7 +2107,7 @@
         <v>46275</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2224,7 +2225,7 @@
         <v>45981</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2351,7 +2352,7 @@
         <v>45849</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2464,7 +2465,7 @@
         <v>46163</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2586,7 +2587,7 @@
         <v>46058</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2707,7 +2708,7 @@
         <v>45786</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2824,7 +2825,7 @@
         <v>45509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2936,7 +2937,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3053,7 +3054,7 @@
         <v>45597</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3174,7 +3175,7 @@
         <v>45786</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3290,7 +3291,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3415,7 +3416,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3535,7 +3536,7 @@
         <v>46279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3651,7 +3652,7 @@
         <v>46170</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3771,7 +3772,7 @@
         <v>45957</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3886,7 +3887,7 @@
         <v>45842</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4009,7 +4010,7 @@
         <v>45971</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4128,7 +4129,7 @@
         <v>46010</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4247,7 +4248,7 @@
         <v>45785</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4361,7 +4362,7 @@
         <v>46167</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4476,7 +4477,7 @@
         <v>45993</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4594,7 +4595,7 @@
         <v>46163</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4708,7 +4709,7 @@
         <v>45940</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4827,7 +4828,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4941,7 +4942,7 @@
         <v>45930</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5059,7 +5060,7 @@
         <v>46010</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5177,7 +5178,7 @@
         <v>45541</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5291,7 +5292,7 @@
         <v>46163</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5409,7 +5410,7 @@
         <v>46163</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5522,7 +5523,7 @@
         <v>46163</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5635,7 +5636,7 @@
         <v>46216</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5752,7 +5753,7 @@
         <v>46253</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5870,7 +5871,7 @@
         <v>45926</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5987,7 +5988,7 @@
         <v>45985</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6104,7 +6105,7 @@
         <v>45246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6216,7 +6217,7 @@
         <v>45607</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6329,7 +6330,7 @@
         <v>45596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6446,7 +6447,7 @@
         <v>46198</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6563,7 +6564,7 @@
         <v>46283</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6676,7 +6677,7 @@
         <v>46163</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6788,7 +6789,7 @@
         <v>46155</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6905,7 +6906,7 @@
         <v>45373</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7017,7 +7018,7 @@
         <v>46260</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7129,7 +7130,7 @@
         <v>46260</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7245,7 +7246,7 @@
         <v>46265</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7362,7 +7363,7 @@
         <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7479,7 +7480,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7596,7 +7597,7 @@
         <v>45901</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7707,7 +7708,7 @@
         <v>44560</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7823,7 +7824,7 @@
         <v>45791</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7935,7 +7936,7 @@
         <v>45105</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8051,7 +8052,7 @@
         <v>46168</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8167,7 +8168,7 @@
         <v>46128</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8283,7 +8284,7 @@
         <v>45910</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8394,7 +8395,7 @@
         <v>46170</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8510,7 +8511,7 @@
         <v>44872</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8621,7 +8622,7 @@
         <v>45063</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8732,7 +8733,7 @@
         <v>44994</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8847,7 +8848,7 @@
         <v>45916</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8953,7 +8954,7 @@
         <v>45518</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9063,7 +9064,7 @@
         <v>45923</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9174,7 +9175,7 @@
         <v>44831</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9285,7 +9286,7 @@
         <v>45594</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9391,7 +9392,7 @@
         <v>45940</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9506,7 +9507,7 @@
         <v>45943</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9617,7 +9618,7 @@
         <v>45974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9732,7 +9733,7 @@
         <v>45321</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9838,7 +9839,7 @@
         <v>45978</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9953,7 +9954,7 @@
         <v>44923</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10063,7 +10064,7 @@
         <v>46150</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10178,7 +10179,7 @@
         <v>46125</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10289,7 +10290,7 @@
         <v>46167</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10400,7 +10401,7 @@
         <v>45971</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10515,7 +10516,7 @@
         <v>46198</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10626,7 +10627,7 @@
         <v>46168</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10741,7 +10742,7 @@
         <v>46198</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10852,7 +10853,7 @@
         <v>45940</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10963,7 +10964,7 @@
         <v>45978</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11078,7 +11079,7 @@
         <v>45708</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11188,7 +11189,7 @@
         <v>46260</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11298,7 +11299,7 @@
         <v>46260</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11408,7 +11409,7 @@
         <v>44693</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11523,7 +11524,7 @@
         <v>45687</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11634,7 +11635,7 @@
         <v>46010</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11749,7 +11750,7 @@
         <v>44571</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11859,7 +11860,7 @@
         <v>44643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11964,7 +11965,7 @@
         <v>44872</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12074,7 +12075,7 @@
         <v>45761</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12183,7 +12184,7 @@
         <v>45089</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12288,7 +12289,7 @@
         <v>44998</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12393,7 +12394,7 @@
         <v>45463</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12503,7 +12504,7 @@
         <v>45131</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12608,7 +12609,7 @@
         <v>45321</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12713,7 +12714,7 @@
         <v>44929</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12823,7 +12824,7 @@
         <v>45486</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12932,7 +12933,7 @@
         <v>45923</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13042,7 +13043,7 @@
         <v>45791</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13152,7 +13153,7 @@
         <v>44888</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13262,7 +13263,7 @@
         <v>45093</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13372,7 +13373,7 @@
         <v>44929</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13477,7 +13478,7 @@
         <v>45114</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13582,7 +13583,7 @@
         <v>44706</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13687,7 +13688,7 @@
         <v>44960</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13792,7 +13793,7 @@
         <v>45866</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13901,7 +13902,7 @@
         <v>45825</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14011,7 +14012,7 @@
         <v>45189</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14121,7 +14122,7 @@
         <v>44560</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14231,7 +14232,7 @@
         <v>45761</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14336,7 +14337,7 @@
         <v>45992</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14441,7 +14442,7 @@
         <v>46008</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14551,7 +14552,7 @@
         <v>45993</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14665,7 +14666,7 @@
         <v>46163</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14774,7 +14775,7 @@
         <v>46164</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14888,7 +14889,7 @@
         <v>46009</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14997,7 +14998,7 @@
         <v>46175</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15102,7 +15103,7 @@
         <v>45975</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15216,7 +15217,7 @@
         <v>45596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15326,7 +15327,7 @@
         <v>45644</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15435,7 +15436,7 @@
         <v>46219</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15545,7 +15546,7 @@
         <v>46276</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15655,7 +15656,7 @@
         <v>46247</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15769,7 +15770,7 @@
         <v>46265</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15879,7 +15880,7 @@
         <v>46269</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15989,7 +15990,7 @@
         <v>44771</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16062,7 +16063,7 @@
         <v>44869</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16135,7 +16136,7 @@
         <v>44502</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16208,7 +16209,7 @@
         <v>44503</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16286,7 +16287,7 @@
         <v>44550</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16364,7 +16365,7 @@
         <v>44560</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16442,7 +16443,7 @@
         <v>44658</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16515,7 +16516,7 @@
         <v>44827</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16593,7 +16594,7 @@
         <v>44730</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16671,7 +16672,7 @@
         <v>44590</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16744,7 +16745,7 @@
         <v>44851</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16817,7 +16818,7 @@
         <v>44482</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16890,7 +16891,7 @@
         <v>44616</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16963,7 +16964,7 @@
         <v>44706</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17041,7 +17042,7 @@
         <v>44771</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17114,7 +17115,7 @@
         <v>44482</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17187,7 +17188,7 @@
         <v>44508</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17265,7 +17266,7 @@
         <v>44785</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17343,7 +17344,7 @@
         <v>44872</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17421,7 +17422,7 @@
         <v>44730</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17499,7 +17500,7 @@
         <v>44715</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17577,7 +17578,7 @@
         <v>44720</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17650,7 +17651,7 @@
         <v>45056</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17728,7 +17729,7 @@
         <v>45372</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17801,7 +17802,7 @@
         <v>45166</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17879,7 +17880,7 @@
         <v>45411</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17957,7 +17958,7 @@
         <v>44819</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18035,7 +18036,7 @@
         <v>44942</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18108,7 +18109,7 @@
         <v>45110</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18181,7 +18182,7 @@
         <v>45603</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18259,7 +18260,7 @@
         <v>44730</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18337,7 +18338,7 @@
         <v>45551</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18410,7 +18411,7 @@
         <v>45705</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18483,7 +18484,7 @@
         <v>45637</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18556,7 +18557,7 @@
         <v>44967</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18629,7 +18630,7 @@
         <v>45219</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18707,7 +18708,7 @@
         <v>45554</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18780,7 +18781,7 @@
         <v>45335</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18853,7 +18854,7 @@
         <v>45099</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18931,7 +18932,7 @@
         <v>45520</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19004,7 +19005,7 @@
         <v>45265</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19077,7 +19078,7 @@
         <v>44825</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19155,7 +19156,7 @@
         <v>45202</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19233,7 +19234,7 @@
         <v>45481</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19306,7 +19307,7 @@
         <v>45208</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19384,7 +19385,7 @@
         <v>45297</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19457,7 +19458,7 @@
         <v>45218</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19530,7 +19531,7 @@
         <v>45450</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19603,7 +19604,7 @@
         <v>45071</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19681,7 +19682,7 @@
         <v>45644</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19754,7 +19755,7 @@
         <v>44826</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19832,7 +19833,7 @@
         <v>44853</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19910,7 +19911,7 @@
         <v>45105</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19983,7 +19984,7 @@
         <v>45119</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20061,7 +20062,7 @@
         <v>45611</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20139,7 +20140,7 @@
         <v>45526</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20212,7 +20213,7 @@
         <v>45512</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20290,7 +20291,7 @@
         <v>44825</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20363,7 +20364,7 @@
         <v>44859</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20441,7 +20442,7 @@
         <v>45602</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20514,7 +20515,7 @@
         <v>45288</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20587,7 +20588,7 @@
         <v>45103</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20660,7 +20661,7 @@
         <v>44865</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20738,7 +20739,7 @@
         <v>45680</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20811,7 +20812,7 @@
         <v>44883</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20889,7 +20890,7 @@
         <v>44852</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20962,7 +20963,7 @@
         <v>45399</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21040,7 +21041,7 @@
         <v>45541</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21118,7 +21119,7 @@
         <v>45813</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21196,7 +21197,7 @@
         <v>45799</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21274,7 +21275,7 @@
         <v>45579</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21347,7 +21348,7 @@
         <v>45579</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21420,7 +21421,7 @@
         <v>45537</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21498,7 +21499,7 @@
         <v>44482</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21571,7 +21572,7 @@
         <v>45607</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21649,7 +21650,7 @@
         <v>45569</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21727,7 +21728,7 @@
         <v>45621</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21805,7 +21806,7 @@
         <v>45502</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21878,7 +21879,7 @@
         <v>45891</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21956,7 +21957,7 @@
         <v>45317</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22029,7 +22030,7 @@
         <v>45895</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22102,7 +22103,7 @@
         <v>45898</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22180,7 +22181,7 @@
         <v>45898</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22258,7 +22259,7 @@
         <v>45474</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22331,7 +22332,7 @@
         <v>44844</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22409,7 +22410,7 @@
         <v>45379</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22487,7 +22488,7 @@
         <v>44895</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22565,7 +22566,7 @@
         <v>45512</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22643,7 +22644,7 @@
         <v>45512</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22721,7 +22722,7 @@
         <v>44978</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22794,7 +22795,7 @@
         <v>45212</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22867,7 +22868,7 @@
         <v>45902</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22945,7 +22946,7 @@
         <v>44994</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23018,7 +23019,7 @@
         <v>45646</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23091,7 +23092,7 @@
         <v>45317</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23164,7 +23165,7 @@
         <v>44515</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23242,7 +23243,7 @@
         <v>45903</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23320,7 +23321,7 @@
         <v>45903</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23398,7 +23399,7 @@
         <v>45903</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23476,7 +23477,7 @@
         <v>45562</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23554,7 +23555,7 @@
         <v>45258</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23627,7 +23628,7 @@
         <v>45868</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23700,7 +23701,7 @@
         <v>45404</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23773,7 +23774,7 @@
         <v>45485</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23851,7 +23852,7 @@
         <v>45909</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23924,7 +23925,7 @@
         <v>45743</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23997,7 +23998,7 @@
         <v>45110</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24070,7 +24071,7 @@
         <v>45910</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24148,7 +24149,7 @@
         <v>45910</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24221,7 +24222,7 @@
         <v>45911</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24299,7 +24300,7 @@
         <v>45519</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24372,7 +24373,7 @@
         <v>45911</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24450,7 +24451,7 @@
         <v>45911</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24528,7 +24529,7 @@
         <v>44533</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24606,7 +24607,7 @@
         <v>45910</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24679,7 +24680,7 @@
         <v>45915</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24752,7 +24753,7 @@
         <v>45784</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24825,7 +24826,7 @@
         <v>45784</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24898,7 +24899,7 @@
         <v>45545</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24971,7 +24972,7 @@
         <v>44893</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25044,7 +25045,7 @@
         <v>44893</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25117,7 +25118,7 @@
         <v>45565</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25190,7 +25191,7 @@
         <v>45460</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25263,7 +25264,7 @@
         <v>45230</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25341,7 +25342,7 @@
         <v>45917</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25414,7 +25415,7 @@
         <v>45572</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25492,7 +25493,7 @@
         <v>45581</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25570,7 +25571,7 @@
         <v>45488</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25643,7 +25644,7 @@
         <v>45609</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25721,7 +25722,7 @@
         <v>45581</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25799,7 +25800,7 @@
         <v>45603</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25877,7 +25878,7 @@
         <v>45134</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25955,7 +25956,7 @@
         <v>45789</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26033,7 +26034,7 @@
         <v>45789</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26111,7 +26112,7 @@
         <v>45600</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26184,7 +26185,7 @@
         <v>45533</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26262,7 +26263,7 @@
         <v>45569</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26340,7 +26341,7 @@
         <v>45912</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26418,7 +26419,7 @@
         <v>45924</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26496,7 +26497,7 @@
         <v>45789</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26574,7 +26575,7 @@
         <v>45113</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26652,7 +26653,7 @@
         <v>45924</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26730,7 +26731,7 @@
         <v>45924</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26808,7 +26809,7 @@
         <v>45924</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26886,7 +26887,7 @@
         <v>45602</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26959,7 +26960,7 @@
         <v>45789</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27037,7 +27038,7 @@
         <v>45902</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27115,7 +27116,7 @@
         <v>45586</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27188,7 +27189,7 @@
         <v>45581</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27266,7 +27267,7 @@
         <v>45924</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27344,7 +27345,7 @@
         <v>45925</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27417,7 +27418,7 @@
         <v>45112</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27495,7 +27496,7 @@
         <v>45926</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27573,7 +27574,7 @@
         <v>45560</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27651,7 +27652,7 @@
         <v>45926</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27729,7 +27730,7 @@
         <v>45791</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27807,7 +27808,7 @@
         <v>45786</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27880,7 +27881,7 @@
         <v>45644</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27953,7 +27954,7 @@
         <v>44893</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28026,7 +28027,7 @@
         <v>45926</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28104,7 +28105,7 @@
         <v>45524</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28182,7 +28183,7 @@
         <v>45560</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28260,7 +28261,7 @@
         <v>45639</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28338,7 +28339,7 @@
         <v>45453</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28416,7 +28417,7 @@
         <v>45541</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28494,7 +28495,7 @@
         <v>45569</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28572,7 +28573,7 @@
         <v>45062</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28650,7 +28651,7 @@
         <v>45796</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28728,7 +28729,7 @@
         <v>45541</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28806,7 +28807,7 @@
         <v>45622</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28884,7 +28885,7 @@
         <v>44915</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28962,7 +28963,7 @@
         <v>45499</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29035,7 +29036,7 @@
         <v>45189</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29108,7 +29109,7 @@
         <v>45791</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29186,7 +29187,7 @@
         <v>45191</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29264,7 +29265,7 @@
         <v>45776</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29337,7 +29338,7 @@
         <v>45622</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29415,7 +29416,7 @@
         <v>45791</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29493,7 +29494,7 @@
         <v>45791</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29571,7 +29572,7 @@
         <v>45594</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29649,7 +29650,7 @@
         <v>45622</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29727,7 +29728,7 @@
         <v>45622</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29805,7 +29806,7 @@
         <v>45770</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29878,7 +29879,7 @@
         <v>45198</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29956,7 +29957,7 @@
         <v>45800</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30034,7 +30035,7 @@
         <v>45799</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30112,7 +30113,7 @@
         <v>45800</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30190,7 +30191,7 @@
         <v>45579</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30263,7 +30264,7 @@
         <v>45512</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30341,7 +30342,7 @@
         <v>45805</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30419,7 +30420,7 @@
         <v>45622</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30497,7 +30498,7 @@
         <v>45622</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30575,7 +30576,7 @@
         <v>45099</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30653,7 +30654,7 @@
         <v>45810</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30731,7 +30732,7 @@
         <v>45810</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30809,7 +30810,7 @@
         <v>45810</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30887,7 +30888,7 @@
         <v>45740</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30960,7 +30961,7 @@
         <v>45187</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31038,7 +31039,7 @@
         <v>45687</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31111,7 +31112,7 @@
         <v>45168</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31189,7 +31190,7 @@
         <v>45940</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31267,7 +31268,7 @@
         <v>45940</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31345,7 +31346,7 @@
         <v>45940</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31423,7 +31424,7 @@
         <v>45208</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31501,7 +31502,7 @@
         <v>45569</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31579,7 +31580,7 @@
         <v>44789</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31652,7 +31653,7 @@
         <v>45944</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31725,7 +31726,7 @@
         <v>45623</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31803,7 +31804,7 @@
         <v>45813</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31881,7 +31882,7 @@
         <v>45813</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31959,7 +31960,7 @@
         <v>45813</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32037,7 +32038,7 @@
         <v>45166</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32115,7 +32116,7 @@
         <v>45813</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32193,7 +32194,7 @@
         <v>44970</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32271,7 +32272,7 @@
         <v>44708</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32349,7 +32350,7 @@
         <v>44687</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32422,7 +32423,7 @@
         <v>45210</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32500,7 +32501,7 @@
         <v>44711</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32578,7 +32579,7 @@
         <v>44841</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32651,7 +32652,7 @@
         <v>44960</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32729,7 +32730,7 @@
         <v>45754</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32807,7 +32808,7 @@
         <v>45624</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32880,7 +32881,7 @@
         <v>45603</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32958,7 +32959,7 @@
         <v>45645</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33036,7 +33037,7 @@
         <v>45824</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33109,7 +33110,7 @@
         <v>45629</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33187,7 +33188,7 @@
         <v>45826</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33265,7 +33266,7 @@
         <v>45244</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33338,7 +33339,7 @@
         <v>45952</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33411,7 +33412,7 @@
         <v>45826</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33489,7 +33490,7 @@
         <v>45625</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33562,7 +33563,7 @@
         <v>45827</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33640,7 +33641,7 @@
         <v>45301</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33713,7 +33714,7 @@
         <v>45156</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33786,7 +33787,7 @@
         <v>45519</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33859,7 +33860,7 @@
         <v>45593</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33937,7 +33938,7 @@
         <v>45832</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34015,7 +34016,7 @@
         <v>45831</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34093,7 +34094,7 @@
         <v>45831</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34171,7 +34172,7 @@
         <v>45954</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34244,7 +34245,7 @@
         <v>45954</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34322,7 +34323,7 @@
         <v>45954</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34400,7 +34401,7 @@
         <v>45954</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34478,7 +34479,7 @@
         <v>45954</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34556,7 +34557,7 @@
         <v>45954</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34629,7 +34630,7 @@
         <v>45954</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34707,7 +34708,7 @@
         <v>45954</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34780,7 +34781,7 @@
         <v>45957</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34858,7 +34859,7 @@
         <v>45954</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34931,7 +34932,7 @@
         <v>45957</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35009,7 +35010,7 @@
         <v>45891</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35087,7 +35088,7 @@
         <v>45219</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35165,7 +35166,7 @@
         <v>45253</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35243,7 +35244,7 @@
         <v>45253</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35321,7 +35322,7 @@
         <v>45891</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35399,7 +35400,7 @@
         <v>45062</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35477,7 +35478,7 @@
         <v>45835</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35555,7 +35556,7 @@
         <v>45963</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35633,7 +35634,7 @@
         <v>45924</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35711,7 +35712,7 @@
         <v>45840</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35789,7 +35790,7 @@
         <v>45904</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35862,7 +35863,7 @@
         <v>45966</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35940,7 +35941,7 @@
         <v>45840</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36013,7 +36014,7 @@
         <v>45198</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36091,7 +36092,7 @@
         <v>45965</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36169,7 +36170,7 @@
         <v>45965</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36242,7 +36243,7 @@
         <v>45210</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36320,7 +36321,7 @@
         <v>45208</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36393,7 +36394,7 @@
         <v>45968</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36471,7 +36472,7 @@
         <v>45638</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36544,7 +36545,7 @@
         <v>45644</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36622,7 +36623,7 @@
         <v>45972</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36700,7 +36701,7 @@
         <v>45568</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36773,7 +36774,7 @@
         <v>45845</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36851,7 +36852,7 @@
         <v>45971</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36929,7 +36930,7 @@
         <v>45971</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37007,7 +37008,7 @@
         <v>45971</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37085,7 +37086,7 @@
         <v>45971</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37163,7 +37164,7 @@
         <v>45502</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37241,7 +37242,7 @@
         <v>45974</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37319,7 +37320,7 @@
         <v>45974</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37397,7 +37398,7 @@
         <v>45973</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37475,7 +37476,7 @@
         <v>45974</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37553,7 +37554,7 @@
         <v>45973</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37631,7 +37632,7 @@
         <v>45246</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37704,7 +37705,7 @@
         <v>45754</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37782,7 +37783,7 @@
         <v>45973</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37860,7 +37861,7 @@
         <v>45744</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37938,7 +37939,7 @@
         <v>45973</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38016,7 +38017,7 @@
         <v>45974</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38094,7 +38095,7 @@
         <v>45849</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38172,7 +38173,7 @@
         <v>45974</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38250,7 +38251,7 @@
         <v>45525</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38323,7 +38324,7 @@
         <v>45975</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38401,7 +38402,7 @@
         <v>44729</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38479,7 +38480,7 @@
         <v>45825</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38557,7 +38558,7 @@
         <v>45512</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38635,7 +38636,7 @@
         <v>45832</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38713,7 +38714,7 @@
         <v>45832</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38791,7 +38792,7 @@
         <v>45840</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38869,7 +38870,7 @@
         <v>45832</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38947,7 +38948,7 @@
         <v>45567</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39025,7 +39026,7 @@
         <v>44680</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39103,7 +39104,7 @@
         <v>44581</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39181,7 +39182,7 @@
         <v>44771</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39254,7 +39255,7 @@
         <v>45869</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39332,7 +39333,7 @@
         <v>44820</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39410,7 +39411,7 @@
         <v>44820</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39488,7 +39489,7 @@
         <v>45337</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39561,7 +39562,7 @@
         <v>44915</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39639,7 +39640,7 @@
         <v>44859</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39717,7 +39718,7 @@
         <v>45687</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39790,7 +39791,7 @@
         <v>45761</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39863,7 +39864,7 @@
         <v>45762</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39936,7 +39937,7 @@
         <v>45875</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40009,7 +40010,7 @@
         <v>45981</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40087,7 +40088,7 @@
         <v>45765</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40160,7 +40161,7 @@
         <v>45243</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40233,7 +40234,7 @@
         <v>45616</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40311,7 +40312,7 @@
         <v>45279</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40384,7 +40385,7 @@
         <v>45301</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40457,7 +40458,7 @@
         <v>44916</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40535,7 +40536,7 @@
         <v>45775</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40613,7 +40614,7 @@
         <v>44879</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40686,7 +40687,7 @@
         <v>45887</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40764,7 +40765,7 @@
         <v>45891</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40842,7 +40843,7 @@
         <v>45929</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40920,7 +40921,7 @@
         <v>45929</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40998,7 +40999,7 @@
         <v>45497</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41071,7 +41072,7 @@
         <v>45988</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41149,7 +41150,7 @@
         <v>45106</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41222,7 +41223,7 @@
         <v>45988</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41300,7 +41301,7 @@
         <v>45909</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41373,7 +41374,7 @@
         <v>45989</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41446,7 +41447,7 @@
         <v>45989</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41519,7 +41520,7 @@
         <v>45989</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41597,7 +41598,7 @@
         <v>45989</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41670,7 +41671,7 @@
         <v>46114</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41748,7 +41749,7 @@
         <v>44970</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41826,7 +41827,7 @@
         <v>46119</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41904,7 +41905,7 @@
         <v>44552</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41977,7 +41978,7 @@
         <v>46122</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42055,7 +42056,7 @@
         <v>46122</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42133,7 +42134,7 @@
         <v>46122</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42211,7 +42212,7 @@
         <v>45995</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42284,7 +42285,7 @@
         <v>45995</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42362,7 +42363,7 @@
         <v>45995</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42440,7 +42441,7 @@
         <v>46122</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42518,7 +42519,7 @@
         <v>46126</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42596,7 +42597,7 @@
         <v>46126</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42674,7 +42675,7 @@
         <v>46126</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42752,7 +42753,7 @@
         <v>44730</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42830,7 +42831,7 @@
         <v>46001</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42908,7 +42909,7 @@
         <v>46001</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42986,7 +42987,7 @@
         <v>44599</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43059,7 +43060,7 @@
         <v>46128</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43132,7 +43133,7 @@
         <v>46134</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43210,7 +43211,7 @@
         <v>44859</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43288,7 +43289,7 @@
         <v>44960</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43366,7 +43367,7 @@
         <v>46007</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43444,7 +43445,7 @@
         <v>46008</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43522,7 +43523,7 @@
         <v>46007</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43600,7 +43601,7 @@
         <v>46008</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43678,7 +43679,7 @@
         <v>46008</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43756,7 +43757,7 @@
         <v>46008</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43834,7 +43835,7 @@
         <v>46008</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43912,7 +43913,7 @@
         <v>45196</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43990,7 +43991,7 @@
         <v>46135</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44068,7 +44069,7 @@
         <v>45849</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44146,7 +44147,7 @@
         <v>46008</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44224,7 +44225,7 @@
         <v>46008</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44302,7 +44303,7 @@
         <v>45205</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44380,7 +44381,7 @@
         <v>46008</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44458,7 +44459,7 @@
         <v>45960</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44536,7 +44537,7 @@
         <v>46010</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44614,7 +44615,7 @@
         <v>46010</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44692,7 +44693,7 @@
         <v>46009</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44770,7 +44771,7 @@
         <v>46062</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44848,7 +44849,7 @@
         <v>46009</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44921,7 +44922,7 @@
         <v>45825</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44994,7 +44995,7 @@
         <v>45849</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45072,7 +45073,7 @@
         <v>45594</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45150,7 +45151,7 @@
         <v>45594</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45228,7 +45229,7 @@
         <v>45043</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45306,7 +45307,7 @@
         <v>45845</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45384,7 +45385,7 @@
         <v>46066</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45462,7 +45463,7 @@
         <v>44903</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45535,7 +45536,7 @@
         <v>45827</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45613,7 +45614,7 @@
         <v>45968</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45691,7 +45692,7 @@
         <v>46029</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45769,7 +45770,7 @@
         <v>44970</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45847,7 +45848,7 @@
         <v>45225</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45925,7 +45926,7 @@
         <v>45954</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45998,7 +45999,7 @@
         <v>45988</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46076,7 +46077,7 @@
         <v>45971</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46154,7 +46155,7 @@
         <v>45835</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46232,7 +46233,7 @@
         <v>46002</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46310,7 +46311,7 @@
         <v>45531</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46388,7 +46389,7 @@
         <v>45161</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46466,7 +46467,7 @@
         <v>45562</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46539,7 +46540,7 @@
         <v>44890</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46617,7 +46618,7 @@
         <v>45562</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46695,7 +46696,7 @@
         <v>45860</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46773,7 +46774,7 @@
         <v>45902</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46846,7 +46847,7 @@
         <v>45961</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46924,7 +46925,7 @@
         <v>45574</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47002,7 +47003,7 @@
         <v>45961</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47080,7 +47081,7 @@
         <v>45371</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47153,7 +47154,7 @@
         <v>45243</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47226,7 +47227,7 @@
         <v>46037</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47299,7 +47300,7 @@
         <v>45373</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47372,7 +47373,7 @@
         <v>45588</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47445,7 +47446,7 @@
         <v>46141</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47523,7 +47524,7 @@
         <v>45631</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47601,7 +47602,7 @@
         <v>45176</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47674,7 +47675,7 @@
         <v>46141</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47752,7 +47753,7 @@
         <v>45581</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47830,7 +47831,7 @@
         <v>46141</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47908,7 +47909,7 @@
         <v>46142</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -47986,7 +47987,7 @@
         <v>46142</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48064,7 +48065,7 @@
         <v>46062</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48142,7 +48143,7 @@
         <v>46148</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48220,7 +48221,7 @@
         <v>45975</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48298,7 +48299,7 @@
         <v>45831</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48371,7 +48372,7 @@
         <v>46150</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48449,7 +48450,7 @@
         <v>45224</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48522,7 +48523,7 @@
         <v>46150</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48600,7 +48601,7 @@
         <v>46007</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48678,7 +48679,7 @@
         <v>46148</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48756,7 +48757,7 @@
         <v>45973</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48834,7 +48835,7 @@
         <v>45883</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48907,7 +48908,7 @@
         <v>46142</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -48985,7 +48986,7 @@
         <v>46155</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49058,7 +49059,7 @@
         <v>45679</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49131,7 +49132,7 @@
         <v>46155</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49209,7 +49210,7 @@
         <v>46155</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49287,7 +49288,7 @@
         <v>46155</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49365,7 +49366,7 @@
         <v>46155</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49443,7 +49444,7 @@
         <v>46113</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49516,7 +49517,7 @@
         <v>46160</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49594,7 +49595,7 @@
         <v>46160</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49672,7 +49673,7 @@
         <v>46161</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49750,7 +49751,7 @@
         <v>45791</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49828,7 +49829,7 @@
         <v>46167</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49906,7 +49907,7 @@
         <v>45833</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -49979,7 +49980,7 @@
         <v>45834</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50052,7 +50053,7 @@
         <v>46038</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50125,7 +50126,7 @@
         <v>46171</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50203,7 +50204,7 @@
         <v>46171</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50281,7 +50282,7 @@
         <v>46171</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50354,7 +50355,7 @@
         <v>46175</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50427,7 +50428,7 @@
         <v>46171</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50505,7 +50506,7 @@
         <v>46171</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50583,7 +50584,7 @@
         <v>46171</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50661,7 +50662,7 @@
         <v>46171</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50739,7 +50740,7 @@
         <v>46163</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50817,7 +50818,7 @@
         <v>46171</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50895,7 +50896,7 @@
         <v>46176</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -50973,7 +50974,7 @@
         <v>46167</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51051,7 +51052,7 @@
         <v>45938</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51129,7 +51130,7 @@
         <v>46142</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51207,7 +51208,7 @@
         <v>46183</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51285,7 +51286,7 @@
         <v>46163</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51358,7 +51359,7 @@
         <v>46185</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51436,7 +51437,7 @@
         <v>46185</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51514,7 +51515,7 @@
         <v>45596</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51592,7 +51593,7 @@
         <v>46184</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51670,7 +51671,7 @@
         <v>46190</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51748,7 +51749,7 @@
         <v>46190</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51826,7 +51827,7 @@
         <v>46190</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51904,7 +51905,7 @@
         <v>46183</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51982,7 +51983,7 @@
         <v>46190</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52060,7 +52061,7 @@
         <v>46191</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52133,7 +52134,7 @@
         <v>46030</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52206,7 +52207,7 @@
         <v>46160</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52284,7 +52285,7 @@
         <v>46146</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52362,7 +52363,7 @@
         <v>46146</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52440,7 +52441,7 @@
         <v>46160</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52518,7 +52519,7 @@
         <v>46160</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52596,7 +52597,7 @@
         <v>46160</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52674,7 +52675,7 @@
         <v>46198</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52752,7 +52753,7 @@
         <v>46171</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52830,7 +52831,7 @@
         <v>46155</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52908,7 +52909,7 @@
         <v>46190</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52986,7 +52987,7 @@
         <v>46205</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53064,7 +53065,7 @@
         <v>46142</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53142,7 +53143,7 @@
         <v>46167</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53220,7 +53221,7 @@
         <v>46206</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53298,7 +53299,7 @@
         <v>46206</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53376,7 +53377,7 @@
         <v>46195</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53454,7 +53455,7 @@
         <v>46198</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53532,7 +53533,7 @@
         <v>46198</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53610,7 +53611,7 @@
         <v>46195</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53688,7 +53689,7 @@
         <v>46154</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53766,7 +53767,7 @@
         <v>46198</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53844,7 +53845,7 @@
         <v>46195</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53922,7 +53923,7 @@
         <v>46195</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54000,7 +54001,7 @@
         <v>46195</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54078,7 +54079,7 @@
         <v>46195</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54156,7 +54157,7 @@
         <v>46142</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54234,7 +54235,7 @@
         <v>46195</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54312,7 +54313,7 @@
         <v>46195</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54390,7 +54391,7 @@
         <v>46195</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54468,7 +54469,7 @@
         <v>45685</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54541,7 +54542,7 @@
         <v>46195</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54619,7 +54620,7 @@
         <v>46195</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54697,7 +54698,7 @@
         <v>46217</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54775,7 +54776,7 @@
         <v>46218</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54853,7 +54854,7 @@
         <v>46219</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54931,7 +54932,7 @@
         <v>46265</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55009,7 +55010,7 @@
         <v>46225</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55087,7 +55088,7 @@
         <v>46267</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55160,7 +55161,7 @@
         <v>46230</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55238,7 +55239,7 @@
         <v>46272</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55311,7 +55312,7 @@
         <v>46206</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55389,7 +55390,7 @@
         <v>46273</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55462,7 +55463,7 @@
         <v>46230</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55540,7 +55541,7 @@
         <v>46273</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55618,7 +55619,7 @@
         <v>46273</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55696,7 +55697,7 @@
         <v>46273</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55774,7 +55775,7 @@
         <v>46267</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55852,7 +55853,7 @@
         <v>46267</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55930,7 +55931,7 @@
         <v>46275</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56003,7 +56004,7 @@
         <v>46276</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56076,7 +56077,7 @@
         <v>46280</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56154,7 +56155,7 @@
         <v>46279</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56232,7 +56233,7 @@
         <v>46279</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56310,7 +56311,7 @@
         <v>46233</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56388,7 +56389,7 @@
         <v>46280</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56466,7 +56467,7 @@
         <v>46279</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56544,7 +56545,7 @@
         <v>46281</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56622,7 +56623,7 @@
         <v>46282</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56700,7 +56701,7 @@
         <v>46241</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56778,7 +56779,7 @@
         <v>46241</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56856,7 +56857,7 @@
         <v>46241</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56929,7 +56930,7 @@
         <v>46283</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57007,7 +57008,7 @@
         <v>46283</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57085,7 +57086,7 @@
         <v>46241</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57163,7 +57164,7 @@
         <v>46241</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57241,7 +57242,7 @@
         <v>46283</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57319,7 +57320,7 @@
         <v>46283</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57397,7 +57398,7 @@
         <v>46287</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57475,7 +57476,7 @@
         <v>46287</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57553,7 +57554,7 @@
         <v>46288</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57626,7 +57627,7 @@
         <v>46247</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57704,7 +57705,7 @@
         <v>46290</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57782,7 +57783,7 @@
         <v>46247</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57855,7 +57856,7 @@
         <v>46286</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57933,7 +57934,7 @@
         <v>46290</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58011,7 +58012,7 @@
         <v>46290</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58089,7 +58090,7 @@
         <v>46290</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58167,7 +58168,7 @@
         <v>46286</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58245,7 +58246,7 @@
         <v>46290</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58323,7 +58324,7 @@
         <v>46290</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58401,7 +58402,7 @@
         <v>46294</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58479,7 +58480,7 @@
         <v>46248</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58552,7 +58553,7 @@
         <v>46294</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58630,7 +58631,7 @@
         <v>46294</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58708,7 +58709,7 @@
         <v>46294</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58786,7 +58787,7 @@
         <v>46294</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58864,7 +58865,7 @@
         <v>46255</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58942,7 +58943,7 @@
         <v>46255</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59020,7 +59021,7 @@
         <v>46255</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59098,7 +59099,7 @@
         <v>46255</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59176,7 +59177,7 @@
         <v>46122</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59254,7 +59255,7 @@
         <v>46255</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59332,7 +59333,7 @@
         <v>46255</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59410,7 +59411,7 @@
         <v>46255</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59488,7 +59489,7 @@
         <v>46301</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59561,7 +59562,7 @@
         <v>46258</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59639,7 +59640,7 @@
         <v>46253</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59717,7 +59718,7 @@
         <v>46258</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59795,7 +59796,7 @@
         <v>46262</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59873,7 +59874,7 @@
         <v>46247</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59951,7 +59952,7 @@
         <v>46147</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60029,7 +60030,7 @@
         <v>46204</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60107,7 +60108,7 @@
         <v>46260</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60180,7 +60181,7 @@
         <v>46260</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60253,7 +60254,7 @@
         <v>46265</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60331,7 +60332,7 @@
         <v>46260</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60404,7 +60405,7 @@
         <v>46220</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60482,7 +60483,7 @@
         <v>45167</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60560,7 +60561,7 @@
         <v>45015</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60638,7 +60639,7 @@
         <v>45216</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60716,7 +60717,7 @@
         <v>45400</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60794,7 +60795,7 @@
         <v>45391</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60872,7 +60873,7 @@
         <v>44805</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60950,7 +60951,7 @@
         <v>45015</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61028,7 +61029,7 @@
         <v>46190</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -601,7 +601,7 @@
         <v>45791</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45940</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>45961</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>46058</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45993</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>44631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46275</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45981</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46058</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45849</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>45945</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45509</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45597</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45786</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46170</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45785</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45957</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>45971</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>46010</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45993</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>46163</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>45842</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>45541</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>45930</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>46163</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46010</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>46163</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>46253</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>46163</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>46216</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45926</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>45246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45985</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>46198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>46283</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>46163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>46155</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>45596</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>45373</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>46265</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>46260</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>46260</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>44560</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45901</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>45105</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>46128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>46168</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>45791</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45910</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>46170</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44872</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45594</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45518</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>45063</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44923</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>45916</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45923</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>46150</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>45940</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>44994</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>45943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45321</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>46125</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>46167</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>46198</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45971</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>46168</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>46198</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45940</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44831</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45708</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>46260</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>46260</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45687</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>46010</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44571</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44872</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45761</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44960</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>44888</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44929</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45321</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>45131</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45093</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45089</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45923</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45866</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>46163</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>46164</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45992</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45761</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>44706</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>46009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>46175</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>46008</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45993</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>44929</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45114</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45463</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>44998</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>46219</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46276</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>46247</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45486</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45791</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45644</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>46265</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>46269</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45825</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44560</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44771</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44869</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44502</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44550</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44503</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>44730</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>44771</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44730</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44851</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44872</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44720</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44560</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>44658</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>44827</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>44590</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>44616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>44706</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>44785</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>44508</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>44715</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44893</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44841</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45212</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45569</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45594</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44711</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45317</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45572</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>45219</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45611</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>45687</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>45512</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>44960</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>45645</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>44852</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>44844</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>45519</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44730</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>45450</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>45105</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>44895</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44859</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45106</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45371</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45754</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>45646</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45622</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45208</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45625</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>44859</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45208</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45579</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45603</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>44890</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45191</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45623</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45744</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44893</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>44515</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>44994</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45502</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45512</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45253</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45208</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45246</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45562</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45594</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>44916</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45968</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45531</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45849</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45954</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45825</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45607</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45210</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45210</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45202</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45827</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45644</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45537</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45860</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45637</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45813</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45849</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44859</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45891</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45895</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44687</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45971</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45562</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>44978</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45588</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45845</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>46037</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45541</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45225</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45898</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45799</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>46062</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>46141</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>46141</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45898</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45903</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>45562</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45581</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>46141</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>44789</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45902</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45903</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45903</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44893</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45868</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44552</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45474</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45189</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45909</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>46066</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45911</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45911</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45910</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45910</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45910</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45911</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>46142</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46142</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45917</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45915</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44825</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45902</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45301</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45301</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45912</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45297</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45924</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45924</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45925</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45924</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45335</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>46148</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45926</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45926</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45639</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45883</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>46148</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>46150</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45512</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45196</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>46150</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45940</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45940</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45940</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45219</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45944</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45379</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45099</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46155</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>45113</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45973</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46155</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45952</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>46155</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>46142</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45679</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45954</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>46113</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>46155</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45954</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45957</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45954</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45488</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45954</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45954</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45954</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45954</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>45954</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>45957</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45954</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>44970</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44970</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45551</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>46160</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>46161</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45924</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45965</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>44853</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45965</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45891</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>45963</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>45891</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>45966</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45904</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>46160</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45279</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45971</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45099</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45971</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45968</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45971</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45971</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45568</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>45973</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45973</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45973</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>45973</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45972</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45974</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45975</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>45974</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>45974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45974</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45974</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>44825</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45043</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>45981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45399</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45644</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45288</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45743</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>46167</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45909</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>45989</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>45988</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45929</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45929</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45988</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45791</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45989</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44903</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45989</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45989</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45579</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45579</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45995</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45995</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45995</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>46001</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>46001</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46038</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45833</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45834</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45705</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45112</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45198</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45265</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>46007</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>46171</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44865</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>46007</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>46008</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>46008</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>46009</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>46009</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>46008</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>46008</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>46008</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>46008</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>46008</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>46008</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>46171</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>46010</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>46010</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45481</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45411</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>46171</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>44771</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45624</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>46029</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45103</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45775</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>45166</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>46171</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>46163</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>46171</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45520</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>46176</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>46171</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>46175</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>46171</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>46171</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>46167</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>46002</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>46142</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45938</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>44883</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46163</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45961</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>45062</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>45961</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>45168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45616</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45765</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45594</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45740</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>46183</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>44533</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45224</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45831</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>46007</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45569</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>46185</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>46185</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45110</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39395,7 +39395,7 @@
         <v>45166</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>46190</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>45119</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>45526</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>44730</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39780,7 +39780,7 @@
         <v>45373</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>46183</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>45243</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>46191</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45512</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>46190</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>46190</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>46190</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44915</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45485</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>45644</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45603</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45621</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>44942</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40847,7 +40847,7 @@
         <v>46030</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>46160</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>46160</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>46198</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>46160</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46160</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46114</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>46146</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>46146</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>46119</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>46122</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>46122</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>46122</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
         <v>46126</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>46126</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>46126</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>46128</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>46155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>46171</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46134</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45754</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45960</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44599</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45988</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>46062</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45835</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>46205</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42938,7 +42938,7 @@
         <v>46206</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>45244</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44970</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>46206</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>45198</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>46190</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>44879</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>46167</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>46195</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>46142</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43708,7 +43708,7 @@
         <v>46142</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45631</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>46154</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>44819</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>45685</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>46195</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>46195</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>46195</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>46195</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46195</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44483,7 +44483,7 @@
         <v>46198</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44561,7 +44561,7 @@
         <v>46195</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>46195</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>46195</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>46195</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>46198</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>46195</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>46218</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>46217</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>46198</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>46219</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45062</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>45404</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>46225</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>44826</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>46273</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>46272</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>46273</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>46273</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>46273</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>46230</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>46230</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>46206</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45593</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45156</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>46275</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45372</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>46279</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>46233</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>46279</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>46276</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>46279</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>44820</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>44820</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47100,7 +47100,7 @@
         <v>44708</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>45218</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>46280</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>46281</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>46280</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45243</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45560</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45519</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>46283</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>46283</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45071</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>46283</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>46283</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>46282</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45317</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45680</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>45205</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>44581</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45603</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>46241</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>46287</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45554</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45253</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45187</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>46287</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>46241</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>46241</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49171,7 +49171,7 @@
         <v>46241</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45110</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>44729</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>46241</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>44960</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49556,7 +49556,7 @@
         <v>46288</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49629,7 +49629,7 @@
         <v>44967</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>46286</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45258</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>46290</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>46290</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>46247</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>46286</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>46248</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45541</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>45622</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>46247</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>46290</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>46290</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45497</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45056</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45638</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>46294</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>46294</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>45602</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45176</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>46294</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>45622</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>46294</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45622</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51539,7 +51539,7 @@
         <v>45622</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51617,7 +51617,7 @@
         <v>45687</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45762</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45602</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>46122</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51914,7 +51914,7 @@
         <v>46255</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>46255</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52070,7 +52070,7 @@
         <v>46255</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>46255</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45545</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52299,7 +52299,7 @@
         <v>46258</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52377,7 +52377,7 @@
         <v>45784</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52450,7 +52450,7 @@
         <v>45565</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45230</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>45609</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45784</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>46301</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45134</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>46255</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>46255</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>46255</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>46253</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>45581</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45560</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45789</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45789</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>45789</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53605,7 +53605,7 @@
         <v>45581</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>45581</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>45600</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45569</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>46260</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45460</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45789</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45791</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45524</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45533</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54370,7 +54370,7 @@
         <v>45586</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>46260</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>46258</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45786</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54667,7 +54667,7 @@
         <v>44915</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54745,7 +54745,7 @@
         <v>45770</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54818,7 +54818,7 @@
         <v>45791</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>45453</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54974,7 +54974,7 @@
         <v>45541</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55052,7 +55052,7 @@
         <v>45776</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>45887</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>46307</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>45596</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45796</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55437,7 +55437,7 @@
         <v>46247</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55515,7 +55515,7 @@
         <v>46204</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
         <v>46220</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55671,7 +55671,7 @@
         <v>46307</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>45791</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55827,7 +55827,7 @@
         <v>45791</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>45975</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55983,7 +55983,7 @@
         <v>45499</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45799</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>46262</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56212,7 +56212,7 @@
         <v>45800</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45800</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56368,7 +56368,7 @@
         <v>46309</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56441,7 +56441,7 @@
         <v>45805</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>46267</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56592,7 +56592,7 @@
         <v>46286</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56670,7 +56670,7 @@
         <v>46265</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56748,7 +56748,7 @@
         <v>45810</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56826,7 +56826,7 @@
         <v>46260</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>46265</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56977,7 +56977,7 @@
         <v>45810</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57055,7 +57055,7 @@
         <v>45810</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45569</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57211,7 +57211,7 @@
         <v>45813</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57289,7 +57289,7 @@
         <v>45813</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57367,7 +57367,7 @@
         <v>45813</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45813</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57523,7 +57523,7 @@
         <v>46267</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>46311</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57679,7 +57679,7 @@
         <v>46290</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45824</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>46290</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57908,7 +57908,7 @@
         <v>46267</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57986,7 +57986,7 @@
         <v>45827</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>45826</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45826</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>45831</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         <v>45831</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>45832</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58454,7 +58454,7 @@
         <v>45835</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>45840</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58605,7 +58605,7 @@
         <v>45840</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58683,7 +58683,7 @@
         <v>45845</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58761,7 +58761,7 @@
         <v>45502</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58839,7 +58839,7 @@
         <v>45849</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58917,7 +58917,7 @@
         <v>45525</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58990,7 +58990,7 @@
         <v>45825</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59068,7 +59068,7 @@
         <v>45512</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45832</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59224,7 +59224,7 @@
         <v>45832</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59302,7 +59302,7 @@
         <v>45832</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59380,7 +59380,7 @@
         <v>45840</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59458,7 +59458,7 @@
         <v>44680</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>45869</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59614,7 +59614,7 @@
         <v>45567</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59692,7 +59692,7 @@
         <v>45337</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59765,7 +59765,7 @@
         <v>45761</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59838,7 +59838,7 @@
         <v>45875</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>45167</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59989,7 +59989,7 @@
         <v>45015</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60067,7 +60067,7 @@
         <v>45216</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60145,7 +60145,7 @@
         <v>45400</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60223,7 +60223,7 @@
         <v>45391</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>44805</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>45015</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>46190</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -601,7 +601,7 @@
         <v>45791</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45940</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>45961</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>46058</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>45993</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>44631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>46275</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>45981</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>46058</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         <v>45849</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>45945</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>45509</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45597</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45981</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3300,7 +3300,7 @@
         <v>45786</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46170</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45785</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45957</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4001,7 +4001,7 @@
         <v>45971</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>46010</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>46167</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4354,7 +4354,7 @@
         <v>45993</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>46163</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4586,7 +4586,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4705,7 +4705,7 @@
         <v>45842</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>45541</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5056,7 +5056,7 @@
         <v>45930</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>46163</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46010</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>46163</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5523,7 +5523,7 @@
         <v>46253</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>46163</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5754,7 +5754,7 @@
         <v>46216</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45607</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45926</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6101,7 +6101,7 @@
         <v>45246</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6213,7 +6213,7 @@
         <v>45985</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6330,7 +6330,7 @@
         <v>46198</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>46283</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>46163</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>46155</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6789,7 +6789,7 @@
         <v>45596</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>45373</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>46265</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>46260</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7251,7 +7251,7 @@
         <v>46260</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7363,7 +7363,7 @@
         <v>45929</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>44560</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7713,7 +7713,7 @@
         <v>45901</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>45105</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>46128</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
         <v>46168</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8172,7 +8172,7 @@
         <v>45791</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45910</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>46170</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>44872</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8622,7 +8622,7 @@
         <v>45594</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45518</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8838,7 +8838,7 @@
         <v>45063</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8949,7 +8949,7 @@
         <v>44923</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9059,7 +9059,7 @@
         <v>45916</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9165,7 +9165,7 @@
         <v>45923</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>46150</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9391,7 +9391,7 @@
         <v>45940</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9506,7 +9506,7 @@
         <v>44994</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9621,7 +9621,7 @@
         <v>45943</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45974</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>45321</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9953,7 +9953,7 @@
         <v>46125</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>46167</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10175,7 +10175,7 @@
         <v>45978</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>46198</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10401,7 +10401,7 @@
         <v>45971</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10516,7 +10516,7 @@
         <v>46168</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>46198</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>45940</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>45978</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11083,7 +11083,7 @@
         <v>44831</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45708</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11304,7 +11304,7 @@
         <v>46260</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>46260</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45687</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>46010</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44571</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44872</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>45761</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>45189</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12290,7 +12290,7 @@
         <v>44960</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12395,7 +12395,7 @@
         <v>44888</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12505,7 +12505,7 @@
         <v>44929</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12615,7 +12615,7 @@
         <v>45321</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12720,7 +12720,7 @@
         <v>45131</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12825,7 +12825,7 @@
         <v>45093</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12935,7 +12935,7 @@
         <v>45089</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>45923</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13150,7 +13150,7 @@
         <v>45866</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13259,7 +13259,7 @@
         <v>46163</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13368,7 +13368,7 @@
         <v>46164</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13482,7 +13482,7 @@
         <v>45992</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13587,7 +13587,7 @@
         <v>45761</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>44706</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>46009</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13910,7 +13910,7 @@
         <v>46175</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14015,7 +14015,7 @@
         <v>46008</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45993</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>44929</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>45114</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14449,7 +14449,7 @@
         <v>45463</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>44998</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14664,7 +14664,7 @@
         <v>46219</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14774,7 +14774,7 @@
         <v>46276</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>46247</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45486</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15107,7 +15107,7 @@
         <v>45791</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>45596</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15327,7 +15327,7 @@
         <v>45644</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15436,7 +15436,7 @@
         <v>46265</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>46269</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15656,7 +15656,7 @@
         <v>45825</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44560</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15876,7 +15876,7 @@
         <v>44771</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15949,7 +15949,7 @@
         <v>44869</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44502</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16095,7 +16095,7 @@
         <v>44550</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16173,7 +16173,7 @@
         <v>44503</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16251,7 +16251,7 @@
         <v>44730</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>44771</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>44730</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>44851</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16553,7 +16553,7 @@
         <v>44872</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16631,7 +16631,7 @@
         <v>44720</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16704,7 +16704,7 @@
         <v>44560</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16782,7 +16782,7 @@
         <v>44658</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>44827</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16933,7 +16933,7 @@
         <v>44590</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>44616</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17079,7 +17079,7 @@
         <v>44706</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
         <v>44785</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17235,7 +17235,7 @@
         <v>44508</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
         <v>44715</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44893</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>44841</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45212</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45569</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45594</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17766,7 +17766,7 @@
         <v>44711</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17844,7 +17844,7 @@
         <v>45317</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17917,7 +17917,7 @@
         <v>45572</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>45219</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18073,7 +18073,7 @@
         <v>45611</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45622</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>45687</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18302,7 +18302,7 @@
         <v>45512</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>44960</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18458,7 +18458,7 @@
         <v>45645</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>44852</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18609,7 +18609,7 @@
         <v>44844</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
         <v>45519</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>44730</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>45450</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>45105</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18984,7 +18984,7 @@
         <v>44895</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>44859</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>45106</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>45371</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>45754</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19364,7 +19364,7 @@
         <v>45646</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19437,7 +19437,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>45622</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19593,7 +19593,7 @@
         <v>45208</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19671,7 +19671,7 @@
         <v>45625</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>44859</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45208</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>45579</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45603</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>44890</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45191</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>45623</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20285,7 +20285,7 @@
         <v>45744</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44893</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
         <v>44515</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>44994</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45502</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45512</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45253</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45208</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45246</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45562</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45594</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21118,7 +21118,7 @@
         <v>44916</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45968</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45531</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45849</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21430,7 +21430,7 @@
         <v>45954</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45825</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45607</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45210</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>45210</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45202</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21888,7 +21888,7 @@
         <v>45827</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>45902</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45644</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45537</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45860</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>45637</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45813</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22419,7 +22419,7 @@
         <v>45849</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22497,7 +22497,7 @@
         <v>44859</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>45891</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22653,7 +22653,7 @@
         <v>45895</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22726,7 +22726,7 @@
         <v>44687</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22799,7 +22799,7 @@
         <v>45971</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22877,7 +22877,7 @@
         <v>45562</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22955,7 +22955,7 @@
         <v>44978</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23028,7 +23028,7 @@
         <v>45588</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23101,7 +23101,7 @@
         <v>45845</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23179,7 +23179,7 @@
         <v>46037</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45541</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23330,7 +23330,7 @@
         <v>45225</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45898</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23486,7 +23486,7 @@
         <v>45799</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23564,7 +23564,7 @@
         <v>45574</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>46062</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23720,7 +23720,7 @@
         <v>46141</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23798,7 +23798,7 @@
         <v>46141</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23876,7 +23876,7 @@
         <v>45898</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23954,7 +23954,7 @@
         <v>45903</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>45562</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45581</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24183,7 +24183,7 @@
         <v>46141</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24261,7 +24261,7 @@
         <v>44789</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45902</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24412,7 +24412,7 @@
         <v>45903</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24490,7 +24490,7 @@
         <v>45903</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24568,7 +24568,7 @@
         <v>44893</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24641,7 +24641,7 @@
         <v>45868</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24714,7 +24714,7 @@
         <v>44552</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24787,7 +24787,7 @@
         <v>45474</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24860,7 +24860,7 @@
         <v>45189</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24933,7 +24933,7 @@
         <v>45629</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25011,7 +25011,7 @@
         <v>45909</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25084,7 +25084,7 @@
         <v>46066</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25162,7 +25162,7 @@
         <v>45911</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25240,7 +25240,7 @@
         <v>45911</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45910</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45910</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45910</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45911</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>46142</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>46142</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45917</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45915</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25922,7 +25922,7 @@
         <v>44825</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45902</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45301</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45301</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45912</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45297</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45924</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45924</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45925</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45924</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26682,7 +26682,7 @@
         <v>45335</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26755,7 +26755,7 @@
         <v>46148</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>45926</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45926</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26989,7 +26989,7 @@
         <v>45926</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27067,7 +27067,7 @@
         <v>45639</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27145,7 +27145,7 @@
         <v>45883</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27218,7 +27218,7 @@
         <v>46148</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27296,7 +27296,7 @@
         <v>46150</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45512</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27452,7 +27452,7 @@
         <v>45196</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27530,7 +27530,7 @@
         <v>46150</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27608,7 +27608,7 @@
         <v>45940</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27686,7 +27686,7 @@
         <v>45940</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27764,7 +27764,7 @@
         <v>45940</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27842,7 +27842,7 @@
         <v>45219</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27920,7 +27920,7 @@
         <v>45944</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27993,7 +27993,7 @@
         <v>45379</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28071,7 +28071,7 @@
         <v>45099</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28149,7 +28149,7 @@
         <v>46155</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28227,7 +28227,7 @@
         <v>45113</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28305,7 +28305,7 @@
         <v>45973</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28383,7 +28383,7 @@
         <v>46155</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28456,7 +28456,7 @@
         <v>45952</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28529,7 +28529,7 @@
         <v>46155</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28607,7 +28607,7 @@
         <v>46142</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28685,7 +28685,7 @@
         <v>45679</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28758,7 +28758,7 @@
         <v>45954</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>46113</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28909,7 +28909,7 @@
         <v>46155</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28987,7 +28987,7 @@
         <v>45954</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29065,7 +29065,7 @@
         <v>45957</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45954</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45488</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45954</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29367,7 +29367,7 @@
         <v>45954</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45954</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29518,7 +29518,7 @@
         <v>45954</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>45954</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29669,7 +29669,7 @@
         <v>45957</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29747,7 +29747,7 @@
         <v>45954</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29820,7 +29820,7 @@
         <v>44970</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44970</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>45551</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30049,7 +30049,7 @@
         <v>46160</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30127,7 +30127,7 @@
         <v>46161</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30205,7 +30205,7 @@
         <v>45924</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45965</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30356,7 +30356,7 @@
         <v>44853</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45965</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30512,7 +30512,7 @@
         <v>45891</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30590,7 +30590,7 @@
         <v>45963</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30668,7 +30668,7 @@
         <v>45891</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30746,7 +30746,7 @@
         <v>45966</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>45904</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30897,7 +30897,7 @@
         <v>46160</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45279</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31048,7 +31048,7 @@
         <v>45971</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45099</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31204,7 +31204,7 @@
         <v>45971</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31282,7 +31282,7 @@
         <v>45968</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31360,7 +31360,7 @@
         <v>45971</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31438,7 +31438,7 @@
         <v>45971</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31516,7 +31516,7 @@
         <v>45568</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31589,7 +31589,7 @@
         <v>45973</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45973</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>45973</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>45973</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45972</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31979,7 +31979,7 @@
         <v>45974</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32057,7 +32057,7 @@
         <v>45975</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>45974</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32213,7 +32213,7 @@
         <v>45974</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45974</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45974</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32447,7 +32447,7 @@
         <v>44825</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32520,7 +32520,7 @@
         <v>45043</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32598,7 +32598,7 @@
         <v>45981</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32676,7 +32676,7 @@
         <v>45399</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32754,7 +32754,7 @@
         <v>45644</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>45288</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32905,7 +32905,7 @@
         <v>45743</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32978,7 +32978,7 @@
         <v>46167</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>45909</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33129,7 +33129,7 @@
         <v>45989</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33202,7 +33202,7 @@
         <v>45988</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45929</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33358,7 +33358,7 @@
         <v>45929</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33436,7 +33436,7 @@
         <v>45988</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33514,7 +33514,7 @@
         <v>45791</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33592,7 +33592,7 @@
         <v>45989</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33665,7 +33665,7 @@
         <v>44903</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45989</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33811,7 +33811,7 @@
         <v>45989</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33889,7 +33889,7 @@
         <v>45579</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45579</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>45995</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34108,7 +34108,7 @@
         <v>45995</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34186,7 +34186,7 @@
         <v>45995</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>46001</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34342,7 +34342,7 @@
         <v>46001</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34420,7 +34420,7 @@
         <v>46038</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34493,7 +34493,7 @@
         <v>45833</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34566,7 +34566,7 @@
         <v>45834</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34639,7 +34639,7 @@
         <v>45705</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45112</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34790,7 +34790,7 @@
         <v>45198</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34868,7 +34868,7 @@
         <v>45265</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34941,7 +34941,7 @@
         <v>46007</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>46171</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35092,7 +35092,7 @@
         <v>44865</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35170,7 +35170,7 @@
         <v>46007</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35248,7 +35248,7 @@
         <v>46008</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35326,7 +35326,7 @@
         <v>46008</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>46009</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>46009</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35555,7 +35555,7 @@
         <v>46008</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35633,7 +35633,7 @@
         <v>46008</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35711,7 +35711,7 @@
         <v>46008</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35789,7 +35789,7 @@
         <v>46008</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>46008</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>46008</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>46171</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36101,7 +36101,7 @@
         <v>46010</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>46010</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36257,7 +36257,7 @@
         <v>45481</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45411</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36408,7 +36408,7 @@
         <v>46171</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36486,7 +36486,7 @@
         <v>44771</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45624</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>46029</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36710,7 +36710,7 @@
         <v>45103</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36783,7 +36783,7 @@
         <v>45775</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36861,7 +36861,7 @@
         <v>45166</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36939,7 +36939,7 @@
         <v>46171</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37017,7 +37017,7 @@
         <v>46163</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37095,7 +37095,7 @@
         <v>46171</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>45520</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>46176</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37324,7 +37324,7 @@
         <v>46171</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37402,7 +37402,7 @@
         <v>46175</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37475,7 +37475,7 @@
         <v>46171</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>46171</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37631,7 +37631,7 @@
         <v>46167</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37709,7 +37709,7 @@
         <v>46002</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37787,7 +37787,7 @@
         <v>46142</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45938</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37943,7 +37943,7 @@
         <v>44883</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38021,7 +38021,7 @@
         <v>46163</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>45961</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>45062</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38250,7 +38250,7 @@
         <v>45961</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>45168</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38406,7 +38406,7 @@
         <v>45616</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38484,7 +38484,7 @@
         <v>45765</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38557,7 +38557,7 @@
         <v>45594</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45740</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>46183</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38786,7 +38786,7 @@
         <v>44533</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38864,7 +38864,7 @@
         <v>45224</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38937,7 +38937,7 @@
         <v>45831</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39010,7 +39010,7 @@
         <v>46007</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39088,7 +39088,7 @@
         <v>45569</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39166,7 +39166,7 @@
         <v>46185</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39244,7 +39244,7 @@
         <v>46185</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45110</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39395,7 +39395,7 @@
         <v>45166</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39473,7 +39473,7 @@
         <v>46190</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>45119</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>45526</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39702,7 +39702,7 @@
         <v>44730</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39780,7 +39780,7 @@
         <v>45373</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39853,7 +39853,7 @@
         <v>46183</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39931,7 +39931,7 @@
         <v>45243</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40004,7 +40004,7 @@
         <v>46191</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40077,7 +40077,7 @@
         <v>45512</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40155,7 +40155,7 @@
         <v>46190</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40233,7 +40233,7 @@
         <v>46190</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>46190</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44915</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45485</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40545,7 +40545,7 @@
         <v>45644</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40618,7 +40618,7 @@
         <v>45603</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40696,7 +40696,7 @@
         <v>45621</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>44942</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40847,7 +40847,7 @@
         <v>46030</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40920,7 +40920,7 @@
         <v>46160</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40998,7 +40998,7 @@
         <v>46160</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41076,7 +41076,7 @@
         <v>46198</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>46160</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41232,7 +41232,7 @@
         <v>46160</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>46114</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>46146</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41466,7 +41466,7 @@
         <v>46146</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41544,7 +41544,7 @@
         <v>46119</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>46122</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41700,7 +41700,7 @@
         <v>46122</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41778,7 +41778,7 @@
         <v>46122</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41856,7 +41856,7 @@
         <v>46126</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>46126</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>46126</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42090,7 +42090,7 @@
         <v>46128</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42163,7 +42163,7 @@
         <v>46155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42241,7 +42241,7 @@
         <v>46171</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>46134</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42397,7 +42397,7 @@
         <v>45754</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42475,7 +42475,7 @@
         <v>45960</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>44599</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45988</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42704,7 +42704,7 @@
         <v>46062</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42782,7 +42782,7 @@
         <v>45835</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42860,7 +42860,7 @@
         <v>46205</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42938,7 +42938,7 @@
         <v>46206</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43016,7 +43016,7 @@
         <v>45244</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43089,7 +43089,7 @@
         <v>44970</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>46206</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43245,7 +43245,7 @@
         <v>45198</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43323,7 +43323,7 @@
         <v>46190</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>44879</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>46167</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>46195</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43630,7 +43630,7 @@
         <v>46142</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43708,7 +43708,7 @@
         <v>46142</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45631</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43864,7 +43864,7 @@
         <v>46154</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>44819</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>45685</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>46195</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44171,7 +44171,7 @@
         <v>46195</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>46195</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44327,7 +44327,7 @@
         <v>46195</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44405,7 +44405,7 @@
         <v>46195</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44483,7 +44483,7 @@
         <v>46198</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44561,7 +44561,7 @@
         <v>46195</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44639,7 +44639,7 @@
         <v>46195</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44717,7 +44717,7 @@
         <v>46195</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44795,7 +44795,7 @@
         <v>46195</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44873,7 +44873,7 @@
         <v>46198</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>46195</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>46218</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45107,7 +45107,7 @@
         <v>46217</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45185,7 +45185,7 @@
         <v>46198</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45263,7 +45263,7 @@
         <v>46219</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45341,7 +45341,7 @@
         <v>45062</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45419,7 +45419,7 @@
         <v>45404</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>46225</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45570,7 +45570,7 @@
         <v>44826</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45648,7 +45648,7 @@
         <v>46273</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45726,7 +45726,7 @@
         <v>46272</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45799,7 +45799,7 @@
         <v>46273</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45877,7 +45877,7 @@
         <v>46273</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -45950,7 +45950,7 @@
         <v>46273</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>46230</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>46230</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46184,7 +46184,7 @@
         <v>46206</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46262,7 +46262,7 @@
         <v>45593</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46340,7 +46340,7 @@
         <v>45156</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46413,7 +46413,7 @@
         <v>46275</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46486,7 +46486,7 @@
         <v>45372</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46559,7 +46559,7 @@
         <v>46279</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46637,7 +46637,7 @@
         <v>46233</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46715,7 +46715,7 @@
         <v>46279</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46793,7 +46793,7 @@
         <v>46276</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46866,7 +46866,7 @@
         <v>46279</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -46944,7 +46944,7 @@
         <v>44820</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>44820</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47100,7 +47100,7 @@
         <v>44708</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>45218</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>46280</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>46281</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47407,7 +47407,7 @@
         <v>46280</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47485,7 +47485,7 @@
         <v>45243</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47558,7 +47558,7 @@
         <v>45560</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47636,7 +47636,7 @@
         <v>45519</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47709,7 +47709,7 @@
         <v>46283</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>46283</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47865,7 +47865,7 @@
         <v>45071</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -47943,7 +47943,7 @@
         <v>46283</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>46283</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48099,7 +48099,7 @@
         <v>46282</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48177,7 +48177,7 @@
         <v>45317</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48250,7 +48250,7 @@
         <v>45680</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48323,7 +48323,7 @@
         <v>45205</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48401,7 +48401,7 @@
         <v>44581</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48479,7 +48479,7 @@
         <v>45603</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48557,7 +48557,7 @@
         <v>46241</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48630,7 +48630,7 @@
         <v>46287</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48708,7 +48708,7 @@
         <v>45554</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48781,7 +48781,7 @@
         <v>45253</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45187</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>46287</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49015,7 +49015,7 @@
         <v>46241</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49093,7 +49093,7 @@
         <v>46241</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49171,7 +49171,7 @@
         <v>46241</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>45110</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49322,7 +49322,7 @@
         <v>44729</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49400,7 +49400,7 @@
         <v>46241</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49478,7 +49478,7 @@
         <v>44960</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49556,7 +49556,7 @@
         <v>46288</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49629,7 +49629,7 @@
         <v>44967</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>46286</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49780,7 +49780,7 @@
         <v>45258</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49853,7 +49853,7 @@
         <v>46290</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -49931,7 +49931,7 @@
         <v>46290</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50009,7 +50009,7 @@
         <v>46247</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>46286</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50165,7 +50165,7 @@
         <v>46248</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>45541</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50316,7 +50316,7 @@
         <v>45622</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>46247</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50467,7 +50467,7 @@
         <v>46290</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50545,7 +50545,7 @@
         <v>46290</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50623,7 +50623,7 @@
         <v>45497</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50696,7 +50696,7 @@
         <v>45056</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50774,7 +50774,7 @@
         <v>45638</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50847,7 +50847,7 @@
         <v>46294</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -50925,7 +50925,7 @@
         <v>46294</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51003,7 +51003,7 @@
         <v>46294</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51081,7 +51081,7 @@
         <v>45602</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51154,7 +51154,7 @@
         <v>45176</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51227,7 +51227,7 @@
         <v>46294</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51305,7 +51305,7 @@
         <v>45622</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51383,7 +51383,7 @@
         <v>46294</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51461,7 +51461,7 @@
         <v>45622</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51539,7 +51539,7 @@
         <v>45622</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51617,7 +51617,7 @@
         <v>45687</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51690,7 +51690,7 @@
         <v>45762</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51763,7 +51763,7 @@
         <v>45602</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51836,7 +51836,7 @@
         <v>46122</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -51914,7 +51914,7 @@
         <v>46255</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -51992,7 +51992,7 @@
         <v>46255</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52070,7 +52070,7 @@
         <v>46255</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52148,7 +52148,7 @@
         <v>46255</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52226,7 +52226,7 @@
         <v>45545</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52299,7 +52299,7 @@
         <v>46258</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52377,7 +52377,7 @@
         <v>45784</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52450,7 +52450,7 @@
         <v>45565</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52523,7 +52523,7 @@
         <v>45230</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52601,7 +52601,7 @@
         <v>45609</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52679,7 +52679,7 @@
         <v>45784</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52752,7 +52752,7 @@
         <v>46301</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52825,7 +52825,7 @@
         <v>45134</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>46255</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -52981,7 +52981,7 @@
         <v>46255</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53059,7 +53059,7 @@
         <v>46255</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>46253</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>45581</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53293,7 +53293,7 @@
         <v>45560</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53371,7 +53371,7 @@
         <v>45789</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53449,7 +53449,7 @@
         <v>45789</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53527,7 +53527,7 @@
         <v>45789</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53605,7 +53605,7 @@
         <v>45581</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53683,7 +53683,7 @@
         <v>45581</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53761,7 +53761,7 @@
         <v>45600</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53834,7 +53834,7 @@
         <v>45569</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -53912,7 +53912,7 @@
         <v>46260</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -53985,7 +53985,7 @@
         <v>45460</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54058,7 +54058,7 @@
         <v>45789</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54136,7 +54136,7 @@
         <v>45791</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54214,7 +54214,7 @@
         <v>45524</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54292,7 +54292,7 @@
         <v>45533</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54370,7 +54370,7 @@
         <v>45586</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54443,7 +54443,7 @@
         <v>46260</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54516,7 +54516,7 @@
         <v>46258</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54594,7 +54594,7 @@
         <v>45786</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54667,7 +54667,7 @@
         <v>44915</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54745,7 +54745,7 @@
         <v>45770</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54818,7 +54818,7 @@
         <v>45791</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -54896,7 +54896,7 @@
         <v>45453</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -54974,7 +54974,7 @@
         <v>45541</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55052,7 +55052,7 @@
         <v>45776</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55125,7 +55125,7 @@
         <v>45887</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55203,7 +55203,7 @@
         <v>46307</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55281,7 +55281,7 @@
         <v>45596</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>45796</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55437,7 +55437,7 @@
         <v>46247</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55515,7 +55515,7 @@
         <v>46204</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55593,7 +55593,7 @@
         <v>46220</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55671,7 +55671,7 @@
         <v>46307</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55749,7 +55749,7 @@
         <v>45791</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55827,7 +55827,7 @@
         <v>45791</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55905,7 +55905,7 @@
         <v>45975</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -55983,7 +55983,7 @@
         <v>45499</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56056,7 +56056,7 @@
         <v>45799</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56134,7 +56134,7 @@
         <v>46262</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56212,7 +56212,7 @@
         <v>45800</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56290,7 +56290,7 @@
         <v>45800</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56368,7 +56368,7 @@
         <v>46309</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56441,7 +56441,7 @@
         <v>45805</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56519,7 +56519,7 @@
         <v>46267</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56592,7 +56592,7 @@
         <v>46286</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56670,7 +56670,7 @@
         <v>46265</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56748,7 +56748,7 @@
         <v>45810</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56826,7 +56826,7 @@
         <v>46260</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56899,7 +56899,7 @@
         <v>46265</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -56977,7 +56977,7 @@
         <v>45810</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57055,7 +57055,7 @@
         <v>45810</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57133,7 +57133,7 @@
         <v>45569</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57211,7 +57211,7 @@
         <v>45813</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57289,7 +57289,7 @@
         <v>45813</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57367,7 +57367,7 @@
         <v>45813</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57445,7 +57445,7 @@
         <v>45813</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57523,7 +57523,7 @@
         <v>46267</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57601,7 +57601,7 @@
         <v>46311</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57679,7 +57679,7 @@
         <v>46290</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57757,7 +57757,7 @@
         <v>45824</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57830,7 +57830,7 @@
         <v>46290</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57908,7 +57908,7 @@
         <v>46267</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -57986,7 +57986,7 @@
         <v>45827</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58064,7 +58064,7 @@
         <v>45826</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58142,7 +58142,7 @@
         <v>45826</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58220,7 +58220,7 @@
         <v>45831</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58298,7 +58298,7 @@
         <v>45831</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58376,7 +58376,7 @@
         <v>45832</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58454,7 +58454,7 @@
         <v>45835</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58532,7 +58532,7 @@
         <v>45840</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58605,7 +58605,7 @@
         <v>45840</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58683,7 +58683,7 @@
         <v>45845</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58761,7 +58761,7 @@
         <v>45502</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58839,7 +58839,7 @@
         <v>45849</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58917,7 +58917,7 @@
         <v>45525</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -58990,7 +58990,7 @@
         <v>45825</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59068,7 +59068,7 @@
         <v>45512</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59146,7 +59146,7 @@
         <v>45832</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59224,7 +59224,7 @@
         <v>45832</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59302,7 +59302,7 @@
         <v>45832</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59380,7 +59380,7 @@
         <v>45840</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59458,7 +59458,7 @@
         <v>44680</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59536,7 +59536,7 @@
         <v>45869</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59614,7 +59614,7 @@
         <v>45567</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59692,7 +59692,7 @@
         <v>45337</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59765,7 +59765,7 @@
         <v>45761</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59838,7 +59838,7 @@
         <v>45875</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59911,7 +59911,7 @@
         <v>45167</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -59989,7 +59989,7 @@
         <v>45015</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60067,7 +60067,7 @@
         <v>45216</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60145,7 +60145,7 @@
         <v>45400</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60223,7 +60223,7 @@
         <v>45391</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60301,7 +60301,7 @@
         <v>44805</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60379,7 +60379,7 @@
         <v>45015</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60457,7 +60457,7 @@
         <v>46190</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -601,7 +601,7 @@
         <v>45791</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45940</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>45961</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>44631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45981</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46275</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45849</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>45786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>46058</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>45509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45597</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45786</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46170</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>46167</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45957</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45971</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>46010</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45842</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>45785</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>45993</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>46163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>45930</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45541</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46010</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>46253</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>46216</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>46163</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>46163</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45926</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>45985</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>46198</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>46283</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>45596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>46265</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45929</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>45373</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>46260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>46163</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>46155</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>46260</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45246</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45901</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>45105</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46128</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>45791</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44560</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>46168</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>46170</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45916</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>45923</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45940</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>46125</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>46167</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>45943</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45971</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45974</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>46198</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>45063</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>46198</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45978</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45708</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44994</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44693</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>46260</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45940</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>46260</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45978</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>46168</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>46150</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44923</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45594</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45321</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45687</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>46010</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44571</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44872</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>46163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>46164</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45923</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>46009</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>46175</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45463</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45866</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44929</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45992</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>46219</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>46008</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45486</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45791</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45993</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>46247</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45825</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44560</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>46265</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>45596</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>46269</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>46314</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44888</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>46276</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>45644</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45093</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44929</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45114</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>44960</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45189</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45761</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45089</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44998</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>45131</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45321</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>44706</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45761</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44771</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44869</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44502</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>44503</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>44550</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>44730</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44771</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44730</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>44851</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>44872</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>44720</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>44560</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>44658</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44827</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>44590</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44706</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>44785</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>44616</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44508</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>44715</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45541</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45813</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45799</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45537</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44819</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45705</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45219</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45335</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44825</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45202</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45891</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45205</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45895</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45071</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>44826</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45898</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45526</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44825</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44859</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>44978</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45902</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45372</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45903</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45903</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45903</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45594</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45594</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45043</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45868</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45909</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>46161</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45910</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45910</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45911</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45911</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>44903</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>45911</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>45910</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45915</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>44970</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45917</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45912</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45924</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45924</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>45791</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45902</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45924</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45925</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45161</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45926</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45562</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>45926</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>46167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>44890</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>45833</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45926</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45834</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>46038</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>46171</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>46171</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>45371</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>45243</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45373</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45631</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>45176</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>46175</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>45056</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45940</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45940</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45940</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45166</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>46171</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>46171</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>46171</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46171</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>46163</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>46171</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45208</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>46176</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46167</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45450</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45110</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45944</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45551</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>44853</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45938</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45105</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45119</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44967</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45554</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45952</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>46142</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>45520</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>45954</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>45954</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45954</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>45954</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>46163</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45954</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45954</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>45954</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45954</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45481</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45512</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45297</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>45957</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45218</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45954</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45957</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>46185</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>46185</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45644</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45891</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45891</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45963</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45924</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45904</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45611</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45966</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45965</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45965</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>46190</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>46190</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>46190</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>46183</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>45602</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45968</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>46190</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>46191</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45972</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45971</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>45971</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45103</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45971</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45971</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>46030</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>46160</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45974</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45974</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45973</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45974</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45973</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>46146</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>46146</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>46160</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45973</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>45973</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45974</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>45680</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>46160</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>46160</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45974</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45975</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>46198</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>46171</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>46155</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45579</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45579</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>46190</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>46205</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45981</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>46142</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>45317</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>45929</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45929</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>46167</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>46206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45379</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>45988</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45988</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45909</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>46206</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45989</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>46195</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45989</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45989</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45989</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45212</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>46198</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>46198</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>46195</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>46154</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>46198</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45995</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45995</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45995</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>46195</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>46195</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>46195</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45646</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45317</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>46195</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>46142</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>46195</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>46195</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>46195</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45685</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>46195</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>46195</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>46217</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>46218</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>46219</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>44883</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>45485</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45743</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>46001</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>46001</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>46225</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>45784</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>46230</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45784</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45545</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>46206</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>46230</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>46007</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>46008</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>46007</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>46008</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>46008</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>46008</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>46008</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>46008</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46008</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>46008</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44852</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>46280</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>46279</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>46279</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>45565</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35340,7 +35340,7 @@
         <v>45460</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>45230</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>46010</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>46010</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>46009</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>46233</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>46009</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>45581</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45609</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>46280</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45581</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>46279</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>46281</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>45134</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>45789</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45789</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45600</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>45533</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45569</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>46282</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45789</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>45789</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45586</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45581</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45560</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>45791</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>45786</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>46029</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>46241</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45524</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>46241</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45453</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45541</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>46241</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>46283</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>46283</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>46241</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>46241</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>46283</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>46283</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>46287</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>46002</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>46287</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45796</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44915</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45499</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45791</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45776</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45791</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45791</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>45961</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45961</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45770</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>45800</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39507,7 +39507,7 @@
         <v>46288</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>46247</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>46290</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45799</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45800</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>46247</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>46286</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>46290</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45805</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45810</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45810</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>46286</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>46290</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45810</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>46290</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>46294</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>46248</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45569</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40896,7 +40896,7 @@
         <v>45813</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>45813</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>45813</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>45813</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>46294</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>46294</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>46294</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>45831</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>46294</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>45224</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>46007</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45824</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41817,7 +41817,7 @@
         <v>45826</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45826</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45827</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45832</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>45831</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45831</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>46255</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46255</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>46255</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45835</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46255</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45621</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>46122</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45840</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45840</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>46255</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>45502</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>46255</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45845</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>46255</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45502</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>45474</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>44844</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>46301</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>46258</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>45849</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45525</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>46253</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45825</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44054,7 +44054,7 @@
         <v>46258</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>44895</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45512</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>45832</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>45832</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44444,7 +44444,7 @@
         <v>45840</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45512</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45512</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45832</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>46247</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44834,7 +44834,7 @@
         <v>46114</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45567</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>46119</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>44680</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>46204</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>46260</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>45869</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45337</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>46260</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>46122</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>44994</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>46122</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>46122</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45761</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46126</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46126</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>46126</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45875</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>46220</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45887</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44515</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>46128</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>46265</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>46134</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>46307</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45562</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>46286</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45975</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45596</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>46265</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45519</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>46262</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>44893</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>44893</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>46307</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47514,7 +47514,7 @@
         <v>45849</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>45960</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>46062</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>46267</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>46267</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45825</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>45849</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>46309</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45603</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45845</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>46066</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45827</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48440,7 +48440,7 @@
         <v>45968</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>46290</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48596,7 +48596,7 @@
         <v>46272</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45225</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>46311</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>46290</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48903,7 +48903,7 @@
         <v>45954</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>46314</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>45988</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45971</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>45835</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>46267</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49361,7 +49361,7 @@
         <v>44893</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>46314</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>45560</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45531</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>46273</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49746,7 +49746,7 @@
         <v>46315</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45562</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>45860</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>46273</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50058,7 +50058,7 @@
         <v>45902</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>46315</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50209,7 +50209,7 @@
         <v>46171</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50282,7 +50282,7 @@
         <v>45574</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>46273</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50433,7 +50433,7 @@
         <v>46037</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>45062</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>46273</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50662,7 +50662,7 @@
         <v>46318</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45588</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>46318</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>46318</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>46141</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51047,7 +51047,7 @@
         <v>46141</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45581</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>46260</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51276,7 +51276,7 @@
         <v>46141</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45622</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>45622</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51510,7 +51510,7 @@
         <v>46142</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>46318</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>46318</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51744,7 +51744,7 @@
         <v>46276</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>46142</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>46062</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>46318</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>46275</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>46148</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45579</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>46150</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>46150</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>46148</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>45740</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45187</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>45973</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45883</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>46142</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>46155</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45623</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53035,7 +53035,7 @@
         <v>45679</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>46155</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53186,7 +53186,7 @@
         <v>46155</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>46155</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53342,7 +53342,7 @@
         <v>46113</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>44970</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>46160</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>44711</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>44960</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53727,7 +53727,7 @@
         <v>46160</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>45624</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45603</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45629</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54034,7 +54034,7 @@
         <v>45625</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         <v>45301</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>45519</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54253,7 +54253,7 @@
         <v>45593</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54331,7 +54331,7 @@
         <v>45062</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>45210</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54487,7 +54487,7 @@
         <v>45638</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54560,7 +54560,7 @@
         <v>45644</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>45568</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54711,7 +54711,7 @@
         <v>44729</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54789,7 +54789,7 @@
         <v>44581</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54867,7 +54867,7 @@
         <v>44820</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>44820</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55023,7 +55023,7 @@
         <v>45687</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55096,7 +55096,7 @@
         <v>45762</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45765</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>44916</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55320,7 +55320,7 @@
         <v>45497</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45106</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55466,7 +55466,7 @@
         <v>45411</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>44942</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55617,7 +55617,7 @@
         <v>45603</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>44730</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>45637</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>45099</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55924,7 +55924,7 @@
         <v>45265</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>45288</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56070,7 +56070,7 @@
         <v>44865</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56148,7 +56148,7 @@
         <v>45399</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56226,7 +56226,7 @@
         <v>45569</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45258</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>45404</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56450,7 +56450,7 @@
         <v>45110</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56523,7 +56523,7 @@
         <v>44533</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56601,7 +56601,7 @@
         <v>45572</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56679,7 +56679,7 @@
         <v>45488</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56752,7 +56752,7 @@
         <v>45113</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45602</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45112</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>45644</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57054,7 +57054,7 @@
         <v>45639</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57132,7 +57132,7 @@
         <v>45569</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>45541</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>45622</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57366,7 +57366,7 @@
         <v>45189</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>45191</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57517,7 +57517,7 @@
         <v>45622</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57595,7 +57595,7 @@
         <v>45594</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57673,7 +57673,7 @@
         <v>45198</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45512</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45622</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57907,7 +57907,7 @@
         <v>45622</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45099</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45687</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58136,7 +58136,7 @@
         <v>45168</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58214,7 +58214,7 @@
         <v>45208</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58292,7 +58292,7 @@
         <v>44789</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58365,7 +58365,7 @@
         <v>45166</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58443,7 +58443,7 @@
         <v>44708</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58521,7 +58521,7 @@
         <v>44687</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>45210</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>44841</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58745,7 +58745,7 @@
         <v>45754</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>45645</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58901,7 +58901,7 @@
         <v>45244</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58974,7 +58974,7 @@
         <v>45156</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59047,7 +59047,7 @@
         <v>45219</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59125,7 +59125,7 @@
         <v>45253</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45253</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59281,7 +59281,7 @@
         <v>45198</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59359,7 +59359,7 @@
         <v>45208</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59432,7 +59432,7 @@
         <v>45246</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59505,7 +59505,7 @@
         <v>45754</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>45744</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59661,7 +59661,7 @@
         <v>44771</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>44915</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59812,7 +59812,7 @@
         <v>44859</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59890,7 +59890,7 @@
         <v>45243</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59963,7 +59963,7 @@
         <v>45616</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>45279</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60114,7 +60114,7 @@
         <v>45301</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45775</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60265,7 +60265,7 @@
         <v>44879</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>44970</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60416,7 +60416,7 @@
         <v>44552</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>44730</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60567,7 +60567,7 @@
         <v>44599</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>44859</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>44960</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60796,7 +60796,7 @@
         <v>45167</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60874,7 +60874,7 @@
         <v>45015</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45216</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61030,7 +61030,7 @@
         <v>45400</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61108,7 +61108,7 @@
         <v>45391</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61186,7 +61186,7 @@
         <v>44805</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>45015</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>46190</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>

--- a/Översikt LUDVIKA.xlsx
+++ b/Översikt LUDVIKA.xlsx
@@ -601,7 +601,7 @@
         <v>45791</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -728,7 +728,7 @@
         <v>45275</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>45835</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
         <v>45940</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1122,7 +1122,7 @@
         <v>45961</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
         <v>45993</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1374,7 +1374,7 @@
         <v>46058</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1499,7 +1499,7 @@
         <v>44631</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1621,7 +1621,7 @@
         <v>44937</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1863,7 +1863,7 @@
         <v>45629</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1987,7 +1987,7 @@
         <v>45847</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>45981</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2234,7 +2234,7 @@
         <v>46275</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>46163</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2474,7 +2474,7 @@
         <v>45849</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>45786</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2704,7 +2704,7 @@
         <v>46058</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2825,7 +2825,7 @@
         <v>45509</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>45945</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3054,7 +3054,7 @@
         <v>45597</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
         <v>45786</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3291,7 +3291,7 @@
         <v>45981</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3416,7 +3416,7 @@
         <v>44844</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3536,7 +3536,7 @@
         <v>46279</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>46170</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>46167</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45957</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>45971</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         <v>46010</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>45842</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4363,7 +4363,7 @@
         <v>45785</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>45993</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4595,7 +4595,7 @@
         <v>45940</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>46163</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4828,7 +4828,7 @@
         <v>44694</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4942,7 +4942,7 @@
         <v>46163</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5060,7 +5060,7 @@
         <v>45930</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5178,7 +5178,7 @@
         <v>45541</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5292,7 +5292,7 @@
         <v>46010</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>46253</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5528,7 +5528,7 @@
         <v>46216</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>46163</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5758,7 +5758,7 @@
         <v>46163</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>45926</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5988,7 +5988,7 @@
         <v>45985</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>46198</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>46283</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>45596</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>46265</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6569,7 +6569,7 @@
         <v>45929</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6686,7 +6686,7 @@
         <v>45373</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6798,7 +6798,7 @@
         <v>45607</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>46260</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -7023,7 +7023,7 @@
         <v>46163</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7135,7 +7135,7 @@
         <v>46155</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7252,7 +7252,7 @@
         <v>46260</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7368,7 +7368,7 @@
         <v>45246</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7480,7 +7480,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>45901</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>45105</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7824,7 +7824,7 @@
         <v>46128</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7940,7 +7940,7 @@
         <v>45791</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -8052,7 +8052,7 @@
         <v>44560</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8168,7 +8168,7 @@
         <v>45910</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8279,7 +8279,7 @@
         <v>46168</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>46170</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8511,7 +8511,7 @@
         <v>45916</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>45923</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8728,7 +8728,7 @@
         <v>45940</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>44872</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8954,7 +8954,7 @@
         <v>46125</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -9065,7 +9065,7 @@
         <v>46167</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9176,7 +9176,7 @@
         <v>45943</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9287,7 +9287,7 @@
         <v>45971</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45974</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>46198</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>45063</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
         <v>46198</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>44831</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>45978</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>45708</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>44994</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>44693</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10416,7 +10416,7 @@
         <v>46260</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10526,7 +10526,7 @@
         <v>45940</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10637,7 +10637,7 @@
         <v>46260</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10747,7 +10747,7 @@
         <v>45978</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10862,7 +10862,7 @@
         <v>46168</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10977,7 +10977,7 @@
         <v>46150</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44923</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>45518</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>45594</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11418,7 +11418,7 @@
         <v>45321</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11524,7 +11524,7 @@
         <v>45687</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11635,7 +11635,7 @@
         <v>46010</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11750,7 +11750,7 @@
         <v>44571</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11860,7 +11860,7 @@
         <v>44643</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11965,7 +11965,7 @@
         <v>44872</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>46163</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -12184,7 +12184,7 @@
         <v>46164</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12298,7 +12298,7 @@
         <v>45923</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12408,7 +12408,7 @@
         <v>46009</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>46175</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12622,7 +12622,7 @@
         <v>45463</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45866</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12841,7 +12841,7 @@
         <v>44929</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45992</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>46219</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>46008</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -13276,7 +13276,7 @@
         <v>45486</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>45791</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13495,7 +13495,7 @@
         <v>45993</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>46247</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13723,7 +13723,7 @@
         <v>45825</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13833,7 +13833,7 @@
         <v>44560</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13943,7 +13943,7 @@
         <v>46265</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -14053,7 +14053,7 @@
         <v>45596</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>46269</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -14273,7 +14273,7 @@
         <v>46314</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44888</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -14493,7 +14493,7 @@
         <v>46276</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14603,7 +14603,7 @@
         <v>45644</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>45093</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>44929</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>45114</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -15032,7 +15032,7 @@
         <v>44960</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>45189</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -15247,7 +15247,7 @@
         <v>45761</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -15356,7 +15356,7 @@
         <v>45089</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -15461,7 +15461,7 @@
         <v>44998</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>45131</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15671,7 +15671,7 @@
         <v>45321</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15776,7 +15776,7 @@
         <v>44706</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15881,7 +15881,7 @@
         <v>45761</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44771</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>44869</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>44502</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>44503</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -16283,7 +16283,7 @@
         <v>44550</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16361,7 +16361,7 @@
         <v>44730</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44771</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>44730</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>44851</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16663,7 +16663,7 @@
         <v>44872</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>44720</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>44560</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16892,7 +16892,7 @@
         <v>44658</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>44827</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -17043,7 +17043,7 @@
         <v>44590</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -17116,7 +17116,7 @@
         <v>44706</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -17194,7 +17194,7 @@
         <v>44785</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17272,7 +17272,7 @@
         <v>44616</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17345,7 +17345,7 @@
         <v>44508</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>44715</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17501,7 +17501,7 @@
         <v>45541</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17579,7 +17579,7 @@
         <v>45813</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45799</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17735,7 +17735,7 @@
         <v>45537</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17813,7 +17813,7 @@
         <v>44819</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45705</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45607</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>45219</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -18120,7 +18120,7 @@
         <v>45335</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -18193,7 +18193,7 @@
         <v>44825</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18271,7 +18271,7 @@
         <v>45196</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>45202</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>45891</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18505,7 +18505,7 @@
         <v>45205</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45895</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45071</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>44826</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18812,7 +18812,7 @@
         <v>45898</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18890,7 +18890,7 @@
         <v>45526</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18963,7 +18963,7 @@
         <v>44825</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>44859</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -19114,7 +19114,7 @@
         <v>45898</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -19192,7 +19192,7 @@
         <v>44978</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -19265,7 +19265,7 @@
         <v>45902</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45372</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19416,7 +19416,7 @@
         <v>45903</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>45903</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19572,7 +19572,7 @@
         <v>45903</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19650,7 +19650,7 @@
         <v>45594</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19728,7 +19728,7 @@
         <v>45594</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19806,7 +19806,7 @@
         <v>45043</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45868</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45909</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -20030,7 +20030,7 @@
         <v>46161</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>45910</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -20186,7 +20186,7 @@
         <v>45910</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>45911</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
         <v>45911</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20415,7 +20415,7 @@
         <v>44903</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>45911</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>45910</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45915</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>44970</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45917</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20863,7 +20863,7 @@
         <v>45912</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45924</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
         <v>45924</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
         <v>45791</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -21175,7 +21175,7 @@
         <v>45902</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -21253,7 +21253,7 @@
         <v>45924</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45925</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21404,7 +21404,7 @@
         <v>45161</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45926</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45562</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>45926</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21711,7 +21711,7 @@
         <v>46167</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21789,7 +21789,7 @@
         <v>44890</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21867,7 +21867,7 @@
         <v>45833</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45926</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -22018,7 +22018,7 @@
         <v>45834</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>46038</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>46171</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -22242,7 +22242,7 @@
         <v>46171</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -22320,7 +22320,7 @@
         <v>45371</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22393,7 +22393,7 @@
         <v>45243</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45373</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22539,7 +22539,7 @@
         <v>45631</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22617,7 +22617,7 @@
         <v>45176</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22690,7 +22690,7 @@
         <v>46175</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22763,7 +22763,7 @@
         <v>45056</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22841,7 +22841,7 @@
         <v>45940</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45940</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22997,7 +22997,7 @@
         <v>45940</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45166</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -23153,7 +23153,7 @@
         <v>46171</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -23231,7 +23231,7 @@
         <v>46171</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -23309,7 +23309,7 @@
         <v>46171</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23387,7 +23387,7 @@
         <v>46171</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>46163</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23543,7 +23543,7 @@
         <v>46171</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23621,7 +23621,7 @@
         <v>45208</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23699,7 +23699,7 @@
         <v>46176</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23777,7 +23777,7 @@
         <v>46167</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>45450</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>45110</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45944</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>45551</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>44853</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -24225,7 +24225,7 @@
         <v>45938</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -24303,7 +24303,7 @@
         <v>45105</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -24376,7 +24376,7 @@
         <v>45119</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24454,7 +24454,7 @@
         <v>44967</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24527,7 +24527,7 @@
         <v>45554</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24600,7 +24600,7 @@
         <v>45952</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24673,7 +24673,7 @@
         <v>46142</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24751,7 +24751,7 @@
         <v>45520</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24824,7 +24824,7 @@
         <v>45954</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24897,7 +24897,7 @@
         <v>45954</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>46183</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>45954</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -25131,7 +25131,7 @@
         <v>45954</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>46163</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -25282,7 +25282,7 @@
         <v>45954</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45954</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>45954</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45954</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45481</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45512</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25735,7 +25735,7 @@
         <v>45297</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>45957</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25886,7 +25886,7 @@
         <v>45218</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25959,7 +25959,7 @@
         <v>45954</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -26032,7 +26032,7 @@
         <v>45957</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -26110,7 +26110,7 @@
         <v>46185</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -26188,7 +26188,7 @@
         <v>46185</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -26266,7 +26266,7 @@
         <v>45644</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -26339,7 +26339,7 @@
         <v>45891</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45891</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26495,7 +26495,7 @@
         <v>45963</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26573,7 +26573,7 @@
         <v>45924</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26651,7 +26651,7 @@
         <v>45904</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>45611</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>45966</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>45965</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>45965</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -27031,7 +27031,7 @@
         <v>46190</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -27109,7 +27109,7 @@
         <v>46190</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>46190</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>46183</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -27343,7 +27343,7 @@
         <v>45602</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -27416,7 +27416,7 @@
         <v>45968</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -27494,7 +27494,7 @@
         <v>46190</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>46191</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27645,7 +27645,7 @@
         <v>45972</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45971</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27801,7 +27801,7 @@
         <v>45971</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27879,7 +27879,7 @@
         <v>45103</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27952,7 +27952,7 @@
         <v>45971</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -28030,7 +28030,7 @@
         <v>45971</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -28108,7 +28108,7 @@
         <v>46030</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>46160</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -28259,7 +28259,7 @@
         <v>45974</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45974</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45973</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45974</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28571,7 +28571,7 @@
         <v>45973</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28649,7 +28649,7 @@
         <v>46146</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28727,7 +28727,7 @@
         <v>46146</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28805,7 +28805,7 @@
         <v>46160</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45973</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28961,7 +28961,7 @@
         <v>45973</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -29039,7 +29039,7 @@
         <v>45974</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -29117,7 +29117,7 @@
         <v>45680</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>46160</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>46160</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45974</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -29424,7 +29424,7 @@
         <v>45975</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -29502,7 +29502,7 @@
         <v>46198</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>46171</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>46155</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29736,7 +29736,7 @@
         <v>45579</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29809,7 +29809,7 @@
         <v>45579</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>46190</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29960,7 +29960,7 @@
         <v>46205</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45981</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -30116,7 +30116,7 @@
         <v>46142</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -30194,7 +30194,7 @@
         <v>45317</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -30267,7 +30267,7 @@
         <v>45929</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45929</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -30423,7 +30423,7 @@
         <v>46167</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -30501,7 +30501,7 @@
         <v>46206</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -30579,7 +30579,7 @@
         <v>45379</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30657,7 +30657,7 @@
         <v>45988</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30735,7 +30735,7 @@
         <v>45988</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45909</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30886,7 +30886,7 @@
         <v>46206</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45989</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>46195</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45989</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45989</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45989</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45212</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>46198</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>46198</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -31568,7 +31568,7 @@
         <v>46195</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -31646,7 +31646,7 @@
         <v>46154</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>46198</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31802,7 +31802,7 @@
         <v>45995</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45995</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31953,7 +31953,7 @@
         <v>45995</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>46195</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -32109,7 +32109,7 @@
         <v>46195</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -32187,7 +32187,7 @@
         <v>46195</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -32265,7 +32265,7 @@
         <v>45646</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>45317</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>46195</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>46142</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>46195</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>46195</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32723,7 +32723,7 @@
         <v>46195</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45685</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32874,7 +32874,7 @@
         <v>46195</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32952,7 +32952,7 @@
         <v>46195</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -33030,7 +33030,7 @@
         <v>46217</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -33108,7 +33108,7 @@
         <v>46218</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -33186,7 +33186,7 @@
         <v>46219</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>44883</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -33342,7 +33342,7 @@
         <v>45485</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -33420,7 +33420,7 @@
         <v>45743</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -33493,7 +33493,7 @@
         <v>46001</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -33571,7 +33571,7 @@
         <v>46001</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -33649,7 +33649,7 @@
         <v>46225</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33727,7 +33727,7 @@
         <v>45784</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33800,7 +33800,7 @@
         <v>46230</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45784</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>45545</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>46206</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>46230</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>46007</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>46008</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -34336,7 +34336,7 @@
         <v>46007</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>46008</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>46008</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>46008</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -34648,7 +34648,7 @@
         <v>46008</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -34726,7 +34726,7 @@
         <v>46008</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34804,7 +34804,7 @@
         <v>46008</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>46008</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34960,7 +34960,7 @@
         <v>44852</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
         <v>46280</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>46279</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>46279</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -35267,7 +35267,7 @@
         <v>45565</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -35340,7 +35340,7 @@
         <v>45460</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -35413,7 +35413,7 @@
         <v>45230</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -35491,7 +35491,7 @@
         <v>46010</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -35569,7 +35569,7 @@
         <v>46010</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>46009</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -35725,7 +35725,7 @@
         <v>46233</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35803,7 +35803,7 @@
         <v>46009</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35876,7 +35876,7 @@
         <v>45581</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35954,7 +35954,7 @@
         <v>45609</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -36032,7 +36032,7 @@
         <v>46280</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -36110,7 +36110,7 @@
         <v>45581</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -36188,7 +36188,7 @@
         <v>46279</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>46281</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -36344,7 +36344,7 @@
         <v>45134</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -36422,7 +36422,7 @@
         <v>45789</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -36500,7 +36500,7 @@
         <v>45789</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45600</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -36651,7 +36651,7 @@
         <v>45533</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -36729,7 +36729,7 @@
         <v>45569</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36807,7 +36807,7 @@
         <v>46282</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36885,7 +36885,7 @@
         <v>45789</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36963,7 +36963,7 @@
         <v>45789</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -37041,7 +37041,7 @@
         <v>45586</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -37114,7 +37114,7 @@
         <v>45581</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -37192,7 +37192,7 @@
         <v>45560</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -37270,7 +37270,7 @@
         <v>45791</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -37348,7 +37348,7 @@
         <v>45786</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -37421,7 +37421,7 @@
         <v>46029</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>46241</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -37577,7 +37577,7 @@
         <v>45524</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -37655,7 +37655,7 @@
         <v>46241</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45453</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>45541</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37889,7 +37889,7 @@
         <v>46241</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37962,7 +37962,7 @@
         <v>46283</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>46283</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>46241</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -38196,7 +38196,7 @@
         <v>46241</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -38274,7 +38274,7 @@
         <v>46283</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -38352,7 +38352,7 @@
         <v>46283</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -38430,7 +38430,7 @@
         <v>46287</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -38508,7 +38508,7 @@
         <v>46002</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -38586,7 +38586,7 @@
         <v>46287</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -38664,7 +38664,7 @@
         <v>45796</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44915</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -38820,7 +38820,7 @@
         <v>45499</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38893,7 +38893,7 @@
         <v>45791</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38971,7 +38971,7 @@
         <v>45776</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -39044,7 +39044,7 @@
         <v>45791</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -39122,7 +39122,7 @@
         <v>45791</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -39200,7 +39200,7 @@
         <v>45961</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -39278,7 +39278,7 @@
         <v>45961</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -39356,7 +39356,7 @@
         <v>45770</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -39429,7 +39429,7 @@
         <v>45800</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -39507,7 +39507,7 @@
         <v>46288</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>46247</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>46290</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45799</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -39814,7 +39814,7 @@
         <v>45800</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>46247</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39965,7 +39965,7 @@
         <v>46286</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>46290</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -40121,7 +40121,7 @@
         <v>45805</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45810</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -40277,7 +40277,7 @@
         <v>45810</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -40355,7 +40355,7 @@
         <v>46286</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -40433,7 +40433,7 @@
         <v>46290</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -40511,7 +40511,7 @@
         <v>45810</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -40589,7 +40589,7 @@
         <v>46290</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -40667,7 +40667,7 @@
         <v>46294</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -40745,7 +40745,7 @@
         <v>46248</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -40818,7 +40818,7 @@
         <v>45569</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -40896,7 +40896,7 @@
         <v>45813</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40974,7 +40974,7 @@
         <v>45813</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -41052,7 +41052,7 @@
         <v>45813</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>45813</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>46294</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>46294</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>46294</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -41442,7 +41442,7 @@
         <v>45831</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -41515,7 +41515,7 @@
         <v>46294</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -41593,7 +41593,7 @@
         <v>45224</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -41666,7 +41666,7 @@
         <v>46007</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -41744,7 +41744,7 @@
         <v>45824</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -41817,7 +41817,7 @@
         <v>45826</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45826</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45827</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45832</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -42129,7 +42129,7 @@
         <v>45831</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45831</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -42285,7 +42285,7 @@
         <v>46255</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -42363,7 +42363,7 @@
         <v>46255</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>46255</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -42519,7 +42519,7 @@
         <v>45835</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46255</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45621</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -42753,7 +42753,7 @@
         <v>46122</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -42831,7 +42831,7 @@
         <v>45840</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -42909,7 +42909,7 @@
         <v>45840</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -42982,7 +42982,7 @@
         <v>46255</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>45502</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>46255</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -43211,7 +43211,7 @@
         <v>45845</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -43289,7 +43289,7 @@
         <v>46255</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -43367,7 +43367,7 @@
         <v>45502</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -43445,7 +43445,7 @@
         <v>45474</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -43518,7 +43518,7 @@
         <v>44844</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>46301</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -43669,7 +43669,7 @@
         <v>46258</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -43747,7 +43747,7 @@
         <v>45849</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -43825,7 +43825,7 @@
         <v>45525</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -43898,7 +43898,7 @@
         <v>46253</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -43976,7 +43976,7 @@
         <v>45825</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -44054,7 +44054,7 @@
         <v>46258</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>44895</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -44210,7 +44210,7 @@
         <v>45512</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -44288,7 +44288,7 @@
         <v>45832</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -44366,7 +44366,7 @@
         <v>45832</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -44444,7 +44444,7 @@
         <v>45840</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -44522,7 +44522,7 @@
         <v>45512</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -44600,7 +44600,7 @@
         <v>45512</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -44678,7 +44678,7 @@
         <v>45832</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -44756,7 +44756,7 @@
         <v>46247</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -44834,7 +44834,7 @@
         <v>46114</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -44912,7 +44912,7 @@
         <v>45567</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>46119</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -45068,7 +45068,7 @@
         <v>44680</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -45146,7 +45146,7 @@
         <v>46204</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>46260</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>45869</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>45337</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>46260</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>46122</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>44994</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>46122</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>46122</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -45828,7 +45828,7 @@
         <v>45761</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46126</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46126</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -46057,7 +46057,7 @@
         <v>46126</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -46135,7 +46135,7 @@
         <v>45875</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -46208,7 +46208,7 @@
         <v>46220</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -46286,7 +46286,7 @@
         <v>45887</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -46364,7 +46364,7 @@
         <v>44515</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -46442,7 +46442,7 @@
         <v>46128</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>46265</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -46593,7 +46593,7 @@
         <v>46134</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -46671,7 +46671,7 @@
         <v>46307</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -46749,7 +46749,7 @@
         <v>45562</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -46827,7 +46827,7 @@
         <v>46286</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -46905,7 +46905,7 @@
         <v>45975</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -46983,7 +46983,7 @@
         <v>45596</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -47061,7 +47061,7 @@
         <v>46265</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -47139,7 +47139,7 @@
         <v>45519</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>46262</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -47290,7 +47290,7 @@
         <v>44893</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>44893</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -47436,7 +47436,7 @@
         <v>46307</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -47514,7 +47514,7 @@
         <v>45849</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -47592,7 +47592,7 @@
         <v>45960</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -47670,7 +47670,7 @@
         <v>46062</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>46267</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>46267</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -47904,7 +47904,7 @@
         <v>45825</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -47977,7 +47977,7 @@
         <v>45849</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -48055,7 +48055,7 @@
         <v>46309</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -48128,7 +48128,7 @@
         <v>45603</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -48206,7 +48206,7 @@
         <v>45845</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>46066</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45827</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -48440,7 +48440,7 @@
         <v>45968</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -48518,7 +48518,7 @@
         <v>46290</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -48596,7 +48596,7 @@
         <v>46272</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -48669,7 +48669,7 @@
         <v>45225</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>46311</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -48825,7 +48825,7 @@
         <v>46290</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -48903,7 +48903,7 @@
         <v>45954</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -48976,7 +48976,7 @@
         <v>46314</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -49054,7 +49054,7 @@
         <v>45988</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45971</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -49210,7 +49210,7 @@
         <v>45835</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -49288,7 +49288,7 @@
         <v>46267</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -49361,7 +49361,7 @@
         <v>44893</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>46314</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>45560</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -49590,7 +49590,7 @@
         <v>45531</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -49668,7 +49668,7 @@
         <v>46273</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -49746,7 +49746,7 @@
         <v>46315</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -49824,7 +49824,7 @@
         <v>45562</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -49902,7 +49902,7 @@
         <v>45860</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -49980,7 +49980,7 @@
         <v>46273</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -50058,7 +50058,7 @@
         <v>45902</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -50131,7 +50131,7 @@
         <v>46315</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -50209,7 +50209,7 @@
         <v>46171</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -50282,7 +50282,7 @@
         <v>45574</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>46273</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -50433,7 +50433,7 @@
         <v>46037</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -50506,7 +50506,7 @@
         <v>45062</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -50584,7 +50584,7 @@
         <v>46273</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -50662,7 +50662,7 @@
         <v>46318</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45588</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>46318</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -50891,7 +50891,7 @@
         <v>46318</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -50969,7 +50969,7 @@
         <v>46141</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -51047,7 +51047,7 @@
         <v>46141</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -51125,7 +51125,7 @@
         <v>45581</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -51203,7 +51203,7 @@
         <v>46260</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -51276,7 +51276,7 @@
         <v>46141</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -51354,7 +51354,7 @@
         <v>45622</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>45622</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -51510,7 +51510,7 @@
         <v>46142</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -51588,7 +51588,7 @@
         <v>46318</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -51666,7 +51666,7 @@
         <v>46318</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -51744,7 +51744,7 @@
         <v>46276</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -51817,7 +51817,7 @@
         <v>46142</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -51895,7 +51895,7 @@
         <v>46062</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -51973,7 +51973,7 @@
         <v>46318</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -52046,7 +52046,7 @@
         <v>46275</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>46148</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -52197,7 +52197,7 @@
         <v>45579</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -52270,7 +52270,7 @@
         <v>46150</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -52348,7 +52348,7 @@
         <v>46150</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -52426,7 +52426,7 @@
         <v>46148</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -52504,7 +52504,7 @@
         <v>45740</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -52577,7 +52577,7 @@
         <v>45187</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -52655,7 +52655,7 @@
         <v>45973</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45883</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>46142</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>46155</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>45623</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -53035,7 +53035,7 @@
         <v>45679</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>46155</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -53186,7 +53186,7 @@
         <v>46155</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -53264,7 +53264,7 @@
         <v>46155</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -53342,7 +53342,7 @@
         <v>46113</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -53415,7 +53415,7 @@
         <v>44970</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -53493,7 +53493,7 @@
         <v>46160</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -53571,7 +53571,7 @@
         <v>44711</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -53649,7 +53649,7 @@
         <v>44960</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -53727,7 +53727,7 @@
         <v>46160</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -53805,7 +53805,7 @@
         <v>45624</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -53878,7 +53878,7 @@
         <v>45603</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -53956,7 +53956,7 @@
         <v>45629</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -54034,7 +54034,7 @@
         <v>45625</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -54107,7 +54107,7 @@
         <v>45301</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -54180,7 +54180,7 @@
         <v>45519</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -54253,7 +54253,7 @@
         <v>45593</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -54331,7 +54331,7 @@
         <v>45062</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -54409,7 +54409,7 @@
         <v>45210</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -54487,7 +54487,7 @@
         <v>45638</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -54560,7 +54560,7 @@
         <v>45644</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -54638,7 +54638,7 @@
         <v>45568</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -54711,7 +54711,7 @@
         <v>44729</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -54789,7 +54789,7 @@
         <v>44581</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -54867,7 +54867,7 @@
         <v>44820</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -54945,7 +54945,7 @@
         <v>44820</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -55023,7 +55023,7 @@
         <v>45687</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -55096,7 +55096,7 @@
         <v>45762</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -55169,7 +55169,7 @@
         <v>45765</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -55242,7 +55242,7 @@
         <v>44916</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -55320,7 +55320,7 @@
         <v>45497</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -55393,7 +55393,7 @@
         <v>45106</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -55466,7 +55466,7 @@
         <v>45411</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -55544,7 +55544,7 @@
         <v>44942</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -55617,7 +55617,7 @@
         <v>45603</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -55695,7 +55695,7 @@
         <v>44730</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -55773,7 +55773,7 @@
         <v>45637</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -55846,7 +55846,7 @@
         <v>45099</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -55924,7 +55924,7 @@
         <v>45265</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -55997,7 +55997,7 @@
         <v>45288</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -56070,7 +56070,7 @@
         <v>44865</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -56148,7 +56148,7 @@
         <v>45399</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -56226,7 +56226,7 @@
         <v>45569</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -56304,7 +56304,7 @@
         <v>45258</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -56377,7 +56377,7 @@
         <v>45404</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -56450,7 +56450,7 @@
         <v>45110</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -56523,7 +56523,7 @@
         <v>44533</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -56601,7 +56601,7 @@
         <v>45572</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -56679,7 +56679,7 @@
         <v>45488</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -56752,7 +56752,7 @@
         <v>45113</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -56830,7 +56830,7 @@
         <v>45602</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -56903,7 +56903,7 @@
         <v>45112</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -56981,7 +56981,7 @@
         <v>45644</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -57054,7 +57054,7 @@
         <v>45639</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -57132,7 +57132,7 @@
         <v>45569</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -57210,7 +57210,7 @@
         <v>45541</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -57288,7 +57288,7 @@
         <v>45622</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -57366,7 +57366,7 @@
         <v>45189</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -57439,7 +57439,7 @@
         <v>45191</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -57517,7 +57517,7 @@
         <v>45622</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -57595,7 +57595,7 @@
         <v>45594</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -57673,7 +57673,7 @@
         <v>45198</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45512</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>45622</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -57907,7 +57907,7 @@
         <v>45622</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -57985,7 +57985,7 @@
         <v>45099</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -58063,7 +58063,7 @@
         <v>45687</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -58136,7 +58136,7 @@
         <v>45168</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -58214,7 +58214,7 @@
         <v>45208</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -58292,7 +58292,7 @@
         <v>44789</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -58365,7 +58365,7 @@
         <v>45166</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -58443,7 +58443,7 @@
         <v>44708</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -58521,7 +58521,7 @@
         <v>44687</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -58594,7 +58594,7 @@
         <v>45210</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>44841</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -58745,7 +58745,7 @@
         <v>45754</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -58823,7 +58823,7 @@
         <v>45645</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -58901,7 +58901,7 @@
         <v>45244</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -58974,7 +58974,7 @@
         <v>45156</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -59047,7 +59047,7 @@
         <v>45219</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -59125,7 +59125,7 @@
         <v>45253</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -59203,7 +59203,7 @@
         <v>45253</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -59281,7 +59281,7 @@
         <v>45198</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -59359,7 +59359,7 @@
         <v>45208</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -59432,7 +59432,7 @@
         <v>45246</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -59505,7 +59505,7 @@
         <v>45754</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>45744</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -59661,7 +59661,7 @@
         <v>44771</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -59734,7 +59734,7 @@
         <v>44915</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -59812,7 +59812,7 @@
         <v>44859</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -59890,7 +59890,7 @@
         <v>45243</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -59963,7 +59963,7 @@
         <v>45616</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -60041,7 +60041,7 @@
         <v>45279</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -60114,7 +60114,7 @@
         <v>45301</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45775</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -60265,7 +60265,7 @@
         <v>44879</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -60338,7 +60338,7 @@
         <v>44970</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -60416,7 +60416,7 @@
         <v>44552</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -60489,7 +60489,7 @@
         <v>44730</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -60567,7 +60567,7 @@
         <v>44599</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -60640,7 +60640,7 @@
         <v>44859</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -60718,7 +60718,7 @@
         <v>44960</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -60796,7 +60796,7 @@
         <v>45167</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -60874,7 +60874,7 @@
         <v>45015</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -60952,7 +60952,7 @@
         <v>45216</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -61030,7 +61030,7 @@
         <v>45400</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -61108,7 +61108,7 @@
         <v>45391</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -61186,7 +61186,7 @@
         <v>44805</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -61264,7 +61264,7 @@
         <v>45015</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -61342,7 +61342,7 @@
         <v>46190</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
